--- a/artfynd/A 61324-2022 artfynd.xlsx
+++ b/artfynd/A 61324-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 61324-2022 artfynd.xlsx
+++ b/artfynd/A 61324-2022 artfynd.xlsx
@@ -1121,10 +1121,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123548423</v>
+        <v>123549099</v>
       </c>
       <c r="B6" t="n">
-        <v>78511</v>
+        <v>78775</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1137,21 +1137,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459082</v>
+        <v>459197</v>
       </c>
       <c r="R6" t="n">
-        <v>6808839</v>
+        <v>6808824</v>
       </c>
       <c r="S6" t="n">
         <v>9</v>
@@ -1196,7 +1196,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,7 +1233,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123549099</v>
+        <v>123549137</v>
       </c>
       <c r="B7" t="n">
         <v>78775</v>
@@ -1269,17 +1269,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Andljusen, Andljusen, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>459197</v>
+        <v>459240</v>
       </c>
       <c r="R7" t="n">
-        <v>6808824</v>
+        <v>6808796</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1333,22 +1333,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123549137</v>
+        <v>123548423</v>
       </c>
       <c r="B8" t="n">
-        <v>78775</v>
+        <v>78511</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1361,37 +1361,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>459240</v>
+        <v>459082</v>
       </c>
       <c r="R8" t="n">
-        <v>6808796</v>
+        <v>6808839</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1445,12 +1445,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -2246,7 +2246,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123549200</v>
+        <v>123549662</v>
       </c>
       <c r="B16" t="n">
         <v>78775</v>
@@ -2286,13 +2286,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>459265</v>
+        <v>459479</v>
       </c>
       <c r="R16" t="n">
-        <v>6808827</v>
+        <v>6808853</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2346,19 +2346,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123549662</v>
+        <v>123549200</v>
       </c>
       <c r="B17" t="n">
         <v>78775</v>
@@ -2398,13 +2398,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>459479</v>
+        <v>459265</v>
       </c>
       <c r="R17" t="n">
-        <v>6808853</v>
+        <v>6808827</v>
       </c>
       <c r="S17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2458,12 +2458,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -6995,10 +6995,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123575257</v>
+        <v>123573768</v>
       </c>
       <c r="B58" t="n">
-        <v>78512</v>
+        <v>78775</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7011,21 +7011,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7035,13 +7035,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>459595</v>
+        <v>459699</v>
       </c>
       <c r="R58" t="n">
-        <v>6808516</v>
+        <v>6808517</v>
       </c>
       <c r="S58" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7070,7 +7070,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7080,7 +7080,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>På tallstammar</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7095,22 +7100,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123573768</v>
+        <v>123575257</v>
       </c>
       <c r="B59" t="n">
-        <v>78775</v>
+        <v>78512</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7123,21 +7128,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7147,13 +7152,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>459699</v>
+        <v>459595</v>
       </c>
       <c r="R59" t="n">
-        <v>6808517</v>
+        <v>6808516</v>
       </c>
       <c r="S59" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7182,7 +7187,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7192,12 +7197,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:27</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>På tallstammar</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7212,12 +7212,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -8023,10 +8023,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123577958</v>
+        <v>123566093</v>
       </c>
       <c r="B67" t="n">
-        <v>79364</v>
+        <v>78512</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8039,37 +8039,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>459571</v>
+        <v>459675</v>
       </c>
       <c r="R67" t="n">
-        <v>6808546</v>
+        <v>6808804</v>
       </c>
       <c r="S67" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8108,7 +8108,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8135,10 +8135,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123575840</v>
+        <v>123577958</v>
       </c>
       <c r="B68" t="n">
-        <v>78512</v>
+        <v>79364</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8151,21 +8151,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8175,13 +8175,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>459570</v>
+        <v>459571</v>
       </c>
       <c r="R68" t="n">
-        <v>6808531</v>
+        <v>6808546</v>
       </c>
       <c r="S68" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8210,7 +8210,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8247,10 +8247,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123576513</v>
+        <v>123575840</v>
       </c>
       <c r="B69" t="n">
-        <v>78775</v>
+        <v>78512</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8263,21 +8263,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>459499</v>
+        <v>459570</v>
       </c>
       <c r="R69" t="n">
-        <v>6808540</v>
+        <v>6808531</v>
       </c>
       <c r="S69" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8332,12 +8332,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:29</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>På Granar</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8352,22 +8347,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123566093</v>
+        <v>123576513</v>
       </c>
       <c r="B70" t="n">
-        <v>78512</v>
+        <v>78775</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8380,37 +8375,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>459675</v>
+        <v>459499</v>
       </c>
       <c r="R70" t="n">
-        <v>6808804</v>
+        <v>6808540</v>
       </c>
       <c r="S70" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8439,7 +8434,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8449,7 +8444,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>På Granar</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8464,12 +8464,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>

--- a/artfynd/A 61324-2022 artfynd.xlsx
+++ b/artfynd/A 61324-2022 artfynd.xlsx
@@ -1569,10 +1569,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123548646</v>
+        <v>123548439</v>
       </c>
       <c r="B10" t="n">
-        <v>78518</v>
+        <v>78781</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1585,34 +1585,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>459185</v>
+        <v>459138</v>
       </c>
       <c r="R10" t="n">
-        <v>6808785</v>
+        <v>6808765</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1681,7 +1681,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123548439</v>
+        <v>123549501</v>
       </c>
       <c r="B11" t="n">
         <v>78781</v>
@@ -1717,17 +1717,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Andljusen, Andljusen, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>459138</v>
+        <v>459367</v>
       </c>
       <c r="R11" t="n">
-        <v>6808765</v>
+        <v>6808792</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1781,22 +1781,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123549501</v>
+        <v>123548646</v>
       </c>
       <c r="B12" t="n">
-        <v>78781</v>
+        <v>78518</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1809,37 +1809,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>459367</v>
+        <v>459185</v>
       </c>
       <c r="R12" t="n">
-        <v>6808792</v>
+        <v>6808785</v>
       </c>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1893,12 +1893,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -4496,10 +4496,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123549577</v>
+        <v>123549418</v>
       </c>
       <c r="B36" t="n">
-        <v>78781</v>
+        <v>56697</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4508,38 +4508,43 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>459420</v>
+        <v>459318</v>
       </c>
       <c r="R36" t="n">
-        <v>6808812</v>
+        <v>6808809</v>
       </c>
       <c r="S36" t="n">
         <v>9</v>
@@ -4571,7 +4576,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4581,7 +4586,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Under betestall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4608,7 +4618,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123548371</v>
+        <v>123549577</v>
       </c>
       <c r="B37" t="n">
         <v>78781</v>
@@ -4644,17 +4654,17 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Andljusen, Andljusen, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>459133</v>
+        <v>459420</v>
       </c>
       <c r="R37" t="n">
-        <v>6808760</v>
+        <v>6808812</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4683,7 +4693,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4693,7 +4703,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4708,19 +4718,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123549730</v>
+        <v>123548371</v>
       </c>
       <c r="B38" t="n">
         <v>78781</v>
@@ -4756,17 +4766,17 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>459461</v>
+        <v>459133</v>
       </c>
       <c r="R38" t="n">
-        <v>6808868</v>
+        <v>6808760</v>
       </c>
       <c r="S38" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4795,7 +4805,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4805,7 +4815,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4820,19 +4830,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123549689</v>
+        <v>123549730</v>
       </c>
       <c r="B39" t="n">
         <v>78781</v>
@@ -4872,10 +4882,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>459457</v>
+        <v>459461</v>
       </c>
       <c r="R39" t="n">
-        <v>6808865</v>
+        <v>6808868</v>
       </c>
       <c r="S39" t="n">
         <v>9</v>
@@ -4907,7 +4917,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4917,7 +4927,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4944,10 +4954,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123549418</v>
+        <v>123549689</v>
       </c>
       <c r="B40" t="n">
-        <v>56697</v>
+        <v>78781</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4956,43 +4966,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>459318</v>
+        <v>459457</v>
       </c>
       <c r="R40" t="n">
-        <v>6808809</v>
+        <v>6808865</v>
       </c>
       <c r="S40" t="n">
         <v>9</v>
@@ -5024,7 +5029,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5034,12 +5039,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>17:21</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Under betestall</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -6766,10 +6766,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123575257</v>
+        <v>123574181</v>
       </c>
       <c r="B56" t="n">
-        <v>78518</v>
+        <v>78781</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6782,21 +6782,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6806,13 +6806,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>459595</v>
+        <v>459652</v>
       </c>
       <c r="R56" t="n">
-        <v>6808516</v>
+        <v>6808496</v>
       </c>
       <c r="S56" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6841,7 +6841,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6851,7 +6851,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>På tallstammar</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6866,19 +6871,19 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123574181</v>
+        <v>123575574</v>
       </c>
       <c r="B57" t="n">
         <v>78781</v>
@@ -6918,10 +6923,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>459652</v>
+        <v>459574</v>
       </c>
       <c r="R57" t="n">
-        <v>6808496</v>
+        <v>6808461</v>
       </c>
       <c r="S57" t="n">
         <v>9</v>
@@ -6953,7 +6958,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6963,7 +6968,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
@@ -6995,10 +7000,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123575574</v>
+        <v>123575257</v>
       </c>
       <c r="B58" t="n">
-        <v>78781</v>
+        <v>78518</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7011,21 +7016,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7035,13 +7040,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>459574</v>
+        <v>459595</v>
       </c>
       <c r="R58" t="n">
-        <v>6808461</v>
+        <v>6808516</v>
       </c>
       <c r="S58" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7070,7 +7075,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7080,12 +7085,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:07</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>På tallstammar</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7100,12 +7100,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -12478,7 +12478,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>123577342</v>
+        <v>123548240</v>
       </c>
       <c r="B106" t="n">
         <v>56697</v>
@@ -12522,14 +12522,14 @@
       <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>459446</v>
+        <v>459026</v>
       </c>
       <c r="R106" t="n">
-        <v>6808812</v>
+        <v>6808873</v>
       </c>
       <c r="S106" t="n">
         <v>15</v>
@@ -12556,22 +12556,22 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr">
@@ -12603,7 +12603,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>123548240</v>
+        <v>123577342</v>
       </c>
       <c r="B107" t="n">
         <v>56697</v>
@@ -12647,14 +12647,14 @@
       <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Andljusen, Andljusen, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>459026</v>
+        <v>459446</v>
       </c>
       <c r="R107" t="n">
-        <v>6808873</v>
+        <v>6808812</v>
       </c>
       <c r="S107" t="n">
         <v>15</v>
@@ -12681,22 +12681,22 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr">
@@ -12969,7 +12969,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>123549286</v>
+        <v>123567138</v>
       </c>
       <c r="B110" t="n">
         <v>56697</v>
@@ -13013,14 +13013,14 @@
       <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>459241</v>
+        <v>459735</v>
       </c>
       <c r="R110" t="n">
-        <v>6808793</v>
+        <v>6808695</v>
       </c>
       <c r="S110" t="n">
         <v>15</v>
@@ -13047,22 +13047,22 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr">
@@ -13094,7 +13094,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>123567138</v>
+        <v>123549286</v>
       </c>
       <c r="B111" t="n">
         <v>56697</v>
@@ -13138,14 +13138,14 @@
       <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>459735</v>
+        <v>459241</v>
       </c>
       <c r="R111" t="n">
-        <v>6808695</v>
+        <v>6808793</v>
       </c>
       <c r="S111" t="n">
         <v>15</v>
@@ -13172,22 +13172,22 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AC111" t="inlineStr">
@@ -13550,10 +13550,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>123726070</v>
+        <v>123727325</v>
       </c>
       <c r="B115" t="n">
-        <v>57503</v>
+        <v>78517</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13566,39 +13566,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Dyvran, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>458944</v>
+        <v>458886</v>
       </c>
       <c r="R115" t="n">
-        <v>6808335</v>
+        <v>6808352</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13657,10 +13652,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>123727325</v>
+        <v>123728287</v>
       </c>
       <c r="B116" t="n">
-        <v>78517</v>
+        <v>78781</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13673,21 +13668,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13697,10 +13692,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>458886</v>
+        <v>458826</v>
       </c>
       <c r="R116" t="n">
-        <v>6808352</v>
+        <v>6808449</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13733,6 +13728,11 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Garnlav på samtliga träd,mer eller mindre, på bilden.</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13759,10 +13759,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>123728287</v>
+        <v>123728532</v>
       </c>
       <c r="B117" t="n">
-        <v>78781</v>
+        <v>78518</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13775,21 +13775,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13799,10 +13799,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>458826</v>
+        <v>458798</v>
       </c>
       <c r="R117" t="n">
-        <v>6808449</v>
+        <v>6808499</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13835,11 +13835,6 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-04-03</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Garnlav på samtliga träd,mer eller mindre, på bilden.</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13866,10 +13861,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>123728532</v>
+        <v>123726070</v>
       </c>
       <c r="B118" t="n">
-        <v>78518</v>
+        <v>57503</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13882,34 +13877,39 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Dyvran, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>458798</v>
+        <v>458944</v>
       </c>
       <c r="R118" t="n">
-        <v>6808499</v>
+        <v>6808335</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -14386,7 +14386,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>123723313</v>
+        <v>123732682</v>
       </c>
       <c r="B123" t="n">
         <v>78781</v>
@@ -14422,14 +14422,14 @@
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Dyvran, Dlr</t>
+          <t>Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>458948</v>
+        <v>458711</v>
       </c>
       <c r="R123" t="n">
-        <v>6808276</v>
+        <v>6808858</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14466,7 +14466,7 @@
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>Garnlav med miljöbild.</t>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14493,7 +14493,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>123732682</v>
+        <v>123732746</v>
       </c>
       <c r="B124" t="n">
         <v>78781</v>
@@ -14533,10 +14533,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>458711</v>
+        <v>458699</v>
       </c>
       <c r="R124" t="n">
-        <v>6808858</v>
+        <v>6808863</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14600,7 +14600,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>123732746</v>
+        <v>123723313</v>
       </c>
       <c r="B125" t="n">
         <v>78781</v>
@@ -14636,14 +14636,14 @@
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Andljusen, Dlr</t>
+          <t>Dyvran, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>458699</v>
+        <v>458948</v>
       </c>
       <c r="R125" t="n">
-        <v>6808863</v>
+        <v>6808276</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14680,7 +14680,7 @@
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>Miljöbild.</t>
+          <t>Garnlav med miljöbild.</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -15645,10 +15645,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>123728778</v>
+        <v>123725285</v>
       </c>
       <c r="B135" t="n">
-        <v>57503</v>
+        <v>78781</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -15661,21 +15661,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -15685,10 +15685,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>458798</v>
+        <v>458926</v>
       </c>
       <c r="R135" t="n">
-        <v>6808499</v>
+        <v>6808287</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15721,11 +15721,6 @@
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-04-03</t>
-        </is>
-      </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15752,10 +15747,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>123725285</v>
+        <v>123728778</v>
       </c>
       <c r="B136" t="n">
-        <v>78781</v>
+        <v>57503</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15768,21 +15763,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15792,10 +15787,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>458926</v>
+        <v>458798</v>
       </c>
       <c r="R136" t="n">
-        <v>6808287</v>
+        <v>6808499</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15828,6 +15823,11 @@
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>Miljöbilder.</t>
         </is>
       </c>
       <c r="AD136" t="b">

--- a/artfynd/A 61324-2022 artfynd.xlsx
+++ b/artfynd/A 61324-2022 artfynd.xlsx
@@ -785,7 +785,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123543936</v>
+        <v>123549262</v>
       </c>
       <c r="B3" t="n">
         <v>78781</v>
@@ -821,14 +821,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459520</v>
+        <v>459241</v>
       </c>
       <c r="R3" t="n">
-        <v>6808918</v>
+        <v>6808793</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123549262</v>
+        <v>123549170</v>
       </c>
       <c r="B4" t="n">
         <v>78781</v>
@@ -933,17 +933,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459241</v>
+        <v>459062</v>
       </c>
       <c r="R4" t="n">
-        <v>6808793</v>
+        <v>6808854</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -997,19 +997,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123549170</v>
+        <v>123543936</v>
       </c>
       <c r="B5" t="n">
         <v>78781</v>
@@ -1045,17 +1045,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Andljusen, Andljusen, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459062</v>
+        <v>459520</v>
       </c>
       <c r="R5" t="n">
-        <v>6808854</v>
+        <v>6808918</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,12 +1109,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1569,10 +1569,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123548439</v>
+        <v>123548646</v>
       </c>
       <c r="B10" t="n">
-        <v>78781</v>
+        <v>78518</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1585,34 +1585,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Andljusen, Andljusen, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>459138</v>
+        <v>459185</v>
       </c>
       <c r="R10" t="n">
-        <v>6808765</v>
+        <v>6808785</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1681,7 +1681,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123549501</v>
+        <v>123548439</v>
       </c>
       <c r="B11" t="n">
         <v>78781</v>
@@ -1717,17 +1717,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>459367</v>
+        <v>459138</v>
       </c>
       <c r="R11" t="n">
-        <v>6808792</v>
+        <v>6808765</v>
       </c>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1781,22 +1781,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123548646</v>
+        <v>123549501</v>
       </c>
       <c r="B12" t="n">
-        <v>78518</v>
+        <v>78781</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1809,37 +1809,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>459185</v>
+        <v>459367</v>
       </c>
       <c r="R12" t="n">
-        <v>6808785</v>
+        <v>6808792</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1893,12 +1893,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2017,10 +2017,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123548247</v>
+        <v>123546440</v>
       </c>
       <c r="B14" t="n">
-        <v>78781</v>
+        <v>78518</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2033,37 +2033,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Andljusen, Andljusen, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>459057</v>
+        <v>459563</v>
       </c>
       <c r="R14" t="n">
-        <v>6808867</v>
+        <v>6808917</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2117,22 +2117,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123546440</v>
+        <v>123548247</v>
       </c>
       <c r="B15" t="n">
-        <v>78518</v>
+        <v>78781</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2145,37 +2145,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>459563</v>
+        <v>459057</v>
       </c>
       <c r="R15" t="n">
-        <v>6808917</v>
+        <v>6808867</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2229,12 +2229,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -4618,10 +4618,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123549577</v>
+        <v>123549477</v>
       </c>
       <c r="B37" t="n">
-        <v>78781</v>
+        <v>78518</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4634,37 +4634,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>459420</v>
+        <v>459062</v>
       </c>
       <c r="R37" t="n">
-        <v>6808812</v>
+        <v>6808854</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4718,19 +4718,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123548371</v>
+        <v>123549577</v>
       </c>
       <c r="B38" t="n">
         <v>78781</v>
@@ -4766,17 +4766,17 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Andljusen, Andljusen, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>459133</v>
+        <v>459420</v>
       </c>
       <c r="R38" t="n">
-        <v>6808760</v>
+        <v>6808812</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4815,7 +4815,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4830,19 +4830,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123549730</v>
+        <v>123548371</v>
       </c>
       <c r="B39" t="n">
         <v>78781</v>
@@ -4878,17 +4878,17 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>459461</v>
+        <v>459133</v>
       </c>
       <c r="R39" t="n">
-        <v>6808868</v>
+        <v>6808760</v>
       </c>
       <c r="S39" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4927,7 +4927,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4942,19 +4942,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123549689</v>
+        <v>123549730</v>
       </c>
       <c r="B40" t="n">
         <v>78781</v>
@@ -4994,10 +4994,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>459457</v>
+        <v>459461</v>
       </c>
       <c r="R40" t="n">
-        <v>6808865</v>
+        <v>6808868</v>
       </c>
       <c r="S40" t="n">
         <v>9</v>
@@ -5029,7 +5029,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5039,7 +5039,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5066,10 +5066,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123549477</v>
+        <v>123549689</v>
       </c>
       <c r="B41" t="n">
-        <v>78518</v>
+        <v>78781</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5082,37 +5082,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Andljusen, Andljusen, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>459062</v>
+        <v>459457</v>
       </c>
       <c r="R41" t="n">
-        <v>6808854</v>
+        <v>6808865</v>
       </c>
       <c r="S41" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5166,22 +5166,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123548779</v>
+        <v>123548763</v>
       </c>
       <c r="B42" t="n">
-        <v>79370</v>
+        <v>78781</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5194,21 +5194,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5218,13 +5218,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>459073</v>
+        <v>459187</v>
       </c>
       <c r="R42" t="n">
-        <v>6808847</v>
+        <v>6808828</v>
       </c>
       <c r="S42" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5278,22 +5278,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123548763</v>
+        <v>123548779</v>
       </c>
       <c r="B43" t="n">
-        <v>78781</v>
+        <v>79370</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5306,21 +5306,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5330,13 +5330,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>459187</v>
+        <v>459073</v>
       </c>
       <c r="R43" t="n">
-        <v>6808828</v>
+        <v>6808847</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5390,12 +5390,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -12478,7 +12478,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>123548240</v>
+        <v>123577342</v>
       </c>
       <c r="B106" t="n">
         <v>56697</v>
@@ -12522,14 +12522,14 @@
       <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Andljusen, Andljusen, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>459026</v>
+        <v>459446</v>
       </c>
       <c r="R106" t="n">
-        <v>6808873</v>
+        <v>6808812</v>
       </c>
       <c r="S106" t="n">
         <v>15</v>
@@ -12556,22 +12556,22 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr">
@@ -12603,7 +12603,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>123577342</v>
+        <v>123548240</v>
       </c>
       <c r="B107" t="n">
         <v>56697</v>
@@ -12647,14 +12647,14 @@
       <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>459446</v>
+        <v>459026</v>
       </c>
       <c r="R107" t="n">
-        <v>6808812</v>
+        <v>6808873</v>
       </c>
       <c r="S107" t="n">
         <v>15</v>
@@ -12681,22 +12681,22 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr">
@@ -12969,7 +12969,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>123567138</v>
+        <v>123549286</v>
       </c>
       <c r="B110" t="n">
         <v>56697</v>
@@ -13013,14 +13013,14 @@
       <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>459735</v>
+        <v>459241</v>
       </c>
       <c r="R110" t="n">
-        <v>6808695</v>
+        <v>6808793</v>
       </c>
       <c r="S110" t="n">
         <v>15</v>
@@ -13047,22 +13047,22 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr">
@@ -13094,7 +13094,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>123549286</v>
+        <v>123567138</v>
       </c>
       <c r="B111" t="n">
         <v>56697</v>
@@ -13138,14 +13138,14 @@
       <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>459241</v>
+        <v>459735</v>
       </c>
       <c r="R111" t="n">
-        <v>6808793</v>
+        <v>6808695</v>
       </c>
       <c r="S111" t="n">
         <v>15</v>
@@ -13172,22 +13172,22 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AC111" t="inlineStr">
@@ -13550,10 +13550,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>123727325</v>
+        <v>123728287</v>
       </c>
       <c r="B115" t="n">
-        <v>78517</v>
+        <v>78781</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13566,21 +13566,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -13590,10 +13590,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>458886</v>
+        <v>458826</v>
       </c>
       <c r="R115" t="n">
-        <v>6808352</v>
+        <v>6808449</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13626,6 +13626,11 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Garnlav på samtliga träd,mer eller mindre, på bilden.</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13652,10 +13657,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>123728287</v>
+        <v>123728532</v>
       </c>
       <c r="B116" t="n">
-        <v>78781</v>
+        <v>78518</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13668,21 +13673,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13692,10 +13697,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>458826</v>
+        <v>458798</v>
       </c>
       <c r="R116" t="n">
-        <v>6808449</v>
+        <v>6808499</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13728,11 +13733,6 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-04-03</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Garnlav på samtliga träd,mer eller mindre, på bilden.</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13759,10 +13759,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>123728532</v>
+        <v>123726070</v>
       </c>
       <c r="B117" t="n">
-        <v>78518</v>
+        <v>57503</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13775,34 +13775,39 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Dyvran, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>458798</v>
+        <v>458944</v>
       </c>
       <c r="R117" t="n">
-        <v>6808499</v>
+        <v>6808335</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13861,10 +13866,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>123726070</v>
+        <v>123727325</v>
       </c>
       <c r="B118" t="n">
-        <v>57503</v>
+        <v>78517</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13877,39 +13882,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Dyvran, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>458944</v>
+        <v>458886</v>
       </c>
       <c r="R118" t="n">
-        <v>6808335</v>
+        <v>6808352</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13968,10 +13968,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>123728524</v>
+        <v>123728027</v>
       </c>
       <c r="B119" t="n">
-        <v>78517</v>
+        <v>78518</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13984,21 +13984,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -14008,10 +14008,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>458826</v>
+        <v>458836</v>
       </c>
       <c r="R119" t="n">
-        <v>6808449</v>
+        <v>6808421</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -14044,11 +14044,6 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-04-03</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14075,10 +14070,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>123732512</v>
+        <v>123725898</v>
       </c>
       <c r="B120" t="n">
-        <v>78517</v>
+        <v>78781</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -14091,34 +14086,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Andljusen, Dlr</t>
+          <t>Dyvran, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>458701</v>
+        <v>458927</v>
       </c>
       <c r="R120" t="n">
-        <v>6808812</v>
+        <v>6808307</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -14151,11 +14146,6 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-04-03</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14182,10 +14172,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>123728027</v>
+        <v>123732512</v>
       </c>
       <c r="B121" t="n">
-        <v>78518</v>
+        <v>78517</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -14198,34 +14188,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Dyvran, Dlr</t>
+          <t>Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>458836</v>
+        <v>458701</v>
       </c>
       <c r="R121" t="n">
-        <v>6808421</v>
+        <v>6808812</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14258,6 +14248,11 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14284,10 +14279,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>123725898</v>
+        <v>123728524</v>
       </c>
       <c r="B122" t="n">
-        <v>78781</v>
+        <v>78517</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -14300,21 +14295,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -14324,10 +14319,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>458927</v>
+        <v>458826</v>
       </c>
       <c r="R122" t="n">
-        <v>6808307</v>
+        <v>6808449</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -14360,6 +14355,11 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14386,7 +14386,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>123732682</v>
+        <v>123723313</v>
       </c>
       <c r="B123" t="n">
         <v>78781</v>
@@ -14422,14 +14422,14 @@
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Andljusen, Dlr</t>
+          <t>Dyvran, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>458711</v>
+        <v>458948</v>
       </c>
       <c r="R123" t="n">
-        <v>6808858</v>
+        <v>6808276</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14466,7 +14466,7 @@
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>Miljöbild.</t>
+          <t>Garnlav med miljöbild.</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14493,7 +14493,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>123732746</v>
+        <v>123732682</v>
       </c>
       <c r="B124" t="n">
         <v>78781</v>
@@ -14533,10 +14533,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>458699</v>
+        <v>458711</v>
       </c>
       <c r="R124" t="n">
-        <v>6808863</v>
+        <v>6808858</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14600,7 +14600,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>123723313</v>
+        <v>123732746</v>
       </c>
       <c r="B125" t="n">
         <v>78781</v>
@@ -14636,14 +14636,14 @@
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Dyvran, Dlr</t>
+          <t>Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>458948</v>
+        <v>458699</v>
       </c>
       <c r="R125" t="n">
-        <v>6808276</v>
+        <v>6808863</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14680,7 +14680,7 @@
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>Garnlav med miljöbild.</t>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD125" t="b">

--- a/artfynd/A 61324-2022 artfynd.xlsx
+++ b/artfynd/A 61324-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY146"/>
+  <dimension ref="A1:AY209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -785,7 +785,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123549262</v>
+        <v>123543936</v>
       </c>
       <c r="B3" t="n">
         <v>78781</v>
@@ -821,14 +821,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459241</v>
+        <v>459520</v>
       </c>
       <c r="R3" t="n">
-        <v>6808793</v>
+        <v>6808918</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123549170</v>
+        <v>123549262</v>
       </c>
       <c r="B4" t="n">
         <v>78781</v>
@@ -933,17 +933,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Andljusen, Andljusen, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459062</v>
+        <v>459241</v>
       </c>
       <c r="R4" t="n">
-        <v>6808854</v>
+        <v>6808793</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -997,19 +997,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123543936</v>
+        <v>123549170</v>
       </c>
       <c r="B5" t="n">
         <v>78781</v>
@@ -1045,17 +1045,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459520</v>
+        <v>459062</v>
       </c>
       <c r="R5" t="n">
-        <v>6808918</v>
+        <v>6808854</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,12 +1109,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1569,10 +1569,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123548646</v>
+        <v>123548439</v>
       </c>
       <c r="B10" t="n">
-        <v>78518</v>
+        <v>78781</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1585,34 +1585,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>459185</v>
+        <v>459138</v>
       </c>
       <c r="R10" t="n">
-        <v>6808785</v>
+        <v>6808765</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1681,7 +1681,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123548439</v>
+        <v>123549501</v>
       </c>
       <c r="B11" t="n">
         <v>78781</v>
@@ -1717,17 +1717,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Andljusen, Andljusen, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>459138</v>
+        <v>459367</v>
       </c>
       <c r="R11" t="n">
-        <v>6808765</v>
+        <v>6808792</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1781,22 +1781,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123549501</v>
+        <v>123548646</v>
       </c>
       <c r="B12" t="n">
-        <v>78781</v>
+        <v>78518</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1809,37 +1809,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>459367</v>
+        <v>459185</v>
       </c>
       <c r="R12" t="n">
-        <v>6808792</v>
+        <v>6808785</v>
       </c>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1893,12 +1893,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2017,10 +2017,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123546440</v>
+        <v>123548247</v>
       </c>
       <c r="B14" t="n">
-        <v>78518</v>
+        <v>78781</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2033,37 +2033,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>459563</v>
+        <v>459057</v>
       </c>
       <c r="R14" t="n">
-        <v>6808917</v>
+        <v>6808867</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2117,22 +2117,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123548247</v>
+        <v>123546440</v>
       </c>
       <c r="B15" t="n">
-        <v>78781</v>
+        <v>78518</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2145,37 +2145,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Andljusen, Andljusen, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>459057</v>
+        <v>459563</v>
       </c>
       <c r="R15" t="n">
-        <v>6808867</v>
+        <v>6808917</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2229,12 +2229,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -4618,10 +4618,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123549477</v>
+        <v>123549577</v>
       </c>
       <c r="B37" t="n">
-        <v>78518</v>
+        <v>78781</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4634,37 +4634,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Andljusen, Andljusen, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>459062</v>
+        <v>459420</v>
       </c>
       <c r="R37" t="n">
-        <v>6808854</v>
+        <v>6808812</v>
       </c>
       <c r="S37" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4718,19 +4718,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123549577</v>
+        <v>123548371</v>
       </c>
       <c r="B38" t="n">
         <v>78781</v>
@@ -4766,17 +4766,17 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>459420</v>
+        <v>459133</v>
       </c>
       <c r="R38" t="n">
-        <v>6808812</v>
+        <v>6808760</v>
       </c>
       <c r="S38" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4815,7 +4815,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4830,19 +4830,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123548371</v>
+        <v>123549730</v>
       </c>
       <c r="B39" t="n">
         <v>78781</v>
@@ -4878,17 +4878,17 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Andljusen, Andljusen, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>459133</v>
+        <v>459461</v>
       </c>
       <c r="R39" t="n">
-        <v>6808760</v>
+        <v>6808868</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4927,7 +4927,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4942,19 +4942,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123549730</v>
+        <v>123549689</v>
       </c>
       <c r="B40" t="n">
         <v>78781</v>
@@ -4994,10 +4994,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>459461</v>
+        <v>459457</v>
       </c>
       <c r="R40" t="n">
-        <v>6808868</v>
+        <v>6808865</v>
       </c>
       <c r="S40" t="n">
         <v>9</v>
@@ -5029,7 +5029,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5039,7 +5039,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5066,10 +5066,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123549689</v>
+        <v>123549477</v>
       </c>
       <c r="B41" t="n">
-        <v>78781</v>
+        <v>78518</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5082,37 +5082,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>459457</v>
+        <v>459062</v>
       </c>
       <c r="R41" t="n">
-        <v>6808865</v>
+        <v>6808854</v>
       </c>
       <c r="S41" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5166,22 +5166,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123548763</v>
+        <v>123548779</v>
       </c>
       <c r="B42" t="n">
-        <v>78781</v>
+        <v>79370</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5194,21 +5194,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5218,13 +5218,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>459187</v>
+        <v>459073</v>
       </c>
       <c r="R42" t="n">
-        <v>6808828</v>
+        <v>6808847</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5278,22 +5278,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123548779</v>
+        <v>123548763</v>
       </c>
       <c r="B43" t="n">
-        <v>79370</v>
+        <v>78781</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5306,21 +5306,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5330,13 +5330,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>459073</v>
+        <v>459187</v>
       </c>
       <c r="R43" t="n">
-        <v>6808847</v>
+        <v>6808828</v>
       </c>
       <c r="S43" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5390,12 +5390,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -6766,10 +6766,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123574181</v>
+        <v>123575257</v>
       </c>
       <c r="B56" t="n">
-        <v>78781</v>
+        <v>78518</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6782,21 +6782,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6806,13 +6806,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>459652</v>
+        <v>459595</v>
       </c>
       <c r="R56" t="n">
-        <v>6808496</v>
+        <v>6808516</v>
       </c>
       <c r="S56" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6841,7 +6841,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6851,12 +6851,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:37</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>På tallstammar</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6871,19 +6866,19 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123575574</v>
+        <v>123574181</v>
       </c>
       <c r="B57" t="n">
         <v>78781</v>
@@ -6923,10 +6918,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>459574</v>
+        <v>459652</v>
       </c>
       <c r="R57" t="n">
-        <v>6808461</v>
+        <v>6808496</v>
       </c>
       <c r="S57" t="n">
         <v>9</v>
@@ -6958,7 +6953,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6968,7 +6963,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
@@ -7000,10 +6995,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123575257</v>
+        <v>123575574</v>
       </c>
       <c r="B58" t="n">
-        <v>78518</v>
+        <v>78781</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7016,21 +7011,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7040,13 +7035,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>459595</v>
+        <v>459574</v>
       </c>
       <c r="R58" t="n">
-        <v>6808516</v>
+        <v>6808461</v>
       </c>
       <c r="S58" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7075,7 +7070,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7085,7 +7080,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>På tallstammar</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7100,12 +7100,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -10746,10 +10746,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>123575210</v>
+        <v>123573526</v>
       </c>
       <c r="B91" t="n">
-        <v>78517</v>
+        <v>78781</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10762,21 +10762,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10786,10 +10786,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>459619</v>
+        <v>459731</v>
       </c>
       <c r="R91" t="n">
-        <v>6808506</v>
+        <v>6808508</v>
       </c>
       <c r="S91" t="n">
         <v>9</v>
@@ -10821,7 +10821,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10831,7 +10831,12 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>På tallstammar</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10846,19 +10851,19 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>123573526</v>
+        <v>123576585</v>
       </c>
       <c r="B92" t="n">
         <v>78781</v>
@@ -10898,13 +10903,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>459731</v>
+        <v>459565</v>
       </c>
       <c r="R92" t="n">
-        <v>6808508</v>
+        <v>6808543</v>
       </c>
       <c r="S92" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10933,7 +10938,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10943,12 +10948,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>På tallstammar</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10963,22 +10963,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>123576585</v>
+        <v>123575210</v>
       </c>
       <c r="B93" t="n">
-        <v>78781</v>
+        <v>78517</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10991,21 +10991,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -11015,13 +11015,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>459565</v>
+        <v>459619</v>
       </c>
       <c r="R93" t="n">
-        <v>6808543</v>
+        <v>6808506</v>
       </c>
       <c r="S93" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11050,7 +11050,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11060,7 +11060,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11199,7 +11199,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>123566093</v>
+        <v>123577149</v>
       </c>
       <c r="B95" t="n">
         <v>78518</v>
@@ -11235,17 +11235,17 @@
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>459675</v>
+        <v>459571</v>
       </c>
       <c r="R95" t="n">
-        <v>6808804</v>
+        <v>6808546</v>
       </c>
       <c r="S95" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11274,7 +11274,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11284,7 +11284,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11311,7 +11311,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>123577149</v>
+        <v>123566093</v>
       </c>
       <c r="B96" t="n">
         <v>78518</v>
@@ -11347,17 +11347,17 @@
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>459571</v>
+        <v>459675</v>
       </c>
       <c r="R96" t="n">
-        <v>6808546</v>
+        <v>6808804</v>
       </c>
       <c r="S96" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11386,7 +11386,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11396,7 +11396,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12478,7 +12478,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>123577342</v>
+        <v>123548240</v>
       </c>
       <c r="B106" t="n">
         <v>56697</v>
@@ -12522,14 +12522,14 @@
       <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>459446</v>
+        <v>459026</v>
       </c>
       <c r="R106" t="n">
-        <v>6808812</v>
+        <v>6808873</v>
       </c>
       <c r="S106" t="n">
         <v>15</v>
@@ -12556,22 +12556,22 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr">
@@ -12603,7 +12603,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>123548240</v>
+        <v>123577342</v>
       </c>
       <c r="B107" t="n">
         <v>56697</v>
@@ -12647,14 +12647,14 @@
       <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Andljusen, Andljusen, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>459026</v>
+        <v>459446</v>
       </c>
       <c r="R107" t="n">
-        <v>6808873</v>
+        <v>6808812</v>
       </c>
       <c r="S107" t="n">
         <v>15</v>
@@ -12681,22 +12681,22 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr">
@@ -12728,10 +12728,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>123575396</v>
+        <v>123548972</v>
       </c>
       <c r="B108" t="n">
-        <v>79399</v>
+        <v>56697</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12740,44 +12740,49 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>459583</v>
+        <v>459189</v>
       </c>
       <c r="R108" t="n">
-        <v>6808431</v>
+        <v>6808830</v>
       </c>
       <c r="S108" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12801,22 +12806,27 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Under betestall</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12825,29 +12835,28 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>123548972</v>
+        <v>123575396</v>
       </c>
       <c r="B109" t="n">
-        <v>56697</v>
+        <v>79399</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12856,49 +12865,44 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Andljusen, Andljusen, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>459189</v>
+        <v>459583</v>
       </c>
       <c r="R109" t="n">
-        <v>6808830</v>
+        <v>6808431</v>
       </c>
       <c r="S109" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12922,27 +12926,22 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>17:04</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Under betestall</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12951,18 +12950,19 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
@@ -13550,10 +13550,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>123728287</v>
+        <v>123727325</v>
       </c>
       <c r="B115" t="n">
-        <v>78781</v>
+        <v>78517</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13566,21 +13566,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -13590,10 +13590,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>458826</v>
+        <v>458886</v>
       </c>
       <c r="R115" t="n">
-        <v>6808449</v>
+        <v>6808352</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13626,11 +13626,6 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-04-03</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>Garnlav på samtliga träd,mer eller mindre, på bilden.</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13657,10 +13652,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>123728532</v>
+        <v>123728287</v>
       </c>
       <c r="B116" t="n">
-        <v>78518</v>
+        <v>78781</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13673,21 +13668,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13697,10 +13692,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>458798</v>
+        <v>458826</v>
       </c>
       <c r="R116" t="n">
-        <v>6808499</v>
+        <v>6808449</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13733,6 +13728,11 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Garnlav på samtliga träd,mer eller mindre, på bilden.</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13759,10 +13759,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>123726070</v>
+        <v>123728532</v>
       </c>
       <c r="B117" t="n">
-        <v>57503</v>
+        <v>78518</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13775,39 +13775,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Dyvran, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>458944</v>
+        <v>458798</v>
       </c>
       <c r="R117" t="n">
-        <v>6808335</v>
+        <v>6808499</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13866,10 +13861,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>123727325</v>
+        <v>123726070</v>
       </c>
       <c r="B118" t="n">
-        <v>78517</v>
+        <v>57503</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13882,34 +13877,39 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Dyvran, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>458886</v>
+        <v>458944</v>
       </c>
       <c r="R118" t="n">
-        <v>6808352</v>
+        <v>6808335</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13968,10 +13968,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>123728027</v>
+        <v>123728524</v>
       </c>
       <c r="B119" t="n">
-        <v>78518</v>
+        <v>78517</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13984,21 +13984,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -14008,10 +14008,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>458836</v>
+        <v>458826</v>
       </c>
       <c r="R119" t="n">
-        <v>6808421</v>
+        <v>6808449</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -14044,6 +14044,11 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14070,10 +14075,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>123725898</v>
+        <v>123732512</v>
       </c>
       <c r="B120" t="n">
-        <v>78781</v>
+        <v>78517</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -14086,34 +14091,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Dyvran, Dlr</t>
+          <t>Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>458927</v>
+        <v>458701</v>
       </c>
       <c r="R120" t="n">
-        <v>6808307</v>
+        <v>6808812</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -14146,6 +14151,11 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14172,10 +14182,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>123732512</v>
+        <v>123728027</v>
       </c>
       <c r="B121" t="n">
-        <v>78517</v>
+        <v>78518</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -14188,34 +14198,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Andljusen, Dlr</t>
+          <t>Dyvran, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>458701</v>
+        <v>458836</v>
       </c>
       <c r="R121" t="n">
-        <v>6808812</v>
+        <v>6808421</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14248,11 +14258,6 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-04-03</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14279,10 +14284,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>123728524</v>
+        <v>123725898</v>
       </c>
       <c r="B122" t="n">
-        <v>78517</v>
+        <v>78781</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -14295,21 +14300,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -14319,10 +14324,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>458826</v>
+        <v>458927</v>
       </c>
       <c r="R122" t="n">
-        <v>6808449</v>
+        <v>6808307</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -14355,11 +14360,6 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-04-03</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14386,7 +14386,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>123723313</v>
+        <v>123732682</v>
       </c>
       <c r="B123" t="n">
         <v>78781</v>
@@ -14422,14 +14422,14 @@
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Dyvran, Dlr</t>
+          <t>Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>458948</v>
+        <v>458711</v>
       </c>
       <c r="R123" t="n">
-        <v>6808276</v>
+        <v>6808858</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14466,7 +14466,7 @@
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>Garnlav med miljöbild.</t>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14493,7 +14493,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>123732682</v>
+        <v>123732746</v>
       </c>
       <c r="B124" t="n">
         <v>78781</v>
@@ -14533,10 +14533,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>458711</v>
+        <v>458699</v>
       </c>
       <c r="R124" t="n">
-        <v>6808858</v>
+        <v>6808863</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14600,7 +14600,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>123732746</v>
+        <v>123723313</v>
       </c>
       <c r="B125" t="n">
         <v>78781</v>
@@ -14636,14 +14636,14 @@
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Andljusen, Dlr</t>
+          <t>Dyvran, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>458699</v>
+        <v>458948</v>
       </c>
       <c r="R125" t="n">
-        <v>6808863</v>
+        <v>6808276</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14680,7 +14680,7 @@
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>Miljöbild.</t>
+          <t>Garnlav med miljöbild.</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -16272,10 +16272,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>123727363</v>
+        <v>123725953</v>
       </c>
       <c r="B141" t="n">
-        <v>78518</v>
+        <v>78781</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -16288,21 +16288,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -16312,10 +16312,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>458886</v>
+        <v>458928</v>
       </c>
       <c r="R141" t="n">
-        <v>6808352</v>
+        <v>6808305</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16374,10 +16374,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>123727467</v>
+        <v>123727363</v>
       </c>
       <c r="B142" t="n">
-        <v>78781</v>
+        <v>78518</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -16390,21 +16390,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -16414,10 +16414,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>458884</v>
+        <v>458886</v>
       </c>
       <c r="R142" t="n">
-        <v>6808395</v>
+        <v>6808352</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16450,11 +16450,6 @@
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-04-03</t>
-        </is>
-      </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>Garnlav i en radie av ca 50 meter! Återkommande på speciellt tallstammar.</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -16481,7 +16476,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>123725953</v>
+        <v>123727467</v>
       </c>
       <c r="B143" t="n">
         <v>78781</v>
@@ -16521,10 +16516,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>458928</v>
+        <v>458884</v>
       </c>
       <c r="R143" t="n">
-        <v>6808305</v>
+        <v>6808395</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16557,6 +16552,11 @@
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>Garnlav i en radie av ca 50 meter! Återkommande på speciellt tallstammar.</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16897,6 +16897,6667 @@
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>123828923</v>
+      </c>
+      <c r="B147" t="n">
+        <v>78522</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>Härkämäck, Härkämäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q147" t="n">
+        <v>459275</v>
+      </c>
+      <c r="R147" t="n">
+        <v>6808519</v>
+      </c>
+      <c r="S147" t="n">
+        <v>10</v>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AD147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT147" t="inlineStr"/>
+      <c r="AW147" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX147" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>123828892</v>
+      </c>
+      <c r="B148" t="n">
+        <v>78523</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>Härkämäck, Härkämäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q148" t="n">
+        <v>459465</v>
+      </c>
+      <c r="R148" t="n">
+        <v>6808411</v>
+      </c>
+      <c r="S148" t="n">
+        <v>15</v>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AD148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT148" t="inlineStr"/>
+      <c r="AW148" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX148" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>123827321</v>
+      </c>
+      <c r="B149" t="n">
+        <v>78523</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>Andljusen, Andljusen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q149" t="n">
+        <v>458750</v>
+      </c>
+      <c r="R149" t="n">
+        <v>6808601</v>
+      </c>
+      <c r="S149" t="n">
+        <v>10</v>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AD149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT149" t="inlineStr"/>
+      <c r="AW149" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX149" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>123826931</v>
+      </c>
+      <c r="B150" t="n">
+        <v>79399</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>Andljusen, Andljusen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q150" t="n">
+        <v>458763</v>
+      </c>
+      <c r="R150" t="n">
+        <v>6808709</v>
+      </c>
+      <c r="S150" t="n">
+        <v>10</v>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="Z150" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AB150" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AD150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT150" t="inlineStr"/>
+      <c r="AW150" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX150" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>123823930</v>
+      </c>
+      <c r="B151" t="n">
+        <v>56697</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>Andljusen, Andljusen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q151" t="n">
+        <v>458738</v>
+      </c>
+      <c r="R151" t="n">
+        <v>6808851</v>
+      </c>
+      <c r="S151" t="n">
+        <v>10</v>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AD151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT151" t="inlineStr"/>
+      <c r="AW151" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX151" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>123826479</v>
+      </c>
+      <c r="B152" t="n">
+        <v>79370</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr"/>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>Andljusen, Andljusen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q152" t="n">
+        <v>458964</v>
+      </c>
+      <c r="R152" t="n">
+        <v>6808848</v>
+      </c>
+      <c r="S152" t="n">
+        <v>10</v>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W152" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="Z152" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AB152" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AD152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT152" t="inlineStr"/>
+      <c r="AW152" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX152" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>123826431</v>
+      </c>
+      <c r="B153" t="n">
+        <v>78517</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>Andljusen, Andljusen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q153" t="n">
+        <v>458981</v>
+      </c>
+      <c r="R153" t="n">
+        <v>6808888</v>
+      </c>
+      <c r="S153" t="n">
+        <v>10</v>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AD153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT153" t="inlineStr"/>
+      <c r="AW153" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX153" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>123835492</v>
+      </c>
+      <c r="B154" t="n">
+        <v>78786</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>Härkämäck, Härkämäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q154" t="n">
+        <v>459727</v>
+      </c>
+      <c r="R154" t="n">
+        <v>6808211</v>
+      </c>
+      <c r="S154" t="n">
+        <v>15</v>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W154" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AD154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT154" t="inlineStr"/>
+      <c r="AW154" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX154" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>123828787</v>
+      </c>
+      <c r="B155" t="n">
+        <v>78786</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>Härkämäck, Härkämäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q155" t="n">
+        <v>459143</v>
+      </c>
+      <c r="R155" t="n">
+        <v>6808487</v>
+      </c>
+      <c r="S155" t="n">
+        <v>10</v>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AD155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT155" t="inlineStr"/>
+      <c r="AW155" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX155" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>123827116</v>
+      </c>
+      <c r="B156" t="n">
+        <v>79370</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>Andljusen, Andljusen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q156" t="n">
+        <v>458751</v>
+      </c>
+      <c r="R156" t="n">
+        <v>6808636</v>
+      </c>
+      <c r="S156" t="n">
+        <v>10</v>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W156" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AD156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT156" t="inlineStr"/>
+      <c r="AW156" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX156" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>123835620</v>
+      </c>
+      <c r="B157" t="n">
+        <v>78522</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>Härkämäck, Härkämäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q157" t="n">
+        <v>459774</v>
+      </c>
+      <c r="R157" t="n">
+        <v>6808248</v>
+      </c>
+      <c r="S157" t="n">
+        <v>20</v>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AD157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT157" t="inlineStr"/>
+      <c r="AW157" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX157" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>123829348</v>
+      </c>
+      <c r="B158" t="n">
+        <v>78523</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr"/>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>Härkämäck, Härkämäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q158" t="n">
+        <v>459230</v>
+      </c>
+      <c r="R158" t="n">
+        <v>6808362</v>
+      </c>
+      <c r="S158" t="n">
+        <v>15</v>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W158" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AD158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT158" t="inlineStr"/>
+      <c r="AW158" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX158" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>123827325</v>
+      </c>
+      <c r="B159" t="n">
+        <v>78522</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr"/>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>Andljusen, Andljusen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q159" t="n">
+        <v>458750</v>
+      </c>
+      <c r="R159" t="n">
+        <v>6808601</v>
+      </c>
+      <c r="S159" t="n">
+        <v>10</v>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AD159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT159" t="inlineStr"/>
+      <c r="AW159" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX159" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>123826760</v>
+      </c>
+      <c r="B160" t="n">
+        <v>78781</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr"/>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>Andljusen, Andljusen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q160" t="n">
+        <v>458819</v>
+      </c>
+      <c r="R160" t="n">
+        <v>6808759</v>
+      </c>
+      <c r="S160" t="n">
+        <v>10</v>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W160" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y160" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AB160" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AD160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT160" t="inlineStr"/>
+      <c r="AW160" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX160" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>123826673</v>
+      </c>
+      <c r="B161" t="n">
+        <v>79370</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>Andljusen, Andljusen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q161" t="n">
+        <v>458923</v>
+      </c>
+      <c r="R161" t="n">
+        <v>6808811</v>
+      </c>
+      <c r="S161" t="n">
+        <v>10</v>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W161" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y161" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="Z161" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AB161" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AD161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT161" t="inlineStr"/>
+      <c r="AW161" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX161" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>123828981</v>
+      </c>
+      <c r="B162" t="n">
+        <v>78786</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr"/>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>Härkämäck, Härkämäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q162" t="n">
+        <v>459275</v>
+      </c>
+      <c r="R162" t="n">
+        <v>6808519</v>
+      </c>
+      <c r="S162" t="n">
+        <v>10</v>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W162" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y162" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AD162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT162" t="inlineStr"/>
+      <c r="AW162" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX162" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>123829753</v>
+      </c>
+      <c r="B163" t="n">
+        <v>78786</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr"/>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>Härkämäck, Härkämäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q163" t="n">
+        <v>458928</v>
+      </c>
+      <c r="R163" t="n">
+        <v>6808259</v>
+      </c>
+      <c r="S163" t="n">
+        <v>15</v>
+      </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V163" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W163" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y163" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AD163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT163" t="inlineStr"/>
+      <c r="AW163" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX163" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>123827158</v>
+      </c>
+      <c r="B164" t="n">
+        <v>78781</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr"/>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>Härkämäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q164" t="n">
+        <v>459682</v>
+      </c>
+      <c r="R164" t="n">
+        <v>6808249</v>
+      </c>
+      <c r="S164" t="n">
+        <v>10</v>
+      </c>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V164" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W164" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y164" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>Garnlav i en radie av ca 50 meter. Miljöbilder.</t>
+        </is>
+      </c>
+      <c r="AD164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT164" t="inlineStr"/>
+      <c r="AW164" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX164" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>123826671</v>
+      </c>
+      <c r="B165" t="n">
+        <v>79399</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr"/>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>Andljusen, Andljusen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q165" t="n">
+        <v>458923</v>
+      </c>
+      <c r="R165" t="n">
+        <v>6808811</v>
+      </c>
+      <c r="S165" t="n">
+        <v>10</v>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W165" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AB165" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AD165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT165" t="inlineStr"/>
+      <c r="AW165" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX165" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>123828823</v>
+      </c>
+      <c r="B166" t="n">
+        <v>78523</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr"/>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>Härkämäck, Härkämäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q166" t="n">
+        <v>459477</v>
+      </c>
+      <c r="R166" t="n">
+        <v>6808407</v>
+      </c>
+      <c r="S166" t="n">
+        <v>15</v>
+      </c>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V166" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W166" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y166" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AD166" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE166" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG166" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT166" t="inlineStr"/>
+      <c r="AW166" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX166" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>123835827</v>
+      </c>
+      <c r="B167" t="n">
+        <v>78786</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr"/>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>Härkämäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q167" t="n">
+        <v>459669</v>
+      </c>
+      <c r="R167" t="n">
+        <v>6808284</v>
+      </c>
+      <c r="S167" t="n">
+        <v>10</v>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W167" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y167" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>Garnlav i alla riktningar, radie ca 50 meter. Miljöbild.</t>
+        </is>
+      </c>
+      <c r="AD167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT167" t="inlineStr"/>
+      <c r="AW167" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX167" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>123826952</v>
+      </c>
+      <c r="B168" t="n">
+        <v>78781</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr"/>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q168" t="n">
+        <v>459723</v>
+      </c>
+      <c r="R168" t="n">
+        <v>6808290</v>
+      </c>
+      <c r="S168" t="n">
+        <v>20</v>
+      </c>
+      <c r="T168" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V168" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W168" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y168" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AD168" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE168" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG168" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT168" t="inlineStr"/>
+      <c r="AW168" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX168" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>123822912</v>
+      </c>
+      <c r="B169" t="n">
+        <v>57640</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr"/>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>Härkämäck, Härkämäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q169" t="n">
+        <v>459118</v>
+      </c>
+      <c r="R169" t="n">
+        <v>6808615</v>
+      </c>
+      <c r="S169" t="n">
+        <v>10</v>
+      </c>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V169" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W169" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y169" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="Z169" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AB169" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AD169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT169" t="inlineStr"/>
+      <c r="AW169" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX169" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>123826471</v>
+      </c>
+      <c r="B170" t="n">
+        <v>79399</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr"/>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>Andljusen, Andljusen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q170" t="n">
+        <v>458964</v>
+      </c>
+      <c r="R170" t="n">
+        <v>6808848</v>
+      </c>
+      <c r="S170" t="n">
+        <v>10</v>
+      </c>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V170" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W170" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y170" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="Z170" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AB170" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AD170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT170" t="inlineStr"/>
+      <c r="AW170" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX170" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>123829719</v>
+      </c>
+      <c r="B171" t="n">
+        <v>78786</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr"/>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>Härkämäck, Härkämäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q171" t="n">
+        <v>458966</v>
+      </c>
+      <c r="R171" t="n">
+        <v>6808279</v>
+      </c>
+      <c r="S171" t="n">
+        <v>15</v>
+      </c>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V171" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W171" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y171" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AD171" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE171" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG171" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT171" t="inlineStr"/>
+      <c r="AW171" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX171" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>123835308</v>
+      </c>
+      <c r="B172" t="n">
+        <v>78523</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr"/>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>Härkämäck, Härkämäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q172" t="n">
+        <v>459638</v>
+      </c>
+      <c r="R172" t="n">
+        <v>6808207</v>
+      </c>
+      <c r="S172" t="n">
+        <v>15</v>
+      </c>
+      <c r="T172" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V172" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W172" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y172" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AD172" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE172" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG172" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT172" t="inlineStr"/>
+      <c r="AW172" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX172" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>123826845</v>
+      </c>
+      <c r="B173" t="n">
+        <v>79399</v>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr"/>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>Andljusen, Andljusen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q173" t="n">
+        <v>458777</v>
+      </c>
+      <c r="R173" t="n">
+        <v>6808730</v>
+      </c>
+      <c r="S173" t="n">
+        <v>10</v>
+      </c>
+      <c r="T173" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V173" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W173" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y173" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="Z173" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AB173" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AD173" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE173" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG173" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT173" t="inlineStr"/>
+      <c r="AW173" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX173" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>123827076</v>
+      </c>
+      <c r="B174" t="n">
+        <v>78781</v>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr"/>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q174" t="n">
+        <v>459733</v>
+      </c>
+      <c r="R174" t="n">
+        <v>6808277</v>
+      </c>
+      <c r="S174" t="n">
+        <v>20</v>
+      </c>
+      <c r="T174" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V174" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W174" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y174" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AD174" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE174" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG174" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT174" t="inlineStr"/>
+      <c r="AW174" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX174" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>123828501</v>
+      </c>
+      <c r="B175" t="n">
+        <v>79375</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr"/>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>Härkämäck, Härkämäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q175" t="n">
+        <v>459099</v>
+      </c>
+      <c r="R175" t="n">
+        <v>6808563</v>
+      </c>
+      <c r="S175" t="n">
+        <v>10</v>
+      </c>
+      <c r="T175" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V175" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W175" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y175" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AD175" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE175" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG175" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT175" t="inlineStr"/>
+      <c r="AW175" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX175" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>123829038</v>
+      </c>
+      <c r="B176" t="n">
+        <v>78786</v>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E176" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr"/>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>Härkämäck, Härkämäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q176" t="n">
+        <v>459383</v>
+      </c>
+      <c r="R176" t="n">
+        <v>6808474</v>
+      </c>
+      <c r="S176" t="n">
+        <v>15</v>
+      </c>
+      <c r="T176" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V176" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W176" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y176" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AD176" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE176" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG176" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT176" t="inlineStr"/>
+      <c r="AW176" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX176" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>123829383</v>
+      </c>
+      <c r="B177" t="n">
+        <v>78786</v>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E177" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr"/>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>Härkämäck, Härkämäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q177" t="n">
+        <v>459164</v>
+      </c>
+      <c r="R177" t="n">
+        <v>6808349</v>
+      </c>
+      <c r="S177" t="n">
+        <v>15</v>
+      </c>
+      <c r="T177" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U177" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V177" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W177" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y177" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AD177" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE177" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG177" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT177" t="inlineStr"/>
+      <c r="AW177" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX177" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>123829449</v>
+      </c>
+      <c r="B178" t="n">
+        <v>78786</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E178" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr"/>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>Härkämäck, Härkämäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q178" t="n">
+        <v>459115</v>
+      </c>
+      <c r="R178" t="n">
+        <v>6808375</v>
+      </c>
+      <c r="S178" t="n">
+        <v>20</v>
+      </c>
+      <c r="T178" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V178" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W178" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y178" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AD178" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE178" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG178" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT178" t="inlineStr"/>
+      <c r="AW178" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX178" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>123822771</v>
+      </c>
+      <c r="B179" t="n">
+        <v>56697</v>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E179" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr"/>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>Härkämäck, Härkämäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q179" t="n">
+        <v>459307</v>
+      </c>
+      <c r="R179" t="n">
+        <v>6808524</v>
+      </c>
+      <c r="S179" t="n">
+        <v>10</v>
+      </c>
+      <c r="T179" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V179" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W179" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y179" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="Z179" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AB179" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AD179" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE179" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG179" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT179" t="inlineStr"/>
+      <c r="AW179" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX179" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>123826461</v>
+      </c>
+      <c r="B180" t="n">
+        <v>56700</v>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E180" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr"/>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>Andljusen, Andljusen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q180" t="n">
+        <v>458964</v>
+      </c>
+      <c r="R180" t="n">
+        <v>6808848</v>
+      </c>
+      <c r="S180" t="n">
+        <v>10</v>
+      </c>
+      <c r="T180" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V180" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W180" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y180" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="Z180" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AB180" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AD180" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE180" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG180" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT180" t="inlineStr"/>
+      <c r="AW180" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX180" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>123827055</v>
+      </c>
+      <c r="B181" t="n">
+        <v>78781</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E181" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr"/>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q181" t="n">
+        <v>459731</v>
+      </c>
+      <c r="R181" t="n">
+        <v>6808292</v>
+      </c>
+      <c r="S181" t="n">
+        <v>20</v>
+      </c>
+      <c r="T181" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V181" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W181" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y181" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AD181" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE181" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG181" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT181" t="inlineStr"/>
+      <c r="AW181" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX181" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>123828843</v>
+      </c>
+      <c r="B182" t="n">
+        <v>78786</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E182" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr"/>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>Härkämäck, Härkämäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q182" t="n">
+        <v>459477</v>
+      </c>
+      <c r="R182" t="n">
+        <v>6808405</v>
+      </c>
+      <c r="S182" t="n">
+        <v>15</v>
+      </c>
+      <c r="T182" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V182" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W182" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y182" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AD182" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE182" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG182" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT182" t="inlineStr"/>
+      <c r="AW182" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX182" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>123834044</v>
+      </c>
+      <c r="B183" t="n">
+        <v>78522</v>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E183" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr"/>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q183" t="n">
+        <v>459221</v>
+      </c>
+      <c r="R183" t="n">
+        <v>6808409</v>
+      </c>
+      <c r="S183" t="n">
+        <v>20</v>
+      </c>
+      <c r="T183" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V183" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W183" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y183" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AD183" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE183" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG183" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT183" t="inlineStr"/>
+      <c r="AW183" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX183" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>123829684</v>
+      </c>
+      <c r="B184" t="n">
+        <v>78786</v>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E184" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr"/>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>Härkämäck, Härkämäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q184" t="n">
+        <v>458980</v>
+      </c>
+      <c r="R184" t="n">
+        <v>6808290</v>
+      </c>
+      <c r="S184" t="n">
+        <v>15</v>
+      </c>
+      <c r="T184" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V184" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W184" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y184" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AD184" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE184" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG184" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT184" t="inlineStr"/>
+      <c r="AW184" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX184" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>123827370</v>
+      </c>
+      <c r="B185" t="n">
+        <v>79375</v>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E185" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr"/>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>Andljusen, Andljusen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q185" t="n">
+        <v>458810</v>
+      </c>
+      <c r="R185" t="n">
+        <v>6808640</v>
+      </c>
+      <c r="S185" t="n">
+        <v>10</v>
+      </c>
+      <c r="T185" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V185" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W185" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y185" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AD185" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE185" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG185" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT185" t="inlineStr"/>
+      <c r="AW185" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX185" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>123826738</v>
+      </c>
+      <c r="B186" t="n">
+        <v>78781</v>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E186" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr"/>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>Andljusen, Andljusen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q186" t="n">
+        <v>458836</v>
+      </c>
+      <c r="R186" t="n">
+        <v>6808778</v>
+      </c>
+      <c r="S186" t="n">
+        <v>10</v>
+      </c>
+      <c r="T186" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V186" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W186" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y186" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="Z186" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AB186" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AD186" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE186" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG186" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT186" t="inlineStr"/>
+      <c r="AW186" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX186" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>123827572</v>
+      </c>
+      <c r="B187" t="n">
+        <v>78786</v>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E187" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr"/>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>Andljusen, Andljusen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q187" t="n">
+        <v>458901</v>
+      </c>
+      <c r="R187" t="n">
+        <v>6808619</v>
+      </c>
+      <c r="S187" t="n">
+        <v>10</v>
+      </c>
+      <c r="T187" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V187" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W187" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y187" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AD187" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE187" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG187" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT187" t="inlineStr"/>
+      <c r="AW187" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX187" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>123827168</v>
+      </c>
+      <c r="B188" t="n">
+        <v>78781</v>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E188" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr"/>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q188" t="n">
+        <v>459733</v>
+      </c>
+      <c r="R188" t="n">
+        <v>6808263</v>
+      </c>
+      <c r="S188" t="n">
+        <v>20</v>
+      </c>
+      <c r="T188" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U188" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V188" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W188" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y188" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AD188" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE188" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG188" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT188" t="inlineStr"/>
+      <c r="AW188" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX188" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>123827682</v>
+      </c>
+      <c r="B189" t="n">
+        <v>78786</v>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E189" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr"/>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>Härkämäck, Härkämäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q189" t="n">
+        <v>458964</v>
+      </c>
+      <c r="R189" t="n">
+        <v>6808578</v>
+      </c>
+      <c r="S189" t="n">
+        <v>10</v>
+      </c>
+      <c r="T189" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U189" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V189" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W189" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y189" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AD189" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE189" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG189" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT189" t="inlineStr"/>
+      <c r="AW189" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX189" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>123828083</v>
+      </c>
+      <c r="B190" t="n">
+        <v>79404</v>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E190" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr"/>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>Härkämäck, Härkämäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q190" t="n">
+        <v>459055</v>
+      </c>
+      <c r="R190" t="n">
+        <v>6808554</v>
+      </c>
+      <c r="S190" t="n">
+        <v>10</v>
+      </c>
+      <c r="T190" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V190" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W190" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y190" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AD190" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE190" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG190" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT190" t="inlineStr"/>
+      <c r="AW190" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX190" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>123827249</v>
+      </c>
+      <c r="B191" t="n">
+        <v>78165</v>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E191" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr"/>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>Andljusen, Andljusen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q191" t="n">
+        <v>458738</v>
+      </c>
+      <c r="R191" t="n">
+        <v>6808608</v>
+      </c>
+      <c r="S191" t="n">
+        <v>10</v>
+      </c>
+      <c r="T191" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U191" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V191" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W191" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y191" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AD191" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE191" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG191" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT191" t="inlineStr"/>
+      <c r="AW191" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX191" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>123829438</v>
+      </c>
+      <c r="B192" t="n">
+        <v>78523</v>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E192" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr"/>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>Härkämäck, Härkämäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q192" t="n">
+        <v>459113</v>
+      </c>
+      <c r="R192" t="n">
+        <v>6808380</v>
+      </c>
+      <c r="S192" t="n">
+        <v>15</v>
+      </c>
+      <c r="T192" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U192" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V192" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W192" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y192" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AD192" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE192" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG192" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT192" t="inlineStr"/>
+      <c r="AW192" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX192" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>123826647</v>
+      </c>
+      <c r="B193" t="n">
+        <v>78781</v>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E193" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr"/>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>Andljusen, Andljusen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q193" t="n">
+        <v>458946</v>
+      </c>
+      <c r="R193" t="n">
+        <v>6808820</v>
+      </c>
+      <c r="S193" t="n">
+        <v>10</v>
+      </c>
+      <c r="T193" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U193" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V193" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W193" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y193" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="Z193" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AB193" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AD193" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE193" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG193" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT193" t="inlineStr"/>
+      <c r="AW193" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX193" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>123827048</v>
+      </c>
+      <c r="B194" t="n">
+        <v>78782</v>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E194" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr"/>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>Härkämäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q194" t="n">
+        <v>459723</v>
+      </c>
+      <c r="R194" t="n">
+        <v>6808329</v>
+      </c>
+      <c r="S194" t="n">
+        <v>10</v>
+      </c>
+      <c r="T194" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U194" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V194" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W194" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y194" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC194" t="inlineStr">
+        <is>
+          <t>Garnlav i synfältet, ca 50 meter i radie. Miljöbilder.</t>
+        </is>
+      </c>
+      <c r="AD194" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE194" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG194" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT194" t="inlineStr"/>
+      <c r="AW194" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX194" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>123826877</v>
+      </c>
+      <c r="B195" t="n">
+        <v>78781</v>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E195" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr"/>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q195" t="n">
+        <v>459762</v>
+      </c>
+      <c r="R195" t="n">
+        <v>6808288</v>
+      </c>
+      <c r="S195" t="n">
+        <v>20</v>
+      </c>
+      <c r="T195" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V195" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W195" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y195" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AD195" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE195" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG195" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT195" t="inlineStr"/>
+      <c r="AW195" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX195" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>123826892</v>
+      </c>
+      <c r="B196" t="n">
+        <v>78781</v>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E196" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr"/>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>Andljusen, Andljusen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q196" t="n">
+        <v>458763</v>
+      </c>
+      <c r="R196" t="n">
+        <v>6808709</v>
+      </c>
+      <c r="S196" t="n">
+        <v>10</v>
+      </c>
+      <c r="T196" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V196" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W196" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y196" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="Z196" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AB196" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AD196" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE196" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG196" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT196" t="inlineStr"/>
+      <c r="AW196" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX196" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>123829085</v>
+      </c>
+      <c r="B197" t="n">
+        <v>78523</v>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E197" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr"/>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>Härkämäck, Härkämäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q197" t="n">
+        <v>459348</v>
+      </c>
+      <c r="R197" t="n">
+        <v>6808448</v>
+      </c>
+      <c r="S197" t="n">
+        <v>12</v>
+      </c>
+      <c r="T197" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V197" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W197" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y197" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AD197" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE197" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG197" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT197" t="inlineStr"/>
+      <c r="AW197" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX197" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>123835949</v>
+      </c>
+      <c r="B198" t="n">
+        <v>78786</v>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E198" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr"/>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>Härkämäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q198" t="n">
+        <v>459669</v>
+      </c>
+      <c r="R198" t="n">
+        <v>6808383</v>
+      </c>
+      <c r="S198" t="n">
+        <v>10</v>
+      </c>
+      <c r="T198" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V198" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W198" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y198" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC198" t="inlineStr">
+        <is>
+          <t>I en radie av ca 50 meter.  Miljöbild.</t>
+        </is>
+      </c>
+      <c r="AD198" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE198" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG198" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT198" t="inlineStr"/>
+      <c r="AW198" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX198" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>123827028</v>
+      </c>
+      <c r="B199" t="n">
+        <v>78781</v>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E199" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr"/>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q199" t="n">
+        <v>459725</v>
+      </c>
+      <c r="R199" t="n">
+        <v>6808300</v>
+      </c>
+      <c r="S199" t="n">
+        <v>20</v>
+      </c>
+      <c r="T199" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V199" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W199" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y199" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AD199" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE199" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG199" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT199" t="inlineStr"/>
+      <c r="AW199" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX199" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>123822130</v>
+      </c>
+      <c r="B200" t="n">
+        <v>56697</v>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E200" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr"/>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>Andljusen, Andljusen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q200" t="n">
+        <v>458948</v>
+      </c>
+      <c r="R200" t="n">
+        <v>6808785</v>
+      </c>
+      <c r="S200" t="n">
+        <v>10</v>
+      </c>
+      <c r="T200" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V200" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W200" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y200" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="Z200" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AB200" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="AD200" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE200" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG200" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT200" t="inlineStr"/>
+      <c r="AW200" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX200" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>123826946</v>
+      </c>
+      <c r="B201" t="n">
+        <v>78781</v>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E201" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr"/>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>Andljusen, Andljusen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q201" t="n">
+        <v>458734</v>
+      </c>
+      <c r="R201" t="n">
+        <v>6808688</v>
+      </c>
+      <c r="S201" t="n">
+        <v>10</v>
+      </c>
+      <c r="T201" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V201" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W201" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y201" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="Z201" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AB201" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AD201" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE201" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG201" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT201" t="inlineStr"/>
+      <c r="AW201" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX201" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>123829071</v>
+      </c>
+      <c r="B202" t="n">
+        <v>78786</v>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E202" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr"/>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>Härkämäck, Härkämäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q202" t="n">
+        <v>459366</v>
+      </c>
+      <c r="R202" t="n">
+        <v>6808535</v>
+      </c>
+      <c r="S202" t="n">
+        <v>10</v>
+      </c>
+      <c r="T202" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U202" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V202" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W202" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y202" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AD202" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE202" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG202" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT202" t="inlineStr"/>
+      <c r="AW202" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX202" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>123826851</v>
+      </c>
+      <c r="B203" t="n">
+        <v>78517</v>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E203" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr"/>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>Andljusen, Andljusen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q203" t="n">
+        <v>458777</v>
+      </c>
+      <c r="R203" t="n">
+        <v>6808730</v>
+      </c>
+      <c r="S203" t="n">
+        <v>10</v>
+      </c>
+      <c r="T203" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V203" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W203" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y203" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="Z203" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AB203" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AD203" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE203" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG203" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT203" t="inlineStr"/>
+      <c r="AW203" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX203" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>123828373</v>
+      </c>
+      <c r="B204" t="n">
+        <v>78523</v>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E204" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr"/>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>Härkämäck, Härkämäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q204" t="n">
+        <v>459084</v>
+      </c>
+      <c r="R204" t="n">
+        <v>6808547</v>
+      </c>
+      <c r="S204" t="n">
+        <v>10</v>
+      </c>
+      <c r="T204" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V204" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W204" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y204" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AD204" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE204" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG204" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT204" t="inlineStr"/>
+      <c r="AW204" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX204" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>123828543</v>
+      </c>
+      <c r="B205" t="n">
+        <v>78786</v>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E205" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr"/>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>Härkämäck, Härkämäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q205" t="n">
+        <v>459107</v>
+      </c>
+      <c r="R205" t="n">
+        <v>6808550</v>
+      </c>
+      <c r="S205" t="n">
+        <v>10</v>
+      </c>
+      <c r="T205" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V205" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W205" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y205" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AD205" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE205" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG205" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT205" t="inlineStr"/>
+      <c r="AW205" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX205" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>123826696</v>
+      </c>
+      <c r="B206" t="n">
+        <v>78781</v>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E206" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr"/>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>Andljusen, Andljusen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q206" t="n">
+        <v>458878</v>
+      </c>
+      <c r="R206" t="n">
+        <v>6808805</v>
+      </c>
+      <c r="S206" t="n">
+        <v>10</v>
+      </c>
+      <c r="T206" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V206" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W206" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y206" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="Z206" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AB206" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AD206" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE206" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG206" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT206" t="inlineStr"/>
+      <c r="AW206" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX206" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>123828917</v>
+      </c>
+      <c r="B207" t="n">
+        <v>78523</v>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E207" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr"/>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>Härkämäck, Härkämäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q207" t="n">
+        <v>459456</v>
+      </c>
+      <c r="R207" t="n">
+        <v>6808405</v>
+      </c>
+      <c r="S207" t="n">
+        <v>15</v>
+      </c>
+      <c r="T207" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V207" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W207" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y207" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AD207" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE207" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG207" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT207" t="inlineStr"/>
+      <c r="AW207" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX207" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>123829390</v>
+      </c>
+      <c r="B208" t="n">
+        <v>78523</v>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E208" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr"/>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>Härkämäck, Härkämäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q208" t="n">
+        <v>459134</v>
+      </c>
+      <c r="R208" t="n">
+        <v>6808361</v>
+      </c>
+      <c r="S208" t="n">
+        <v>15</v>
+      </c>
+      <c r="T208" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U208" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V208" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W208" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y208" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AD208" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE208" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG208" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT208" t="inlineStr"/>
+      <c r="AW208" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX208" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>123828978</v>
+      </c>
+      <c r="B209" t="n">
+        <v>78786</v>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E209" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr"/>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>Härkämäck, Härkämäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q209" t="n">
+        <v>459415</v>
+      </c>
+      <c r="R209" t="n">
+        <v>6808460</v>
+      </c>
+      <c r="S209" t="n">
+        <v>15</v>
+      </c>
+      <c r="T209" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V209" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W209" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y209" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA209" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AD209" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE209" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG209" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT209" t="inlineStr"/>
+      <c r="AW209" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX209" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY209" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 61324-2022 artfynd.xlsx
+++ b/artfynd/A 61324-2022 artfynd.xlsx
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123548810</v>
+        <v>123544112</v>
       </c>
       <c r="B3" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,34 +801,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Andljusen, Andljusen, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459189</v>
+        <v>459506</v>
       </c>
       <c r="R3" t="n">
-        <v>6808830</v>
+        <v>6808960</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123544112</v>
+        <v>123548209</v>
       </c>
       <c r="B4" t="n">
         <v>78788</v>
@@ -933,17 +933,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459506</v>
+        <v>459014</v>
       </c>
       <c r="R4" t="n">
-        <v>6808960</v>
+        <v>6808874</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -997,22 +997,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123548209</v>
+        <v>123548810</v>
       </c>
       <c r="B5" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,21 +1025,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1049,13 +1049,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459014</v>
+        <v>459189</v>
       </c>
       <c r="R5" t="n">
-        <v>6808874</v>
+        <v>6808830</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,12 +1109,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1798,10 +1798,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123549418</v>
+        <v>123549156</v>
       </c>
       <c r="B12" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1810,46 +1810,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>459318</v>
+        <v>459240</v>
       </c>
       <c r="R12" t="n">
-        <v>6808809</v>
+        <v>6808794</v>
       </c>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1878,7 +1873,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1888,12 +1883,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:21</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Under betestall</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1908,19 +1898,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123549156</v>
+        <v>123543987</v>
       </c>
       <c r="B13" t="n">
         <v>78788</v>
@@ -1960,10 +1950,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>459240</v>
+        <v>459521</v>
       </c>
       <c r="R13" t="n">
-        <v>6808794</v>
+        <v>6808918</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1995,7 +1985,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2005,7 +1995,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2032,10 +2022,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123543987</v>
+        <v>123548636</v>
       </c>
       <c r="B14" t="n">
-        <v>78788</v>
+        <v>78524</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2048,34 +2038,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>459521</v>
+        <v>459184</v>
       </c>
       <c r="R14" t="n">
-        <v>6808918</v>
+        <v>6808784</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2107,7 +2097,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2117,7 +2107,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2144,10 +2134,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123548636</v>
+        <v>123548196</v>
       </c>
       <c r="B15" t="n">
-        <v>78524</v>
+        <v>78788</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2160,34 +2150,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>459184</v>
+        <v>459024</v>
       </c>
       <c r="R15" t="n">
-        <v>6808784</v>
+        <v>6808872</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2219,7 +2209,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2229,7 +2219,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2256,10 +2246,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123548196</v>
+        <v>123549418</v>
       </c>
       <c r="B16" t="n">
-        <v>78788</v>
+        <v>56700</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2268,41 +2258,46 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Andljusen, Andljusen, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>459024</v>
+        <v>459318</v>
       </c>
       <c r="R16" t="n">
-        <v>6808872</v>
+        <v>6808809</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2331,7 +2326,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2341,7 +2336,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Under betestall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2356,22 +2356,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123544364</v>
+        <v>123546440</v>
       </c>
       <c r="B17" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2384,21 +2384,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2414,7 +2414,7 @@
         <v>6808917</v>
       </c>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2480,10 +2480,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123546440</v>
+        <v>123544364</v>
       </c>
       <c r="B18" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2496,21 +2496,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2526,7 +2526,7 @@
         <v>6808917</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2816,10 +2816,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123549137</v>
+        <v>123548646</v>
       </c>
       <c r="B21" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2832,34 +2832,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>459240</v>
+        <v>459185</v>
       </c>
       <c r="R21" t="n">
-        <v>6808796</v>
+        <v>6808785</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2928,10 +2928,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123548646</v>
+        <v>123549137</v>
       </c>
       <c r="B22" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2944,34 +2944,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>459185</v>
+        <v>459240</v>
       </c>
       <c r="R22" t="n">
-        <v>6808785</v>
+        <v>6808796</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -6094,10 +6094,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123566087</v>
+        <v>123577141</v>
       </c>
       <c r="B50" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6110,37 +6110,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>459733</v>
+        <v>459462</v>
       </c>
       <c r="R50" t="n">
-        <v>6808745</v>
+        <v>6808627</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6179,7 +6179,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6194,19 +6194,19 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123575662</v>
+        <v>123566087</v>
       </c>
       <c r="B51" t="n">
         <v>78788</v>
@@ -6242,17 +6242,17 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>459583</v>
+        <v>459733</v>
       </c>
       <c r="R51" t="n">
-        <v>6808519</v>
+        <v>6808745</v>
       </c>
       <c r="S51" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6291,7 +6291,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6306,19 +6306,19 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123576104</v>
+        <v>123575662</v>
       </c>
       <c r="B52" t="n">
         <v>78788</v>
@@ -6358,13 +6358,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>459515</v>
+        <v>459583</v>
       </c>
       <c r="R52" t="n">
-        <v>6808562</v>
+        <v>6808519</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6403,7 +6403,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6418,19 +6418,19 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123564616</v>
+        <v>123576104</v>
       </c>
       <c r="B53" t="n">
         <v>78788</v>
@@ -6466,17 +6466,17 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>459687</v>
+        <v>459515</v>
       </c>
       <c r="R53" t="n">
-        <v>6808829</v>
+        <v>6808562</v>
       </c>
       <c r="S53" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6505,7 +6505,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6515,7 +6515,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6530,22 +6530,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123577141</v>
+        <v>123564616</v>
       </c>
       <c r="B54" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6558,37 +6558,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>459462</v>
+        <v>459687</v>
       </c>
       <c r="R54" t="n">
-        <v>6808627</v>
+        <v>6808829</v>
       </c>
       <c r="S54" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6617,7 +6617,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6627,7 +6627,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6642,12 +6642,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -9036,10 +9036,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>123577149</v>
+        <v>123577066</v>
       </c>
       <c r="B76" t="n">
-        <v>78525</v>
+        <v>56700</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9048,41 +9048,46 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>459571</v>
+        <v>459565</v>
       </c>
       <c r="R76" t="n">
-        <v>6808546</v>
+        <v>6808543</v>
       </c>
       <c r="S76" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9111,7 +9116,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9121,7 +9126,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9148,10 +9153,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>123577066</v>
+        <v>123577149</v>
       </c>
       <c r="B77" t="n">
-        <v>56700</v>
+        <v>78525</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9160,46 +9165,41 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>459565</v>
+        <v>459571</v>
       </c>
       <c r="R77" t="n">
-        <v>6808543</v>
+        <v>6808546</v>
       </c>
       <c r="S77" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9228,7 +9228,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9238,7 +9238,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9377,10 +9377,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>123575257</v>
+        <v>123576740</v>
       </c>
       <c r="B79" t="n">
-        <v>78525</v>
+        <v>79377</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9393,21 +9393,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9417,13 +9417,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>459595</v>
+        <v>459565</v>
       </c>
       <c r="R79" t="n">
-        <v>6808516</v>
+        <v>6808543</v>
       </c>
       <c r="S79" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9452,7 +9452,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9462,7 +9462,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9489,10 +9489,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>123576740</v>
+        <v>123575257</v>
       </c>
       <c r="B80" t="n">
-        <v>79377</v>
+        <v>78525</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9505,21 +9505,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9529,13 +9529,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>459565</v>
+        <v>459595</v>
       </c>
       <c r="R80" t="n">
-        <v>6808543</v>
+        <v>6808516</v>
       </c>
       <c r="S80" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9564,7 +9564,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9574,7 +9574,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -14177,10 +14177,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>123732682</v>
+        <v>123727583</v>
       </c>
       <c r="B121" t="n">
-        <v>78788</v>
+        <v>56700</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -14189,38 +14189,38 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Andljusen, Dlr</t>
+          <t>Dyvran, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>458711</v>
+        <v>458880</v>
       </c>
       <c r="R121" t="n">
-        <v>6808858</v>
+        <v>6808416</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14257,7 +14257,7 @@
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>Miljöbild.</t>
+          <t>Tjäderspillning under tjädertall med garnlav.</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14284,10 +14284,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>123727583</v>
+        <v>123732682</v>
       </c>
       <c r="B122" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -14296,38 +14296,38 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Dyvran, Dlr</t>
+          <t>Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>458880</v>
+        <v>458711</v>
       </c>
       <c r="R122" t="n">
-        <v>6808416</v>
+        <v>6808858</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -14364,7 +14364,7 @@
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>Tjäderspillning under tjädertall med garnlav.</t>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -17307,10 +17307,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>123822130</v>
+        <v>123835827</v>
       </c>
       <c r="B151" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -17319,43 +17319,38 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Andljusen, Andljusen, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>458948</v>
+        <v>459669</v>
       </c>
       <c r="R151" t="n">
-        <v>6808785</v>
+        <v>6808284</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17385,19 +17380,14 @@
           <t>2025-04-07</t>
         </is>
       </c>
-      <c r="Z151" t="inlineStr">
-        <is>
-          <t>09:09</t>
-        </is>
-      </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-04-07</t>
         </is>
       </c>
-      <c r="AB151" t="inlineStr">
-        <is>
-          <t>09:09</t>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>Garnlav i alla riktningar, radie ca 50 meter. Miljöbild.</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -17412,19 +17402,19 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>123835827</v>
+        <v>123826760</v>
       </c>
       <c r="B152" t="n">
         <v>78788</v>
@@ -17460,14 +17450,14 @@
       <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>459669</v>
+        <v>458819</v>
       </c>
       <c r="R152" t="n">
-        <v>6808284</v>
+        <v>6808759</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17497,14 +17487,19 @@
           <t>2025-04-07</t>
         </is>
       </c>
+      <c r="Z152" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-04-07</t>
         </is>
       </c>
-      <c r="AC152" t="inlineStr">
-        <is>
-          <t>Garnlav i alla riktningar, radie ca 50 meter. Miljöbild.</t>
+      <c r="AB152" t="inlineStr">
+        <is>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17519,22 +17514,22 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>123826760</v>
+        <v>123826471</v>
       </c>
       <c r="B153" t="n">
-        <v>78788</v>
+        <v>79406</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -17547,21 +17542,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -17571,10 +17566,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>458819</v>
+        <v>458964</v>
       </c>
       <c r="R153" t="n">
-        <v>6808759</v>
+        <v>6808848</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17643,10 +17638,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>123826471</v>
+        <v>123828843</v>
       </c>
       <c r="B154" t="n">
-        <v>79406</v>
+        <v>78788</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -17659,37 +17654,37 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Andljusen, Andljusen, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>458964</v>
+        <v>459477</v>
       </c>
       <c r="R154" t="n">
-        <v>6808848</v>
+        <v>6808405</v>
       </c>
       <c r="S154" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -17716,19 +17711,9 @@
           <t>2025-04-07</t>
         </is>
       </c>
-      <c r="Z154" t="inlineStr">
-        <is>
-          <t>11:53</t>
-        </is>
-      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AB154" t="inlineStr">
-        <is>
-          <t>11:53</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17743,22 +17728,22 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>123828843</v>
+        <v>123822130</v>
       </c>
       <c r="B155" t="n">
-        <v>78788</v>
+        <v>56700</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -17767,41 +17752,46 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>459477</v>
+        <v>458948</v>
       </c>
       <c r="R155" t="n">
-        <v>6808405</v>
+        <v>6808785</v>
       </c>
       <c r="S155" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -17828,9 +17818,19 @@
           <t>2025-04-07</t>
         </is>
       </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17845,12 +17845,12 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
@@ -18795,7 +18795,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>123829348</v>
+        <v>123829438</v>
       </c>
       <c r="B165" t="n">
         <v>78525</v>
@@ -18835,10 +18835,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>459230</v>
+        <v>459113</v>
       </c>
       <c r="R165" t="n">
-        <v>6808362</v>
+        <v>6808380</v>
       </c>
       <c r="S165" t="n">
         <v>15</v>
@@ -18897,7 +18897,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>123829438</v>
+        <v>123829348</v>
       </c>
       <c r="B166" t="n">
         <v>78525</v>
@@ -18937,10 +18937,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>459113</v>
+        <v>459230</v>
       </c>
       <c r="R166" t="n">
-        <v>6808380</v>
+        <v>6808362</v>
       </c>
       <c r="S166" t="n">
         <v>15</v>
@@ -22149,10 +22149,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>123822771</v>
+        <v>123822912</v>
       </c>
       <c r="B197" t="n">
-        <v>56700</v>
+        <v>57644</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -22161,31 +22161,31 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
       <c r="M197" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P197" t="inlineStr">
@@ -22194,10 +22194,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>459307</v>
+        <v>459118</v>
       </c>
       <c r="R197" t="n">
-        <v>6808524</v>
+        <v>6808615</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -22229,7 +22229,7 @@
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
@@ -22239,7 +22239,7 @@
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -22266,10 +22266,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>123822912</v>
+        <v>123822771</v>
       </c>
       <c r="B198" t="n">
-        <v>57644</v>
+        <v>56700</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -22278,31 +22278,31 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
       <c r="M198" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P198" t="inlineStr">
@@ -22311,10 +22311,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>459118</v>
+        <v>459307</v>
       </c>
       <c r="R198" t="n">
-        <v>6808615</v>
+        <v>6808524</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -22346,7 +22346,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -22356,7 +22356,7 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -23764,10 +23764,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>123866301</v>
+        <v>123866513</v>
       </c>
       <c r="B212" t="n">
-        <v>79377</v>
+        <v>78788</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -23780,37 +23780,37 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>459260</v>
+        <v>459177</v>
       </c>
       <c r="R212" t="n">
-        <v>6808646</v>
+        <v>6808709</v>
       </c>
       <c r="S212" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T212" t="inlineStr">
         <is>
@@ -23854,19 +23854,19 @@
       <c r="AT212" t="inlineStr"/>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>123866613</v>
+        <v>123866301</v>
       </c>
       <c r="B213" t="n">
         <v>79377</v>
@@ -23906,13 +23906,13 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>459110</v>
+        <v>459260</v>
       </c>
       <c r="R213" t="n">
-        <v>6808718</v>
+        <v>6808646</v>
       </c>
       <c r="S213" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T213" t="inlineStr">
         <is>
@@ -23968,10 +23968,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>123866513</v>
+        <v>123866613</v>
       </c>
       <c r="B214" t="n">
-        <v>78788</v>
+        <v>79377</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -23984,37 +23984,37 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>459177</v>
+        <v>459110</v>
       </c>
       <c r="R214" t="n">
-        <v>6808709</v>
+        <v>6808718</v>
       </c>
       <c r="S214" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T214" t="inlineStr">
         <is>
@@ -24058,12 +24058,12 @@
       <c r="AT214" t="inlineStr"/>
       <c r="AW214" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX214" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
@@ -24396,10 +24396,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>123865793</v>
+        <v>123866998</v>
       </c>
       <c r="B218" t="n">
-        <v>56700</v>
+        <v>79377</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -24408,46 +24408,41 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
-      <c r="M218" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P218" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>459341</v>
+        <v>458925</v>
       </c>
       <c r="R218" t="n">
-        <v>6808761</v>
+        <v>6808789</v>
       </c>
       <c r="S218" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T218" t="inlineStr">
         <is>
@@ -24491,22 +24486,22 @@
       <c r="AT218" t="inlineStr"/>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>123868751</v>
+        <v>123865793</v>
       </c>
       <c r="B219" t="n">
-        <v>78788</v>
+        <v>56700</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -24515,41 +24510,46 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P219" t="inlineStr">
         <is>
-          <t>Andljusen, Dlr</t>
+          <t>Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>459228</v>
+        <v>459341</v>
       </c>
       <c r="R219" t="n">
-        <v>6808886</v>
+        <v>6808761</v>
       </c>
       <c r="S219" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T219" t="inlineStr">
         <is>
@@ -24593,22 +24593,22 @@
       <c r="AT219" t="inlineStr"/>
       <c r="AW219" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>123866998</v>
+        <v>123868751</v>
       </c>
       <c r="B220" t="n">
-        <v>79377</v>
+        <v>78788</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -24621,37 +24621,37 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
       <c r="P220" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>458925</v>
+        <v>459228</v>
       </c>
       <c r="R220" t="n">
-        <v>6808789</v>
+        <v>6808886</v>
       </c>
       <c r="S220" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T220" t="inlineStr">
         <is>
@@ -24695,12 +24695,12 @@
       <c r="AT220" t="inlineStr"/>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
@@ -24809,10 +24809,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>123866711</v>
+        <v>123867031</v>
       </c>
       <c r="B222" t="n">
-        <v>56700</v>
+        <v>78525</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -24821,46 +24821,41 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
-      <c r="M222" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P222" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>459001</v>
+        <v>458879</v>
       </c>
       <c r="R222" t="n">
-        <v>6808842</v>
+        <v>6808768</v>
       </c>
       <c r="S222" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T222" t="inlineStr">
         <is>
@@ -24916,10 +24911,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>123867031</v>
+        <v>123866711</v>
       </c>
       <c r="B223" t="n">
-        <v>78525</v>
+        <v>56700</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -24928,41 +24923,46 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P223" t="inlineStr">
         <is>
-          <t>Andljusen, Andljusen, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>458879</v>
+        <v>459001</v>
       </c>
       <c r="R223" t="n">
-        <v>6808768</v>
+        <v>6808842</v>
       </c>
       <c r="S223" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T223" t="inlineStr">
         <is>
@@ -25125,10 +25125,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>123866561</v>
+        <v>123866559</v>
       </c>
       <c r="B225" t="n">
-        <v>79377</v>
+        <v>78788</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -25141,37 +25141,37 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
       <c r="P225" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>459159</v>
+        <v>459128</v>
       </c>
       <c r="R225" t="n">
-        <v>6808628</v>
+        <v>6808639</v>
       </c>
       <c r="S225" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T225" t="inlineStr">
         <is>
@@ -25201,11 +25201,6 @@
       <c r="AA225" t="inlineStr">
         <is>
           <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AC225" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -25220,12 +25215,12 @@
       <c r="AT225" t="inlineStr"/>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
@@ -25339,10 +25334,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>123866559</v>
+        <v>123866561</v>
       </c>
       <c r="B227" t="n">
-        <v>78788</v>
+        <v>79377</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -25355,37 +25350,37 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
       <c r="P227" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>459128</v>
+        <v>459159</v>
       </c>
       <c r="R227" t="n">
-        <v>6808639</v>
+        <v>6808628</v>
       </c>
       <c r="S227" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T227" t="inlineStr">
         <is>
@@ -25415,6 +25410,11 @@
       <c r="AA227" t="inlineStr">
         <is>
           <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC227" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -25429,12 +25429,12 @@
       <c r="AT227" t="inlineStr"/>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
@@ -25655,10 +25655,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>123864080</v>
+        <v>123866153</v>
       </c>
       <c r="B230" t="n">
-        <v>77716</v>
+        <v>56700</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -25667,41 +25667,51 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>6487</v>
+        <v>100138</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P230" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>459555</v>
+        <v>459211</v>
       </c>
       <c r="R230" t="n">
-        <v>6808660</v>
+        <v>6808724</v>
       </c>
       <c r="S230" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T230" t="inlineStr">
         <is>
@@ -25745,22 +25755,22 @@
       <c r="AT230" t="inlineStr"/>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>123866153</v>
+        <v>123864080</v>
       </c>
       <c r="B231" t="n">
-        <v>56700</v>
+        <v>77716</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
@@ -25769,51 +25779,41 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>100138</v>
+        <v>6487</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
-      <c r="L231" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M231" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P231" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>459211</v>
+        <v>459555</v>
       </c>
       <c r="R231" t="n">
-        <v>6808724</v>
+        <v>6808660</v>
       </c>
       <c r="S231" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T231" t="inlineStr">
         <is>
@@ -25857,12 +25857,12 @@
       <c r="AT231" t="inlineStr"/>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
@@ -27153,7 +27153,7 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>123864359</v>
+        <v>123866920</v>
       </c>
       <c r="B244" t="n">
         <v>78788</v>
@@ -27189,17 +27189,17 @@
       <c r="I244" t="inlineStr"/>
       <c r="P244" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>459500</v>
+        <v>458966</v>
       </c>
       <c r="R244" t="n">
-        <v>6808604</v>
+        <v>6808788</v>
       </c>
       <c r="S244" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T244" t="inlineStr">
         <is>
@@ -27229,11 +27229,6 @@
       <c r="AA244" t="inlineStr">
         <is>
           <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AC244" t="inlineStr">
-        <is>
-          <t>Synligt i en radie av ca 50 meter.  Miljöbild på bland annat torraka/silvertall.</t>
         </is>
       </c>
       <c r="AD244" t="b">
@@ -27248,19 +27243,19 @@
       <c r="AT244" t="inlineStr"/>
       <c r="AW244" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX244" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>123866920</v>
+        <v>123864359</v>
       </c>
       <c r="B245" t="n">
         <v>78788</v>
@@ -27296,17 +27291,17 @@
       <c r="I245" t="inlineStr"/>
       <c r="P245" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>458966</v>
+        <v>459500</v>
       </c>
       <c r="R245" t="n">
-        <v>6808788</v>
+        <v>6808604</v>
       </c>
       <c r="S245" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T245" t="inlineStr">
         <is>
@@ -27336,6 +27331,11 @@
       <c r="AA245" t="inlineStr">
         <is>
           <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC245" t="inlineStr">
+        <is>
+          <t>Synligt i en radie av ca 50 meter.  Miljöbild på bland annat torraka/silvertall.</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -27350,12 +27350,12 @@
       <c r="AT245" t="inlineStr"/>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
@@ -28101,10 +28101,10 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>123864015</v>
+        <v>123864326</v>
       </c>
       <c r="B253" t="n">
-        <v>79377</v>
+        <v>78433</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
@@ -28117,21 +28117,21 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -28141,13 +28141,13 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>459594</v>
+        <v>459507</v>
       </c>
       <c r="R253" t="n">
-        <v>6808664</v>
+        <v>6808603</v>
       </c>
       <c r="S253" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T253" t="inlineStr">
         <is>
@@ -28203,10 +28203,10 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>123864326</v>
+        <v>123866750</v>
       </c>
       <c r="B254" t="n">
-        <v>78433</v>
+        <v>78788</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
@@ -28219,37 +28219,37 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
       <c r="P254" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>459507</v>
+        <v>459080</v>
       </c>
       <c r="R254" t="n">
-        <v>6808603</v>
+        <v>6808643</v>
       </c>
       <c r="S254" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T254" t="inlineStr">
         <is>
@@ -28279,6 +28279,11 @@
       <c r="AA254" t="inlineStr">
         <is>
           <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC254" t="inlineStr">
+        <is>
+          <t>I en radie av ca 50 meter, garnlav. Miljöbilder.</t>
         </is>
       </c>
       <c r="AD254" t="b">
@@ -28293,22 +28298,22 @@
       <c r="AT254" t="inlineStr"/>
       <c r="AW254" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>123866750</v>
+        <v>123869316</v>
       </c>
       <c r="B255" t="n">
-        <v>78788</v>
+        <v>56700</v>
       </c>
       <c r="C255" t="inlineStr">
         <is>
@@ -28317,41 +28322,46 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P255" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Dlr</t>
+          <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>459080</v>
+        <v>459292</v>
       </c>
       <c r="R255" t="n">
-        <v>6808643</v>
+        <v>6808848</v>
       </c>
       <c r="S255" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T255" t="inlineStr">
         <is>
@@ -28381,11 +28391,6 @@
       <c r="AA255" t="inlineStr">
         <is>
           <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AC255" t="inlineStr">
-        <is>
-          <t>I en radie av ca 50 meter, garnlav. Miljöbilder.</t>
         </is>
       </c>
       <c r="AD255" t="b">
@@ -28400,22 +28405,22 @@
       <c r="AT255" t="inlineStr"/>
       <c r="AW255" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX255" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>123869316</v>
+        <v>123864015</v>
       </c>
       <c r="B256" t="n">
-        <v>56700</v>
+        <v>79377</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
@@ -28424,46 +28429,41 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
-      <c r="M256" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P256" t="inlineStr">
         <is>
-          <t>Andljusen, Andljusen, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>459292</v>
+        <v>459594</v>
       </c>
       <c r="R256" t="n">
-        <v>6808848</v>
+        <v>6808664</v>
       </c>
       <c r="S256" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T256" t="inlineStr">
         <is>
@@ -28507,12 +28507,12 @@
       <c r="AT256" t="inlineStr"/>
       <c r="AW256" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY256" t="inlineStr"/>
@@ -39705,10 +39705,10 @@
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>123920448</v>
+        <v>123920315</v>
       </c>
       <c r="B366" t="n">
-        <v>56700</v>
+        <v>79406</v>
       </c>
       <c r="C366" t="inlineStr">
         <is>
@@ -39717,43 +39717,38 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E366" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I366" t="inlineStr"/>
-      <c r="M366" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P366" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q366" t="n">
-        <v>458790</v>
+        <v>459450</v>
       </c>
       <c r="R366" t="n">
-        <v>6808708</v>
+        <v>6808625</v>
       </c>
       <c r="S366" t="n">
         <v>10</v>
@@ -39812,7 +39807,7 @@
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>123920807</v>
+        <v>123920795</v>
       </c>
       <c r="B367" t="n">
         <v>78788</v>
@@ -39852,10 +39847,10 @@
         </is>
       </c>
       <c r="Q367" t="n">
-        <v>459115</v>
+        <v>458927</v>
       </c>
       <c r="R367" t="n">
-        <v>6808339</v>
+        <v>6808282</v>
       </c>
       <c r="S367" t="n">
         <v>10</v>
@@ -39914,7 +39909,7 @@
     </row>
     <row r="368">
       <c r="A368" t="n">
-        <v>123920691</v>
+        <v>123920799</v>
       </c>
       <c r="B368" t="n">
         <v>78788</v>
@@ -39954,10 +39949,10 @@
         </is>
       </c>
       <c r="Q368" t="n">
-        <v>459688</v>
+        <v>459007</v>
       </c>
       <c r="R368" t="n">
-        <v>6808555</v>
+        <v>6808305</v>
       </c>
       <c r="S368" t="n">
         <v>10</v>
@@ -39984,12 +39979,12 @@
       </c>
       <c r="Y368" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA368" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD368" t="b">
@@ -40009,14 +40004,14 @@
       </c>
       <c r="AX368" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="n">
-        <v>123920439</v>
+        <v>123920448</v>
       </c>
       <c r="B369" t="n">
         <v>56700</v>
@@ -40052,7 +40047,7 @@
       <c r="I369" t="inlineStr"/>
       <c r="M369" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P369" t="inlineStr">
@@ -40061,10 +40056,10 @@
         </is>
       </c>
       <c r="Q369" t="n">
-        <v>459700</v>
+        <v>458790</v>
       </c>
       <c r="R369" t="n">
-        <v>6808234</v>
+        <v>6808708</v>
       </c>
       <c r="S369" t="n">
         <v>10</v>
@@ -40091,12 +40086,12 @@
       </c>
       <c r="Y369" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA369" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD369" t="b">
@@ -40116,17 +40111,17 @@
       </c>
       <c r="AX369" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>123920316</v>
+        <v>123920807</v>
       </c>
       <c r="B370" t="n">
-        <v>79406</v>
+        <v>78788</v>
       </c>
       <c r="C370" t="inlineStr">
         <is>
@@ -40139,21 +40134,21 @@
         </is>
       </c>
       <c r="E370" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I370" t="inlineStr"/>
@@ -40163,10 +40158,10 @@
         </is>
       </c>
       <c r="Q370" t="n">
-        <v>459455</v>
+        <v>459115</v>
       </c>
       <c r="R370" t="n">
-        <v>6808627</v>
+        <v>6808339</v>
       </c>
       <c r="S370" t="n">
         <v>10</v>
@@ -40193,12 +40188,12 @@
       </c>
       <c r="Y370" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA370" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD370" t="b">
@@ -40218,14 +40213,14 @@
       </c>
       <c r="AX370" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY370" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>123920810</v>
+        <v>123920691</v>
       </c>
       <c r="B371" t="n">
         <v>78788</v>
@@ -40265,10 +40260,10 @@
         </is>
       </c>
       <c r="Q371" t="n">
-        <v>459205</v>
+        <v>459688</v>
       </c>
       <c r="R371" t="n">
-        <v>6808378</v>
+        <v>6808555</v>
       </c>
       <c r="S371" t="n">
         <v>10</v>
@@ -40295,12 +40290,12 @@
       </c>
       <c r="Y371" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA371" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD371" t="b">
@@ -40320,17 +40315,17 @@
       </c>
       <c r="AX371" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>123920826</v>
+        <v>123920439</v>
       </c>
       <c r="B372" t="n">
-        <v>78788</v>
+        <v>56700</v>
       </c>
       <c r="C372" t="inlineStr">
         <is>
@@ -40339,38 +40334,43 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E372" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I372" t="inlineStr"/>
+      <c r="M372" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P372" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q372" t="n">
-        <v>459573</v>
+        <v>459700</v>
       </c>
       <c r="R372" t="n">
-        <v>6808265</v>
+        <v>6808234</v>
       </c>
       <c r="S372" t="n">
         <v>10</v>
@@ -40422,14 +40422,14 @@
       </c>
       <c r="AX372" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY372" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>123920315</v>
+        <v>123920316</v>
       </c>
       <c r="B373" t="n">
         <v>79406</v>
@@ -40469,10 +40469,10 @@
         </is>
       </c>
       <c r="Q373" t="n">
-        <v>459450</v>
+        <v>459455</v>
       </c>
       <c r="R373" t="n">
-        <v>6808625</v>
+        <v>6808627</v>
       </c>
       <c r="S373" t="n">
         <v>10</v>
@@ -40531,7 +40531,7 @@
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>123920795</v>
+        <v>123920810</v>
       </c>
       <c r="B374" t="n">
         <v>78788</v>
@@ -40571,10 +40571,10 @@
         </is>
       </c>
       <c r="Q374" t="n">
-        <v>458927</v>
+        <v>459205</v>
       </c>
       <c r="R374" t="n">
-        <v>6808282</v>
+        <v>6808378</v>
       </c>
       <c r="S374" t="n">
         <v>10</v>
@@ -40633,7 +40633,7 @@
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>123920799</v>
+        <v>123920826</v>
       </c>
       <c r="B375" t="n">
         <v>78788</v>
@@ -40673,10 +40673,10 @@
         </is>
       </c>
       <c r="Q375" t="n">
-        <v>459007</v>
+        <v>459573</v>
       </c>
       <c r="R375" t="n">
-        <v>6808305</v>
+        <v>6808265</v>
       </c>
       <c r="S375" t="n">
         <v>10</v>
@@ -42168,10 +42168,10 @@
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>123920662</v>
+        <v>123920380</v>
       </c>
       <c r="B390" t="n">
-        <v>78788</v>
+        <v>79406</v>
       </c>
       <c r="C390" t="inlineStr">
         <is>
@@ -42184,21 +42184,21 @@
         </is>
       </c>
       <c r="E390" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I390" t="inlineStr"/>
@@ -42208,10 +42208,10 @@
         </is>
       </c>
       <c r="Q390" t="n">
-        <v>458749</v>
+        <v>459217</v>
       </c>
       <c r="R390" t="n">
-        <v>6808795</v>
+        <v>6808383</v>
       </c>
       <c r="S390" t="n">
         <v>10</v>
@@ -42238,12 +42238,12 @@
       </c>
       <c r="Y390" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA390" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD390" t="b">
@@ -42263,17 +42263,17 @@
       </c>
       <c r="AX390" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY390" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" t="n">
-        <v>123920457</v>
+        <v>123920573</v>
       </c>
       <c r="B391" t="n">
-        <v>56700</v>
+        <v>80741</v>
       </c>
       <c r="C391" t="inlineStr">
         <is>
@@ -42282,43 +42282,38 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E391" t="n">
-        <v>100138</v>
+        <v>1049</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I391" t="inlineStr"/>
-      <c r="M391" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P391" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q391" t="n">
-        <v>458767</v>
+        <v>458988</v>
       </c>
       <c r="R391" t="n">
-        <v>6808746</v>
+        <v>6808278</v>
       </c>
       <c r="S391" t="n">
         <v>10</v>
@@ -42345,12 +42340,12 @@
       </c>
       <c r="Y391" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA391" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD391" t="b">
@@ -42370,17 +42365,17 @@
       </c>
       <c r="AX391" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY391" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" t="n">
-        <v>123920336</v>
+        <v>123920452</v>
       </c>
       <c r="B392" t="n">
-        <v>79406</v>
+        <v>56700</v>
       </c>
       <c r="C392" t="inlineStr">
         <is>
@@ -42389,38 +42384,43 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E392" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I392" t="inlineStr"/>
+      <c r="M392" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P392" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q392" t="n">
-        <v>459520</v>
+        <v>459281</v>
       </c>
       <c r="R392" t="n">
-        <v>6808387</v>
+        <v>6808708</v>
       </c>
       <c r="S392" t="n">
         <v>10</v>
@@ -42447,12 +42447,12 @@
       </c>
       <c r="Y392" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA392" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD392" t="b">
@@ -42472,14 +42472,14 @@
       </c>
       <c r="AX392" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY392" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" t="n">
-        <v>123920668</v>
+        <v>123920813</v>
       </c>
       <c r="B393" t="n">
         <v>78788</v>
@@ -42519,10 +42519,10 @@
         </is>
       </c>
       <c r="Q393" t="n">
-        <v>458876</v>
+        <v>459237</v>
       </c>
       <c r="R393" t="n">
-        <v>6808749</v>
+        <v>6808364</v>
       </c>
       <c r="S393" t="n">
         <v>10</v>
@@ -42549,12 +42549,12 @@
       </c>
       <c r="Y393" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA393" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD393" t="b">
@@ -42574,17 +42574,17 @@
       </c>
       <c r="AX393" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY393" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" t="n">
-        <v>123920380</v>
+        <v>123920794</v>
       </c>
       <c r="B394" t="n">
-        <v>79406</v>
+        <v>78788</v>
       </c>
       <c r="C394" t="inlineStr">
         <is>
@@ -42597,21 +42597,21 @@
         </is>
       </c>
       <c r="E394" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I394" t="inlineStr"/>
@@ -42621,10 +42621,10 @@
         </is>
       </c>
       <c r="Q394" t="n">
-        <v>459217</v>
+        <v>458919</v>
       </c>
       <c r="R394" t="n">
-        <v>6808383</v>
+        <v>6808281</v>
       </c>
       <c r="S394" t="n">
         <v>10</v>
@@ -42676,17 +42676,17 @@
       </c>
       <c r="AX394" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY394" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" t="n">
-        <v>123920573</v>
+        <v>123920812</v>
       </c>
       <c r="B395" t="n">
-        <v>80741</v>
+        <v>78788</v>
       </c>
       <c r="C395" t="inlineStr">
         <is>
@@ -42699,21 +42699,21 @@
         </is>
       </c>
       <c r="E395" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I395" t="inlineStr"/>
@@ -42723,10 +42723,10 @@
         </is>
       </c>
       <c r="Q395" t="n">
-        <v>458988</v>
+        <v>459239</v>
       </c>
       <c r="R395" t="n">
-        <v>6808278</v>
+        <v>6808359</v>
       </c>
       <c r="S395" t="n">
         <v>10</v>
@@ -42785,10 +42785,10 @@
     </row>
     <row r="396">
       <c r="A396" t="n">
-        <v>123920452</v>
+        <v>123920662</v>
       </c>
       <c r="B396" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C396" t="inlineStr">
         <is>
@@ -42797,43 +42797,38 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E396" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I396" t="inlineStr"/>
-      <c r="M396" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P396" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q396" t="n">
-        <v>459281</v>
+        <v>458749</v>
       </c>
       <c r="R396" t="n">
-        <v>6808708</v>
+        <v>6808795</v>
       </c>
       <c r="S396" t="n">
         <v>10</v>
@@ -42892,10 +42887,10 @@
     </row>
     <row r="397">
       <c r="A397" t="n">
-        <v>123920813</v>
+        <v>123920457</v>
       </c>
       <c r="B397" t="n">
-        <v>78788</v>
+        <v>56700</v>
       </c>
       <c r="C397" t="inlineStr">
         <is>
@@ -42904,38 +42899,43 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E397" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I397" t="inlineStr"/>
+      <c r="M397" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P397" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q397" t="n">
-        <v>459237</v>
+        <v>458767</v>
       </c>
       <c r="R397" t="n">
-        <v>6808364</v>
+        <v>6808746</v>
       </c>
       <c r="S397" t="n">
         <v>10</v>
@@ -42962,12 +42962,12 @@
       </c>
       <c r="Y397" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA397" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD397" t="b">
@@ -42987,17 +42987,17 @@
       </c>
       <c r="AX397" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY397" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" t="n">
-        <v>123920794</v>
+        <v>123920336</v>
       </c>
       <c r="B398" t="n">
-        <v>78788</v>
+        <v>79406</v>
       </c>
       <c r="C398" t="inlineStr">
         <is>
@@ -43010,21 +43010,21 @@
         </is>
       </c>
       <c r="E398" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I398" t="inlineStr"/>
@@ -43034,10 +43034,10 @@
         </is>
       </c>
       <c r="Q398" t="n">
-        <v>458919</v>
+        <v>459520</v>
       </c>
       <c r="R398" t="n">
-        <v>6808281</v>
+        <v>6808387</v>
       </c>
       <c r="S398" t="n">
         <v>10</v>
@@ -43089,14 +43089,14 @@
       </c>
       <c r="AX398" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY398" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" t="n">
-        <v>123920812</v>
+        <v>123920668</v>
       </c>
       <c r="B399" t="n">
         <v>78788</v>
@@ -43136,10 +43136,10 @@
         </is>
       </c>
       <c r="Q399" t="n">
-        <v>459239</v>
+        <v>458876</v>
       </c>
       <c r="R399" t="n">
-        <v>6808359</v>
+        <v>6808749</v>
       </c>
       <c r="S399" t="n">
         <v>10</v>
@@ -43166,12 +43166,12 @@
       </c>
       <c r="Y399" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA399" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD399" t="b">
@@ -43191,7 +43191,7 @@
       </c>
       <c r="AX399" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY399" t="inlineStr"/>

--- a/artfynd/A 61324-2022 artfynd.xlsx
+++ b/artfynd/A 61324-2022 artfynd.xlsx
@@ -1798,10 +1798,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123549156</v>
+        <v>123549418</v>
       </c>
       <c r="B12" t="n">
-        <v>78788</v>
+        <v>56700</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1810,41 +1810,46 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>459240</v>
+        <v>459318</v>
       </c>
       <c r="R12" t="n">
-        <v>6808794</v>
+        <v>6808809</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1873,7 +1878,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1883,7 +1888,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Under betestall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1898,19 +1908,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123543987</v>
+        <v>123549156</v>
       </c>
       <c r="B13" t="n">
         <v>78788</v>
@@ -1950,10 +1960,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>459521</v>
+        <v>459240</v>
       </c>
       <c r="R13" t="n">
-        <v>6808918</v>
+        <v>6808794</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1985,7 +1995,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1995,7 +2005,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2022,10 +2032,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123548636</v>
+        <v>123543987</v>
       </c>
       <c r="B14" t="n">
-        <v>78524</v>
+        <v>78788</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2038,34 +2048,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>459184</v>
+        <v>459521</v>
       </c>
       <c r="R14" t="n">
-        <v>6808784</v>
+        <v>6808918</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2097,7 +2107,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2107,7 +2117,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2134,10 +2144,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123548196</v>
+        <v>123548636</v>
       </c>
       <c r="B15" t="n">
-        <v>78788</v>
+        <v>78524</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2150,34 +2160,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Andljusen, Andljusen, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>459024</v>
+        <v>459184</v>
       </c>
       <c r="R15" t="n">
-        <v>6808872</v>
+        <v>6808784</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2209,7 +2219,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2219,7 +2229,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2246,10 +2256,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123549418</v>
+        <v>123548196</v>
       </c>
       <c r="B16" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2258,46 +2268,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>459318</v>
+        <v>459024</v>
       </c>
       <c r="R16" t="n">
-        <v>6808809</v>
+        <v>6808872</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2326,7 +2331,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2336,12 +2341,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:21</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Under betestall</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2356,12 +2356,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -3824,10 +3824,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123548439</v>
+        <v>123549476</v>
       </c>
       <c r="B30" t="n">
-        <v>78788</v>
+        <v>56700</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3836,41 +3836,46 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Andljusen, Andljusen, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>459138</v>
+        <v>459369</v>
       </c>
       <c r="R30" t="n">
-        <v>6808765</v>
+        <v>6808793</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3899,7 +3904,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3909,7 +3914,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Under betestall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3924,19 +3934,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123543936</v>
+        <v>123548439</v>
       </c>
       <c r="B31" t="n">
         <v>78788</v>
@@ -3972,14 +3982,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>459520</v>
+        <v>459138</v>
       </c>
       <c r="R31" t="n">
-        <v>6808918</v>
+        <v>6808765</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4011,7 +4021,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4021,7 +4031,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4048,7 +4058,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123548548</v>
+        <v>123543936</v>
       </c>
       <c r="B32" t="n">
         <v>78788</v>
@@ -4084,14 +4094,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>459181</v>
+        <v>459520</v>
       </c>
       <c r="R32" t="n">
-        <v>6808783</v>
+        <v>6808918</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4123,7 +4133,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4133,7 +4143,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4160,7 +4170,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123549630</v>
+        <v>123548548</v>
       </c>
       <c r="B33" t="n">
         <v>78788</v>
@@ -4196,17 +4206,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>459421</v>
+        <v>459181</v>
       </c>
       <c r="R33" t="n">
-        <v>6808816</v>
+        <v>6808783</v>
       </c>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4235,7 +4245,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4245,7 +4255,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4260,22 +4270,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123549476</v>
+        <v>123549630</v>
       </c>
       <c r="B34" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4284,43 +4294,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>459369</v>
+        <v>459421</v>
       </c>
       <c r="R34" t="n">
-        <v>6808793</v>
+        <v>6808816</v>
       </c>
       <c r="S34" t="n">
         <v>9</v>
@@ -4352,7 +4357,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4362,12 +4367,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>17:24</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Under betestall</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4730,10 +4730,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123548779</v>
+        <v>123549662</v>
       </c>
       <c r="B38" t="n">
-        <v>79377</v>
+        <v>78788</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4746,37 +4746,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Andljusen, Andljusen, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>459073</v>
+        <v>459479</v>
       </c>
       <c r="R38" t="n">
-        <v>6808847</v>
+        <v>6808853</v>
       </c>
       <c r="S38" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4815,7 +4815,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4830,19 +4830,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123549662</v>
+        <v>123548763</v>
       </c>
       <c r="B39" t="n">
         <v>78788</v>
@@ -4878,17 +4878,17 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>459479</v>
+        <v>459187</v>
       </c>
       <c r="R39" t="n">
-        <v>6808853</v>
+        <v>6808828</v>
       </c>
       <c r="S39" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4927,7 +4927,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4942,19 +4942,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123548763</v>
+        <v>123549171</v>
       </c>
       <c r="B40" t="n">
         <v>78788</v>
@@ -4990,17 +4990,17 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Andljusen, Andljusen, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>459187</v>
+        <v>459253</v>
       </c>
       <c r="R40" t="n">
-        <v>6808828</v>
+        <v>6808807</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5039,7 +5039,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5054,22 +5054,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123549171</v>
+        <v>123548779</v>
       </c>
       <c r="B41" t="n">
-        <v>78788</v>
+        <v>79377</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5082,34 +5082,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>459253</v>
+        <v>459073</v>
       </c>
       <c r="R41" t="n">
-        <v>6808807</v>
+        <v>6808847</v>
       </c>
       <c r="S41" t="n">
         <v>9</v>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -10512,10 +10512,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>123574629</v>
+        <v>123574181</v>
       </c>
       <c r="B89" t="n">
-        <v>79377</v>
+        <v>78788</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10528,21 +10528,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10552,10 +10552,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>459648</v>
+        <v>459652</v>
       </c>
       <c r="R89" t="n">
-        <v>6808494</v>
+        <v>6808496</v>
       </c>
       <c r="S89" t="n">
         <v>9</v>
@@ -10587,7 +10587,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10597,7 +10597,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>På tallstammar</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10624,7 +10629,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>123574181</v>
+        <v>123573959</v>
       </c>
       <c r="B90" t="n">
         <v>78788</v>
@@ -10664,10 +10669,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>459652</v>
+        <v>459676</v>
       </c>
       <c r="R90" t="n">
-        <v>6808496</v>
+        <v>6808503</v>
       </c>
       <c r="S90" t="n">
         <v>9</v>
@@ -10699,7 +10704,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10709,7 +10714,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
@@ -10741,10 +10746,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>123573959</v>
+        <v>123575210</v>
       </c>
       <c r="B91" t="n">
-        <v>78788</v>
+        <v>78524</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10757,21 +10762,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10781,10 +10786,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>459676</v>
+        <v>459619</v>
       </c>
       <c r="R91" t="n">
-        <v>6808503</v>
+        <v>6808506</v>
       </c>
       <c r="S91" t="n">
         <v>9</v>
@@ -10816,7 +10821,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10826,12 +10831,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>13:31</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>På tallstammar</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10846,22 +10846,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>123575210</v>
+        <v>123574629</v>
       </c>
       <c r="B92" t="n">
-        <v>78524</v>
+        <v>79377</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10874,21 +10874,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10898,10 +10898,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>459619</v>
+        <v>459648</v>
       </c>
       <c r="R92" t="n">
-        <v>6808506</v>
+        <v>6808494</v>
       </c>
       <c r="S92" t="n">
         <v>9</v>
@@ -10933,7 +10933,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10943,7 +10943,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10958,22 +10958,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>123574214</v>
+        <v>123574293</v>
       </c>
       <c r="B93" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10986,21 +10986,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -11010,10 +11010,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>459645</v>
+        <v>459648</v>
       </c>
       <c r="R93" t="n">
-        <v>6808484</v>
+        <v>6808494</v>
       </c>
       <c r="S93" t="n">
         <v>9</v>
@@ -11045,7 +11045,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11055,12 +11055,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>13:38</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>På tallstammar</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11087,7 +11082,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>123574293</v>
+        <v>123565752</v>
       </c>
       <c r="B94" t="n">
         <v>78525</v>
@@ -11123,17 +11118,17 @@
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>459648</v>
+        <v>459733</v>
       </c>
       <c r="R94" t="n">
-        <v>6808494</v>
+        <v>6808745</v>
       </c>
       <c r="S94" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11162,7 +11157,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11172,7 +11167,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11187,22 +11182,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>123565752</v>
+        <v>123574214</v>
       </c>
       <c r="B95" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11215,37 +11210,37 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>459733</v>
+        <v>459645</v>
       </c>
       <c r="R95" t="n">
-        <v>6808745</v>
+        <v>6808484</v>
       </c>
       <c r="S95" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11274,7 +11269,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11284,7 +11279,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>På tallstammar</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11299,12 +11299,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
@@ -12473,7 +12473,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>123567138</v>
+        <v>123576549</v>
       </c>
       <c r="B106" t="n">
         <v>56700</v>
@@ -12517,14 +12517,14 @@
       <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>459735</v>
+        <v>459499</v>
       </c>
       <c r="R106" t="n">
-        <v>6808695</v>
+        <v>6808603</v>
       </c>
       <c r="S106" t="n">
         <v>15</v>
@@ -12556,7 +12556,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12566,7 +12566,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr">
@@ -12598,7 +12598,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>123576549</v>
+        <v>123567138</v>
       </c>
       <c r="B107" t="n">
         <v>56700</v>
@@ -12642,14 +12642,14 @@
       <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>459499</v>
+        <v>459735</v>
       </c>
       <c r="R107" t="n">
-        <v>6808603</v>
+        <v>6808695</v>
       </c>
       <c r="S107" t="n">
         <v>15</v>
@@ -12681,7 +12681,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12691,7 +12691,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr">
@@ -13448,10 +13448,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>123728918</v>
+        <v>123725898</v>
       </c>
       <c r="B114" t="n">
-        <v>79406</v>
+        <v>78788</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -13464,21 +13464,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -13488,10 +13488,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>458818</v>
+        <v>458927</v>
       </c>
       <c r="R114" t="n">
-        <v>6808502</v>
+        <v>6808307</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13550,7 +13550,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>123725898</v>
+        <v>123728287</v>
       </c>
       <c r="B115" t="n">
         <v>78788</v>
@@ -13590,10 +13590,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>458927</v>
+        <v>458826</v>
       </c>
       <c r="R115" t="n">
-        <v>6808307</v>
+        <v>6808449</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13626,6 +13626,11 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Garnlav på samtliga träd,mer eller mindre, på bilden.</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13652,10 +13657,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>123728287</v>
+        <v>123728918</v>
       </c>
       <c r="B116" t="n">
-        <v>78788</v>
+        <v>79406</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13668,21 +13673,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13692,10 +13697,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>458826</v>
+        <v>458818</v>
       </c>
       <c r="R116" t="n">
-        <v>6808449</v>
+        <v>6808502</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13728,11 +13733,6 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-04-03</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Garnlav på samtliga träd,mer eller mindre, på bilden.</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -16486,10 +16486,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>123729517</v>
+        <v>123728549</v>
       </c>
       <c r="B143" t="n">
-        <v>78788</v>
+        <v>79377</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -16502,34 +16502,34 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Andljusen, Dlr</t>
+          <t>Dyvran, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>458715</v>
+        <v>458798</v>
       </c>
       <c r="R143" t="n">
-        <v>6808620</v>
+        <v>6808499</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16562,11 +16562,6 @@
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-04-03</t>
-        </is>
-      </c>
-      <c r="AC143" t="inlineStr">
-        <is>
-          <t>Garnlav i en radie av ca 50 meter.</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16593,10 +16588,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>123728549</v>
+        <v>123729517</v>
       </c>
       <c r="B144" t="n">
-        <v>79377</v>
+        <v>78788</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -16609,34 +16604,34 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Dyvran, Dlr</t>
+          <t>Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>458798</v>
+        <v>458715</v>
       </c>
       <c r="R144" t="n">
-        <v>6808499</v>
+        <v>6808620</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16669,6 +16664,11 @@
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>Garnlav i en radie av ca 50 meter.</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16695,7 +16695,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>123723594</v>
+        <v>123727363</v>
       </c>
       <c r="B145" t="n">
         <v>78525</v>
@@ -16735,10 +16735,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>458948</v>
+        <v>458886</v>
       </c>
       <c r="R145" t="n">
-        <v>6808276</v>
+        <v>6808352</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16797,7 +16797,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>123727363</v>
+        <v>123723594</v>
       </c>
       <c r="B146" t="n">
         <v>78525</v>
@@ -16837,10 +16837,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>458886</v>
+        <v>458948</v>
       </c>
       <c r="R146" t="n">
-        <v>6808352</v>
+        <v>6808276</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -18795,7 +18795,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>123829438</v>
+        <v>123829348</v>
       </c>
       <c r="B165" t="n">
         <v>78525</v>
@@ -18835,10 +18835,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>459113</v>
+        <v>459230</v>
       </c>
       <c r="R165" t="n">
-        <v>6808380</v>
+        <v>6808362</v>
       </c>
       <c r="S165" t="n">
         <v>15</v>
@@ -18897,7 +18897,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>123829348</v>
+        <v>123829438</v>
       </c>
       <c r="B166" t="n">
         <v>78525</v>
@@ -18937,10 +18937,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>459230</v>
+        <v>459113</v>
       </c>
       <c r="R166" t="n">
-        <v>6808362</v>
+        <v>6808380</v>
       </c>
       <c r="S166" t="n">
         <v>15</v>
@@ -22149,10 +22149,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>123822912</v>
+        <v>123822771</v>
       </c>
       <c r="B197" t="n">
-        <v>57644</v>
+        <v>56700</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -22161,31 +22161,31 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
       <c r="M197" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P197" t="inlineStr">
@@ -22194,10 +22194,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>459118</v>
+        <v>459307</v>
       </c>
       <c r="R197" t="n">
-        <v>6808615</v>
+        <v>6808524</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -22229,7 +22229,7 @@
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
@@ -22239,7 +22239,7 @@
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -22266,10 +22266,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>123822771</v>
+        <v>123822912</v>
       </c>
       <c r="B198" t="n">
-        <v>56700</v>
+        <v>57644</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -22278,31 +22278,31 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
       <c r="M198" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P198" t="inlineStr">
@@ -22311,10 +22311,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>459307</v>
+        <v>459118</v>
       </c>
       <c r="R198" t="n">
-        <v>6808524</v>
+        <v>6808615</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -22346,7 +22346,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -22356,7 +22356,7 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -23764,10 +23764,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>123866513</v>
+        <v>123866301</v>
       </c>
       <c r="B212" t="n">
-        <v>78788</v>
+        <v>79377</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -23780,37 +23780,37 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>459177</v>
+        <v>459260</v>
       </c>
       <c r="R212" t="n">
-        <v>6808709</v>
+        <v>6808646</v>
       </c>
       <c r="S212" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T212" t="inlineStr">
         <is>
@@ -23854,19 +23854,19 @@
       <c r="AT212" t="inlineStr"/>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>123866301</v>
+        <v>123866613</v>
       </c>
       <c r="B213" t="n">
         <v>79377</v>
@@ -23906,13 +23906,13 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>459260</v>
+        <v>459110</v>
       </c>
       <c r="R213" t="n">
-        <v>6808646</v>
+        <v>6808718</v>
       </c>
       <c r="S213" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T213" t="inlineStr">
         <is>
@@ -23968,10 +23968,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>123866613</v>
+        <v>123866513</v>
       </c>
       <c r="B214" t="n">
-        <v>79377</v>
+        <v>78788</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -23984,37 +23984,37 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>459110</v>
+        <v>459177</v>
       </c>
       <c r="R214" t="n">
-        <v>6808718</v>
+        <v>6808709</v>
       </c>
       <c r="S214" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T214" t="inlineStr">
         <is>
@@ -24058,12 +24058,12 @@
       <c r="AT214" t="inlineStr"/>
       <c r="AW214" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX214" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
@@ -25125,10 +25125,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>123866559</v>
+        <v>123866561</v>
       </c>
       <c r="B225" t="n">
-        <v>78788</v>
+        <v>79377</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -25141,37 +25141,37 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
       <c r="P225" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>459128</v>
+        <v>459159</v>
       </c>
       <c r="R225" t="n">
-        <v>6808639</v>
+        <v>6808628</v>
       </c>
       <c r="S225" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T225" t="inlineStr">
         <is>
@@ -25201,6 +25201,11 @@
       <c r="AA225" t="inlineStr">
         <is>
           <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC225" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -25215,12 +25220,12 @@
       <c r="AT225" t="inlineStr"/>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
@@ -25334,10 +25339,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>123866561</v>
+        <v>123866559</v>
       </c>
       <c r="B227" t="n">
-        <v>79377</v>
+        <v>78788</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -25350,37 +25355,37 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
       <c r="P227" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>459159</v>
+        <v>459128</v>
       </c>
       <c r="R227" t="n">
-        <v>6808628</v>
+        <v>6808639</v>
       </c>
       <c r="S227" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T227" t="inlineStr">
         <is>
@@ -25410,11 +25415,6 @@
       <c r="AA227" t="inlineStr">
         <is>
           <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AC227" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -25429,12 +25429,12 @@
       <c r="AT227" t="inlineStr"/>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
@@ -25869,10 +25869,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>123866815</v>
+        <v>123864718</v>
       </c>
       <c r="B232" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
@@ -25885,37 +25885,37 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
       <c r="P232" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>458928</v>
+        <v>459500</v>
       </c>
       <c r="R232" t="n">
-        <v>6808783</v>
+        <v>6808604</v>
       </c>
       <c r="S232" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T232" t="inlineStr">
         <is>
@@ -25945,6 +25945,11 @@
       <c r="AA232" t="inlineStr">
         <is>
           <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC232" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -25959,22 +25964,22 @@
       <c r="AT232" t="inlineStr"/>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>123864718</v>
+        <v>123866815</v>
       </c>
       <c r="B233" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -25987,37 +25992,37 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
       <c r="P233" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>459500</v>
+        <v>458928</v>
       </c>
       <c r="R233" t="n">
-        <v>6808604</v>
+        <v>6808783</v>
       </c>
       <c r="S233" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T233" t="inlineStr">
         <is>
@@ -26047,11 +26052,6 @@
       <c r="AA233" t="inlineStr">
         <is>
           <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AC233" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -26066,12 +26066,12 @@
       <c r="AT233" t="inlineStr"/>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
@@ -26842,10 +26842,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>123864022</v>
+        <v>123866962</v>
       </c>
       <c r="B241" t="n">
-        <v>78788</v>
+        <v>79377</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -26858,34 +26858,34 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
       <c r="P241" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>459582</v>
+        <v>459041</v>
       </c>
       <c r="R241" t="n">
-        <v>6808669</v>
+        <v>6808701</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -26920,6 +26920,11 @@
           <t>2025-04-08</t>
         </is>
       </c>
+      <c r="AC241" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
+        </is>
+      </c>
       <c r="AD241" t="b">
         <v>0</v>
       </c>
@@ -26932,19 +26937,19 @@
       <c r="AT241" t="inlineStr"/>
       <c r="AW241" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX241" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>123864392</v>
+        <v>123864022</v>
       </c>
       <c r="B242" t="n">
         <v>78788</v>
@@ -26980,14 +26985,14 @@
       <c r="I242" t="inlineStr"/>
       <c r="P242" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>459501</v>
+        <v>459582</v>
       </c>
       <c r="R242" t="n">
-        <v>6808620</v>
+        <v>6808669</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -27034,22 +27039,22 @@
       <c r="AT242" t="inlineStr"/>
       <c r="AW242" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX242" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>123866962</v>
+        <v>123864392</v>
       </c>
       <c r="B243" t="n">
-        <v>79377</v>
+        <v>78788</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
@@ -27062,34 +27067,34 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
       <c r="P243" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>459041</v>
+        <v>459501</v>
       </c>
       <c r="R243" t="n">
-        <v>6808701</v>
+        <v>6808620</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -27124,11 +27129,6 @@
           <t>2025-04-08</t>
         </is>
       </c>
-      <c r="AC243" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
-        </is>
-      </c>
       <c r="AD243" t="b">
         <v>0</v>
       </c>
@@ -27141,12 +27141,12 @@
       <c r="AT243" t="inlineStr"/>
       <c r="AW243" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
@@ -42785,10 +42785,10 @@
     </row>
     <row r="396">
       <c r="A396" t="n">
-        <v>123920662</v>
+        <v>123866170</v>
       </c>
       <c r="B396" t="n">
-        <v>78788</v>
+        <v>56700</v>
       </c>
       <c r="C396" t="inlineStr">
         <is>
@@ -42797,38 +42797,46 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E396" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I396" t="inlineStr"/>
+      <c r="K396" t="inlineStr"/>
+      <c r="L396" t="inlineStr"/>
+      <c r="M396" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N396" t="inlineStr"/>
       <c r="P396" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q396" t="n">
-        <v>458749</v>
+        <v>459236</v>
       </c>
       <c r="R396" t="n">
-        <v>6808795</v>
+        <v>6808707</v>
       </c>
       <c r="S396" t="n">
         <v>10</v>
@@ -42863,6 +42871,11 @@
           <t>2025-04-08</t>
         </is>
       </c>
+      <c r="AC396" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
+        </is>
+      </c>
       <c r="AD396" t="b">
         <v>0</v>
       </c>
@@ -42875,22 +42888,22 @@
       <c r="AT396" t="inlineStr"/>
       <c r="AW396" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX396" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY396" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" t="n">
-        <v>123920457</v>
+        <v>123920662</v>
       </c>
       <c r="B397" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C397" t="inlineStr">
         <is>
@@ -42899,43 +42912,38 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E397" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I397" t="inlineStr"/>
-      <c r="M397" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P397" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q397" t="n">
-        <v>458767</v>
+        <v>458749</v>
       </c>
       <c r="R397" t="n">
-        <v>6808746</v>
+        <v>6808795</v>
       </c>
       <c r="S397" t="n">
         <v>10</v>
@@ -42994,10 +43002,10 @@
     </row>
     <row r="398">
       <c r="A398" t="n">
-        <v>123920336</v>
+        <v>123920457</v>
       </c>
       <c r="B398" t="n">
-        <v>79406</v>
+        <v>56700</v>
       </c>
       <c r="C398" t="inlineStr">
         <is>
@@ -43006,38 +43014,43 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E398" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I398" t="inlineStr"/>
+      <c r="M398" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P398" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q398" t="n">
-        <v>459520</v>
+        <v>458767</v>
       </c>
       <c r="R398" t="n">
-        <v>6808387</v>
+        <v>6808746</v>
       </c>
       <c r="S398" t="n">
         <v>10</v>
@@ -43064,12 +43077,12 @@
       </c>
       <c r="Y398" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA398" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD398" t="b">
@@ -43089,17 +43102,17 @@
       </c>
       <c r="AX398" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY398" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" t="n">
-        <v>123920668</v>
+        <v>123920336</v>
       </c>
       <c r="B399" t="n">
-        <v>78788</v>
+        <v>79406</v>
       </c>
       <c r="C399" t="inlineStr">
         <is>
@@ -43112,21 +43125,21 @@
         </is>
       </c>
       <c r="E399" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I399" t="inlineStr"/>
@@ -43136,10 +43149,10 @@
         </is>
       </c>
       <c r="Q399" t="n">
-        <v>458876</v>
+        <v>459520</v>
       </c>
       <c r="R399" t="n">
-        <v>6808749</v>
+        <v>6808387</v>
       </c>
       <c r="S399" t="n">
         <v>10</v>
@@ -43166,12 +43179,12 @@
       </c>
       <c r="Y399" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA399" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD399" t="b">
@@ -43191,17 +43204,17 @@
       </c>
       <c r="AX399" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" t="n">
-        <v>123866170</v>
+        <v>123920668</v>
       </c>
       <c r="B400" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C400" t="inlineStr">
         <is>
@@ -43210,46 +43223,38 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E400" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I400" t="inlineStr"/>
-      <c r="K400" t="inlineStr"/>
-      <c r="L400" t="inlineStr"/>
-      <c r="M400" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N400" t="inlineStr"/>
       <c r="P400" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q400" t="n">
-        <v>459236</v>
+        <v>458876</v>
       </c>
       <c r="R400" t="n">
-        <v>6808707</v>
+        <v>6808749</v>
       </c>
       <c r="S400" t="n">
         <v>10</v>
@@ -43284,11 +43289,6 @@
           <t>2025-04-08</t>
         </is>
       </c>
-      <c r="AC400" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
-        </is>
-      </c>
       <c r="AD400" t="b">
         <v>0</v>
       </c>
@@ -43301,12 +43301,12 @@
       <c r="AT400" t="inlineStr"/>
       <c r="AW400" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX400" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY400" t="inlineStr"/>

--- a/artfynd/A 61324-2022 artfynd.xlsx
+++ b/artfynd/A 61324-2022 artfynd.xlsx
@@ -5066,10 +5066,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123548209</v>
+        <v>123548779</v>
       </c>
       <c r="B41" t="n">
-        <v>78788</v>
+        <v>79377</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5082,21 +5082,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>459014</v>
+        <v>459073</v>
       </c>
       <c r="R41" t="n">
-        <v>6808874</v>
+        <v>6808847</v>
       </c>
       <c r="S41" t="n">
         <v>9</v>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5178,10 +5178,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123548779</v>
+        <v>123548209</v>
       </c>
       <c r="B42" t="n">
-        <v>79377</v>
+        <v>78788</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5194,21 +5194,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5218,10 +5218,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>459073</v>
+        <v>459014</v>
       </c>
       <c r="R42" t="n">
-        <v>6808847</v>
+        <v>6808874</v>
       </c>
       <c r="S42" t="n">
         <v>9</v>
@@ -5253,7 +5253,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5263,7 +5263,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6985,10 +6985,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123577141</v>
+        <v>123573526</v>
       </c>
       <c r="B58" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7001,21 +7001,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7025,10 +7025,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>459462</v>
+        <v>459731</v>
       </c>
       <c r="R58" t="n">
-        <v>6808627</v>
+        <v>6808508</v>
       </c>
       <c r="S58" t="n">
         <v>9</v>
@@ -7060,7 +7060,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7070,7 +7070,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>På tallstammar</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7097,10 +7102,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123573526</v>
+        <v>123577141</v>
       </c>
       <c r="B59" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7113,21 +7118,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7137,10 +7142,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>459731</v>
+        <v>459462</v>
       </c>
       <c r="R59" t="n">
-        <v>6808508</v>
+        <v>6808627</v>
       </c>
       <c r="S59" t="n">
         <v>9</v>
@@ -7172,7 +7177,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7182,12 +7187,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>På tallstammar</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7901,10 +7901,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123567883</v>
+        <v>123573768</v>
       </c>
       <c r="B66" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7917,34 +7917,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>459673</v>
+        <v>459699</v>
       </c>
       <c r="R66" t="n">
-        <v>6808740</v>
+        <v>6808517</v>
       </c>
       <c r="S66" t="n">
         <v>9</v>
@@ -7976,7 +7976,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7986,7 +7986,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>På tallstammar</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8001,22 +8006,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123577958</v>
+        <v>123576612</v>
       </c>
       <c r="B67" t="n">
-        <v>79377</v>
+        <v>78788</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8029,21 +8034,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8053,13 +8058,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>459571</v>
+        <v>459480</v>
       </c>
       <c r="R67" t="n">
-        <v>6808546</v>
+        <v>6808666</v>
       </c>
       <c r="S67" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8088,7 +8093,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8098,7 +8103,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8113,19 +8118,19 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123573768</v>
+        <v>123575244</v>
       </c>
       <c r="B68" t="n">
         <v>78788</v>
@@ -8165,13 +8170,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>459699</v>
+        <v>459576</v>
       </c>
       <c r="R68" t="n">
-        <v>6808517</v>
+        <v>6808422</v>
       </c>
       <c r="S68" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8200,7 +8205,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8210,12 +8215,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:27</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>På tallstammar</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8230,22 +8230,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123576612</v>
+        <v>123567883</v>
       </c>
       <c r="B69" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8258,37 +8258,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>459480</v>
+        <v>459673</v>
       </c>
       <c r="R69" t="n">
-        <v>6808666</v>
+        <v>6808740</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8317,7 +8317,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8327,7 +8327,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8342,22 +8342,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123575244</v>
+        <v>123577958</v>
       </c>
       <c r="B70" t="n">
-        <v>78788</v>
+        <v>79377</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8370,21 +8370,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>459576</v>
+        <v>459571</v>
       </c>
       <c r="R70" t="n">
-        <v>6808422</v>
+        <v>6808546</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8439,7 +8439,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8454,22 +8454,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123566457</v>
+        <v>123576740</v>
       </c>
       <c r="B71" t="n">
-        <v>78788</v>
+        <v>79377</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8482,34 +8482,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>459669</v>
+        <v>459565</v>
       </c>
       <c r="R71" t="n">
-        <v>6808772</v>
+        <v>6808543</v>
       </c>
       <c r="S71" t="n">
         <v>12</v>
@@ -8541,7 +8541,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8551,7 +8551,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8578,10 +8578,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123576740</v>
+        <v>123566457</v>
       </c>
       <c r="B72" t="n">
-        <v>79377</v>
+        <v>78788</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8594,34 +8594,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>459565</v>
+        <v>459669</v>
       </c>
       <c r="R72" t="n">
-        <v>6808543</v>
+        <v>6808772</v>
       </c>
       <c r="S72" t="n">
         <v>12</v>
@@ -8653,7 +8653,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8663,7 +8663,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9830,10 +9830,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>123577066</v>
+        <v>123576585</v>
       </c>
       <c r="B83" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9842,33 +9842,28 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Härkämäck, Härkämäck, Dlr</t>
@@ -9881,7 +9876,7 @@
         <v>6808543</v>
       </c>
       <c r="S83" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9910,7 +9905,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9920,7 +9915,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9947,7 +9942,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>123576585</v>
+        <v>123575052</v>
       </c>
       <c r="B84" t="n">
         <v>78788</v>
@@ -9987,13 +9982,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>459565</v>
+        <v>459600</v>
       </c>
       <c r="R84" t="n">
-        <v>6808543</v>
+        <v>6808513</v>
       </c>
       <c r="S84" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10022,7 +10017,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10032,7 +10027,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10059,10 +10054,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>123575052</v>
+        <v>123577066</v>
       </c>
       <c r="B85" t="n">
-        <v>78788</v>
+        <v>56700</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10071,41 +10066,46 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>459600</v>
+        <v>459565</v>
       </c>
       <c r="R85" t="n">
-        <v>6808513</v>
+        <v>6808543</v>
       </c>
       <c r="S85" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10134,7 +10134,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10144,7 +10144,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10395,10 +10395,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>123566093</v>
+        <v>123575672</v>
       </c>
       <c r="B88" t="n">
-        <v>78525</v>
+        <v>78524</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10411,37 +10411,37 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>459675</v>
+        <v>459612</v>
       </c>
       <c r="R88" t="n">
-        <v>6808804</v>
+        <v>6808443</v>
       </c>
       <c r="S88" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10470,7 +10470,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10480,7 +10480,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10495,19 +10495,19 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>123575648</v>
+        <v>123566093</v>
       </c>
       <c r="B89" t="n">
         <v>78525</v>
@@ -10543,17 +10543,17 @@
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>459612</v>
+        <v>459675</v>
       </c>
       <c r="R89" t="n">
-        <v>6808443</v>
+        <v>6808804</v>
       </c>
       <c r="S89" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10582,7 +10582,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10592,7 +10592,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10607,22 +10607,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>123575672</v>
+        <v>123575648</v>
       </c>
       <c r="B90" t="n">
-        <v>78524</v>
+        <v>78525</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10635,21 +10635,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10731,10 +10731,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>123577149</v>
+        <v>123566816</v>
       </c>
       <c r="B91" t="n">
-        <v>78525</v>
+        <v>79870</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10747,37 +10747,37 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>459571</v>
+        <v>459735</v>
       </c>
       <c r="R91" t="n">
-        <v>6808546</v>
+        <v>6808695</v>
       </c>
       <c r="S91" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10806,7 +10806,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10816,7 +10816,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10831,22 +10831,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>123566816</v>
+        <v>123565665</v>
       </c>
       <c r="B92" t="n">
-        <v>79870</v>
+        <v>78524</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10859,21 +10859,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10883,10 +10883,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>459735</v>
+        <v>459733</v>
       </c>
       <c r="R92" t="n">
-        <v>6808695</v>
+        <v>6808745</v>
       </c>
       <c r="S92" t="n">
         <v>15</v>
@@ -10918,7 +10918,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10928,7 +10928,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10955,10 +10955,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>123565665</v>
+        <v>123576648</v>
       </c>
       <c r="B93" t="n">
-        <v>78524</v>
+        <v>78788</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10971,37 +10971,37 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>459733</v>
+        <v>459471</v>
       </c>
       <c r="R93" t="n">
-        <v>6808745</v>
+        <v>6808574</v>
       </c>
       <c r="S93" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11030,7 +11030,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11040,7 +11040,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>På tallstammar</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11055,19 +11060,19 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>123576648</v>
+        <v>123575056</v>
       </c>
       <c r="B94" t="n">
         <v>78788</v>
@@ -11107,10 +11112,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>459471</v>
+        <v>459617</v>
       </c>
       <c r="R94" t="n">
-        <v>6808574</v>
+        <v>6808490</v>
       </c>
       <c r="S94" t="n">
         <v>9</v>
@@ -11142,7 +11147,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11152,7 +11157,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
@@ -11184,10 +11189,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>123575056</v>
+        <v>123577149</v>
       </c>
       <c r="B95" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11200,21 +11205,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -11224,13 +11229,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>459617</v>
+        <v>459571</v>
       </c>
       <c r="R95" t="n">
-        <v>6808490</v>
+        <v>6808546</v>
       </c>
       <c r="S95" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11259,7 +11264,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11269,12 +11274,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>13:55</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>På tallstammar</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11289,12 +11289,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
@@ -12469,10 +12469,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>123577240</v>
+        <v>123549184</v>
       </c>
       <c r="B106" t="n">
-        <v>78788</v>
+        <v>56700</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12481,41 +12481,49 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>459433</v>
+        <v>459240</v>
       </c>
       <c r="R106" t="n">
-        <v>6808657</v>
+        <v>6808793</v>
       </c>
       <c r="S106" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12539,27 +12547,27 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>På tallstammar flera</t>
+          <t>Under betestall</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12574,22 +12582,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>123549184</v>
+        <v>123577240</v>
       </c>
       <c r="B107" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12598,49 +12606,41 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>459240</v>
+        <v>459433</v>
       </c>
       <c r="R107" t="n">
-        <v>6808793</v>
+        <v>6808657</v>
       </c>
       <c r="S107" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12664,27 +12664,27 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>Under betestall</t>
+          <t>På tallstammar flera</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12699,12 +12699,12 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
@@ -18158,10 +18158,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>123828917</v>
+        <v>123829719</v>
       </c>
       <c r="B159" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -18174,21 +18174,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -18198,10 +18198,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>459456</v>
+        <v>458966</v>
       </c>
       <c r="R159" t="n">
-        <v>6808405</v>
+        <v>6808279</v>
       </c>
       <c r="S159" t="n">
         <v>15</v>
@@ -18260,10 +18260,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>123829719</v>
+        <v>123828917</v>
       </c>
       <c r="B160" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -18276,21 +18276,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -18300,10 +18300,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>458966</v>
+        <v>459456</v>
       </c>
       <c r="R160" t="n">
-        <v>6808279</v>
+        <v>6808405</v>
       </c>
       <c r="S160" t="n">
         <v>15</v>
@@ -18362,10 +18362,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>123826696</v>
+        <v>123829348</v>
       </c>
       <c r="B161" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -18378,37 +18378,37 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Andljusen, Andljusen, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>458878</v>
+        <v>459230</v>
       </c>
       <c r="R161" t="n">
-        <v>6808805</v>
+        <v>6808362</v>
       </c>
       <c r="S161" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -18435,19 +18435,9 @@
           <t>2025-04-07</t>
         </is>
       </c>
-      <c r="Z161" t="inlineStr">
-        <is>
-          <t>11:53</t>
-        </is>
-      </c>
       <c r="AA161" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AB161" t="inlineStr">
-        <is>
-          <t>11:53</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -18462,22 +18452,22 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>123829348</v>
+        <v>123826696</v>
       </c>
       <c r="B162" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -18490,37 +18480,37 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>459230</v>
+        <v>458878</v>
       </c>
       <c r="R162" t="n">
-        <v>6808362</v>
+        <v>6808805</v>
       </c>
       <c r="S162" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -18547,9 +18537,19 @@
           <t>2025-04-07</t>
         </is>
       </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
       <c r="AA162" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -18564,12 +18564,12 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
@@ -19417,10 +19417,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>123829390</v>
+        <v>123827249</v>
       </c>
       <c r="B171" t="n">
-        <v>78525</v>
+        <v>78172</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -19433,37 +19433,37 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>459134</v>
+        <v>458738</v>
       </c>
       <c r="R171" t="n">
-        <v>6808361</v>
+        <v>6808608</v>
       </c>
       <c r="S171" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -19507,22 +19507,22 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>123827249</v>
+        <v>123826946</v>
       </c>
       <c r="B172" t="n">
-        <v>78172</v>
+        <v>78788</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -19535,21 +19535,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -19559,10 +19559,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>458738</v>
+        <v>458734</v>
       </c>
       <c r="R172" t="n">
-        <v>6808608</v>
+        <v>6808688</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19592,9 +19592,19 @@
           <t>2025-04-07</t>
         </is>
       </c>
+      <c r="Z172" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
       <c r="AA172" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AB172" t="inlineStr">
+        <is>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -19621,10 +19631,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>123826946</v>
+        <v>123829390</v>
       </c>
       <c r="B173" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -19637,37 +19647,37 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Andljusen, Andljusen, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>458734</v>
+        <v>459134</v>
       </c>
       <c r="R173" t="n">
-        <v>6808688</v>
+        <v>6808361</v>
       </c>
       <c r="S173" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -19694,19 +19704,9 @@
           <t>2025-04-07</t>
         </is>
       </c>
-      <c r="Z173" t="inlineStr">
-        <is>
-          <t>11:53</t>
-        </is>
-      </c>
       <c r="AA173" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AB173" t="inlineStr">
-        <is>
-          <t>11:53</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -19721,12 +19721,12 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
@@ -21226,10 +21226,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>123829753</v>
+        <v>123826479</v>
       </c>
       <c r="B188" t="n">
-        <v>78788</v>
+        <v>79377</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -21242,37 +21242,37 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>458928</v>
+        <v>458964</v>
       </c>
       <c r="R188" t="n">
-        <v>6808259</v>
+        <v>6808848</v>
       </c>
       <c r="S188" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -21299,9 +21299,19 @@
           <t>2025-04-07</t>
         </is>
       </c>
+      <c r="Z188" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
       <c r="AA188" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AB188" t="inlineStr">
+        <is>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -21316,22 +21326,22 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>123826471</v>
+        <v>123829753</v>
       </c>
       <c r="B189" t="n">
-        <v>79406</v>
+        <v>78788</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -21344,37 +21354,37 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Andljusen, Andljusen, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>458964</v>
+        <v>458928</v>
       </c>
       <c r="R189" t="n">
-        <v>6808848</v>
+        <v>6808259</v>
       </c>
       <c r="S189" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -21401,19 +21411,9 @@
           <t>2025-04-07</t>
         </is>
       </c>
-      <c r="Z189" t="inlineStr">
-        <is>
-          <t>11:53</t>
-        </is>
-      </c>
       <c r="AA189" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AB189" t="inlineStr">
-        <is>
-          <t>11:53</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -21428,22 +21428,22 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>123827168</v>
+        <v>123826471</v>
       </c>
       <c r="B190" t="n">
-        <v>78788</v>
+        <v>79406</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -21456,37 +21456,37 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>459733</v>
+        <v>458964</v>
       </c>
       <c r="R190" t="n">
-        <v>6808263</v>
+        <v>6808848</v>
       </c>
       <c r="S190" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T190" t="inlineStr">
         <is>
@@ -21513,9 +21513,19 @@
           <t>2025-04-07</t>
         </is>
       </c>
+      <c r="Z190" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
       <c r="AA190" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AB190" t="inlineStr">
+        <is>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -21530,22 +21540,22 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>123826479</v>
+        <v>123827168</v>
       </c>
       <c r="B191" t="n">
-        <v>79377</v>
+        <v>78788</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -21558,37 +21568,37 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Andljusen, Andljusen, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>458964</v>
+        <v>459733</v>
       </c>
       <c r="R191" t="n">
-        <v>6808848</v>
+        <v>6808263</v>
       </c>
       <c r="S191" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T191" t="inlineStr">
         <is>
@@ -21615,19 +21625,9 @@
           <t>2025-04-07</t>
         </is>
       </c>
-      <c r="Z191" t="inlineStr">
-        <is>
-          <t>11:53</t>
-        </is>
-      </c>
       <c r="AA191" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AB191" t="inlineStr">
-        <is>
-          <t>11:53</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -21642,12 +21642,12 @@
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
@@ -23993,10 +23993,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>123866998</v>
+        <v>123864080</v>
       </c>
       <c r="B214" t="n">
-        <v>79377</v>
+        <v>77716</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -24009,21 +24009,21 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>229821</v>
+        <v>6487</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
@@ -24033,10 +24033,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>458925</v>
+        <v>459555</v>
       </c>
       <c r="R214" t="n">
-        <v>6808789</v>
+        <v>6808660</v>
       </c>
       <c r="S214" t="n">
         <v>20</v>
@@ -24095,10 +24095,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>123864015</v>
+        <v>123864326</v>
       </c>
       <c r="B215" t="n">
-        <v>79377</v>
+        <v>78433</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -24111,21 +24111,21 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
@@ -24135,13 +24135,13 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>459594</v>
+        <v>459507</v>
       </c>
       <c r="R215" t="n">
-        <v>6808664</v>
+        <v>6808603</v>
       </c>
       <c r="S215" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T215" t="inlineStr">
         <is>
@@ -24197,10 +24197,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>123864080</v>
+        <v>123866606</v>
       </c>
       <c r="B216" t="n">
-        <v>77716</v>
+        <v>56700</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -24209,41 +24209,46 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>6487</v>
+        <v>100138</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P216" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>459555</v>
+        <v>459103</v>
       </c>
       <c r="R216" t="n">
-        <v>6808660</v>
+        <v>6808786</v>
       </c>
       <c r="S216" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T216" t="inlineStr">
         <is>
@@ -24287,22 +24292,22 @@
       <c r="AT216" t="inlineStr"/>
       <c r="AW216" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX216" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>123864326</v>
+        <v>123869316</v>
       </c>
       <c r="B217" t="n">
-        <v>78433</v>
+        <v>56700</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -24311,38 +24316,43 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P217" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>459507</v>
+        <v>459292</v>
       </c>
       <c r="R217" t="n">
-        <v>6808603</v>
+        <v>6808848</v>
       </c>
       <c r="S217" t="n">
         <v>20</v>
@@ -24389,22 +24399,22 @@
       <c r="AT217" t="inlineStr"/>
       <c r="AW217" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX217" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>123866606</v>
+        <v>123866998</v>
       </c>
       <c r="B218" t="n">
-        <v>56700</v>
+        <v>79377</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -24413,46 +24423,41 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
-      <c r="M218" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P218" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>459103</v>
+        <v>458925</v>
       </c>
       <c r="R218" t="n">
-        <v>6808786</v>
+        <v>6808789</v>
       </c>
       <c r="S218" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T218" t="inlineStr">
         <is>
@@ -24496,22 +24501,22 @@
       <c r="AT218" t="inlineStr"/>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>123869316</v>
+        <v>123864015</v>
       </c>
       <c r="B219" t="n">
-        <v>56700</v>
+        <v>79377</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -24520,46 +24525,41 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
-      <c r="M219" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P219" t="inlineStr">
         <is>
-          <t>Andljusen, Andljusen, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>459292</v>
+        <v>459594</v>
       </c>
       <c r="R219" t="n">
-        <v>6808848</v>
+        <v>6808664</v>
       </c>
       <c r="S219" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T219" t="inlineStr">
         <is>
@@ -24603,12 +24603,12 @@
       <c r="AT219" t="inlineStr"/>
       <c r="AW219" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
@@ -27260,10 +27260,10 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>123864392</v>
+        <v>123866153</v>
       </c>
       <c r="B245" t="n">
-        <v>78788</v>
+        <v>56700</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -27272,41 +27272,51 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P245" t="inlineStr">
         <is>
           <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>459501</v>
+        <v>459211</v>
       </c>
       <c r="R245" t="n">
-        <v>6808620</v>
+        <v>6808724</v>
       </c>
       <c r="S245" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T245" t="inlineStr">
         <is>
@@ -27362,7 +27372,7 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>123866815</v>
+        <v>123864392</v>
       </c>
       <c r="B246" t="n">
         <v>78788</v>
@@ -27402,13 +27412,13 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>458928</v>
+        <v>459501</v>
       </c>
       <c r="R246" t="n">
-        <v>6808783</v>
+        <v>6808620</v>
       </c>
       <c r="S246" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T246" t="inlineStr">
         <is>
@@ -27464,10 +27474,10 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>123866153</v>
+        <v>123866815</v>
       </c>
       <c r="B247" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
@@ -27476,48 +27486,38 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E247" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
-      <c r="L247" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M247" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P247" t="inlineStr">
         <is>
           <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>459211</v>
+        <v>458928</v>
       </c>
       <c r="R247" t="n">
-        <v>6808724</v>
+        <v>6808783</v>
       </c>
       <c r="S247" t="n">
         <v>15</v>
@@ -27576,10 +27576,10 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>123865679</v>
+        <v>123869911</v>
       </c>
       <c r="B248" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
@@ -27592,37 +27592,37 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
       <c r="P248" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>459324</v>
+        <v>459707</v>
       </c>
       <c r="R248" t="n">
-        <v>6808728</v>
+        <v>6808760</v>
       </c>
       <c r="S248" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T248" t="inlineStr">
         <is>
@@ -27678,7 +27678,7 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>123868751</v>
+        <v>123865679</v>
       </c>
       <c r="B249" t="n">
         <v>78788</v>
@@ -27714,14 +27714,14 @@
       <c r="I249" t="inlineStr"/>
       <c r="P249" t="inlineStr">
         <is>
-          <t>Andljusen, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>459228</v>
+        <v>459324</v>
       </c>
       <c r="R249" t="n">
-        <v>6808886</v>
+        <v>6808728</v>
       </c>
       <c r="S249" t="n">
         <v>15</v>
@@ -27780,7 +27780,7 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>123865853</v>
+        <v>123868751</v>
       </c>
       <c r="B250" t="n">
         <v>78788</v>
@@ -27816,17 +27816,17 @@
       <c r="I250" t="inlineStr"/>
       <c r="P250" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>459295</v>
+        <v>459228</v>
       </c>
       <c r="R250" t="n">
-        <v>6808799</v>
+        <v>6808886</v>
       </c>
       <c r="S250" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T250" t="inlineStr">
         <is>
@@ -27870,22 +27870,22 @@
       <c r="AT250" t="inlineStr"/>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>123865793</v>
+        <v>123865853</v>
       </c>
       <c r="B251" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>
@@ -27894,46 +27894,41 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
-      <c r="M251" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P251" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>459341</v>
+        <v>459295</v>
       </c>
       <c r="R251" t="n">
-        <v>6808761</v>
+        <v>6808799</v>
       </c>
       <c r="S251" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T251" t="inlineStr">
         <is>
@@ -27977,19 +27972,19 @@
       <c r="AT251" t="inlineStr"/>
       <c r="AW251" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>123865783</v>
+        <v>123865793</v>
       </c>
       <c r="B252" t="n">
         <v>56700</v>
@@ -28023,19 +28018,24 @@
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P252" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>459326</v>
+        <v>459341</v>
       </c>
       <c r="R252" t="n">
-        <v>6808793</v>
+        <v>6808761</v>
       </c>
       <c r="S252" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T252" t="inlineStr">
         <is>
@@ -28065,11 +28065,6 @@
       <c r="AA252" t="inlineStr">
         <is>
           <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AC252" t="inlineStr">
-        <is>
-          <t>Nyare spillning.</t>
         </is>
       </c>
       <c r="AD252" t="b">
@@ -28084,22 +28079,22 @@
       <c r="AT252" t="inlineStr"/>
       <c r="AW252" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>123869911</v>
+        <v>123865783</v>
       </c>
       <c r="B253" t="n">
-        <v>78525</v>
+        <v>56700</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
@@ -28108,25 +28103,25 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -28136,13 +28131,13 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>459707</v>
+        <v>459326</v>
       </c>
       <c r="R253" t="n">
-        <v>6808760</v>
+        <v>6808793</v>
       </c>
       <c r="S253" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T253" t="inlineStr">
         <is>
@@ -28172,6 +28167,11 @@
       <c r="AA253" t="inlineStr">
         <is>
           <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC253" t="inlineStr">
+        <is>
+          <t>Nyare spillning.</t>
         </is>
       </c>
       <c r="AD253" t="b">
@@ -28186,12 +28186,12 @@
       <c r="AT253" t="inlineStr"/>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
@@ -31079,7 +31079,7 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>123920459</v>
+        <v>123920451</v>
       </c>
       <c r="B282" t="n">
         <v>56700</v>
@@ -31115,7 +31115,7 @@
       <c r="I282" t="inlineStr"/>
       <c r="M282" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P282" t="inlineStr">
@@ -31124,7 +31124,7 @@
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>459135</v>
+        <v>459257</v>
       </c>
       <c r="R282" t="n">
         <v>6808663</v>
@@ -31186,10 +31186,10 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>123920451</v>
+        <v>123920388</v>
       </c>
       <c r="B283" t="n">
-        <v>56700</v>
+        <v>79377</v>
       </c>
       <c r="C283" t="inlineStr">
         <is>
@@ -31198,33 +31198,28 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E283" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I283" t="inlineStr"/>
-      <c r="M283" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P283" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
@@ -31234,7 +31229,7 @@
         <v>459257</v>
       </c>
       <c r="R283" t="n">
-        <v>6808663</v>
+        <v>6808639</v>
       </c>
       <c r="S283" t="n">
         <v>10</v>
@@ -31293,10 +31288,10 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>123920388</v>
+        <v>123920459</v>
       </c>
       <c r="B284" t="n">
-        <v>79377</v>
+        <v>56700</v>
       </c>
       <c r="C284" t="inlineStr">
         <is>
@@ -31305,38 +31300,43 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E284" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I284" t="inlineStr"/>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P284" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>459257</v>
+        <v>459135</v>
       </c>
       <c r="R284" t="n">
-        <v>6808639</v>
+        <v>6808663</v>
       </c>
       <c r="S284" t="n">
         <v>10</v>
@@ -31395,10 +31395,10 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>123920820</v>
+        <v>123920550</v>
       </c>
       <c r="B285" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
@@ -31411,21 +31411,21 @@
         </is>
       </c>
       <c r="E285" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I285" t="inlineStr"/>
@@ -31435,10 +31435,10 @@
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>459519</v>
+        <v>459448</v>
       </c>
       <c r="R285" t="n">
-        <v>6808390</v>
+        <v>6808388</v>
       </c>
       <c r="S285" t="n">
         <v>10</v>
@@ -31497,7 +31497,7 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>123920679</v>
+        <v>123920820</v>
       </c>
       <c r="B286" t="n">
         <v>78788</v>
@@ -31537,10 +31537,10 @@
         </is>
       </c>
       <c r="Q286" t="n">
-        <v>459257</v>
+        <v>459519</v>
       </c>
       <c r="R286" t="n">
-        <v>6808663</v>
+        <v>6808390</v>
       </c>
       <c r="S286" t="n">
         <v>10</v>
@@ -31567,12 +31567,12 @@
       </c>
       <c r="Y286" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA286" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD286" t="b">
@@ -31592,17 +31592,17 @@
       </c>
       <c r="AX286" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>123920576</v>
+        <v>123920679</v>
       </c>
       <c r="B287" t="n">
-        <v>80741</v>
+        <v>78788</v>
       </c>
       <c r="C287" t="inlineStr">
         <is>
@@ -31615,21 +31615,21 @@
         </is>
       </c>
       <c r="E287" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I287" t="inlineStr"/>
@@ -31639,10 +31639,10 @@
         </is>
       </c>
       <c r="Q287" t="n">
-        <v>459654</v>
+        <v>459257</v>
       </c>
       <c r="R287" t="n">
-        <v>6808298</v>
+        <v>6808663</v>
       </c>
       <c r="S287" t="n">
         <v>10</v>
@@ -31669,12 +31669,12 @@
       </c>
       <c r="Y287" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA287" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD287" t="b">
@@ -31694,17 +31694,17 @@
       </c>
       <c r="AX287" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>123920830</v>
+        <v>123920576</v>
       </c>
       <c r="B288" t="n">
-        <v>78788</v>
+        <v>80741</v>
       </c>
       <c r="C288" t="inlineStr">
         <is>
@@ -31717,21 +31717,21 @@
         </is>
       </c>
       <c r="E288" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I288" t="inlineStr"/>
@@ -31741,10 +31741,10 @@
         </is>
       </c>
       <c r="Q288" t="n">
-        <v>459650</v>
+        <v>459654</v>
       </c>
       <c r="R288" t="n">
-        <v>6808252</v>
+        <v>6808298</v>
       </c>
       <c r="S288" t="n">
         <v>10</v>
@@ -31803,10 +31803,10 @@
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>123920312</v>
+        <v>123920830</v>
       </c>
       <c r="B289" t="n">
-        <v>79406</v>
+        <v>78788</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
@@ -31819,21 +31819,21 @@
         </is>
       </c>
       <c r="E289" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I289" t="inlineStr"/>
@@ -31843,10 +31843,10 @@
         </is>
       </c>
       <c r="Q289" t="n">
-        <v>459317</v>
+        <v>459650</v>
       </c>
       <c r="R289" t="n">
-        <v>6808694</v>
+        <v>6808252</v>
       </c>
       <c r="S289" t="n">
         <v>10</v>
@@ -31873,12 +31873,12 @@
       </c>
       <c r="Y289" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA289" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD289" t="b">
@@ -31898,17 +31898,17 @@
       </c>
       <c r="AX289" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>123920597</v>
+        <v>123920312</v>
       </c>
       <c r="B290" t="n">
-        <v>78524</v>
+        <v>79406</v>
       </c>
       <c r="C290" t="inlineStr">
         <is>
@@ -31921,21 +31921,21 @@
         </is>
       </c>
       <c r="E290" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I290" t="inlineStr"/>
@@ -31945,10 +31945,10 @@
         </is>
       </c>
       <c r="Q290" t="n">
-        <v>459448</v>
+        <v>459317</v>
       </c>
       <c r="R290" t="n">
-        <v>6808388</v>
+        <v>6808694</v>
       </c>
       <c r="S290" t="n">
         <v>10</v>
@@ -31975,12 +31975,12 @@
       </c>
       <c r="Y290" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA290" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD290" t="b">
@@ -32000,17 +32000,17 @@
       </c>
       <c r="AX290" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>123920661</v>
+        <v>123920597</v>
       </c>
       <c r="B291" t="n">
-        <v>78788</v>
+        <v>78524</v>
       </c>
       <c r="C291" t="inlineStr">
         <is>
@@ -32023,21 +32023,21 @@
         </is>
       </c>
       <c r="E291" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I291" t="inlineStr"/>
@@ -32047,10 +32047,10 @@
         </is>
       </c>
       <c r="Q291" t="n">
-        <v>458763</v>
+        <v>459448</v>
       </c>
       <c r="R291" t="n">
-        <v>6808761</v>
+        <v>6808388</v>
       </c>
       <c r="S291" t="n">
         <v>10</v>
@@ -32077,12 +32077,12 @@
       </c>
       <c r="Y291" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA291" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD291" t="b">
@@ -32102,17 +32102,17 @@
       </c>
       <c r="AX291" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>123920305</v>
+        <v>123920661</v>
       </c>
       <c r="B292" t="n">
-        <v>79406</v>
+        <v>78788</v>
       </c>
       <c r="C292" t="inlineStr">
         <is>
@@ -32125,21 +32125,21 @@
         </is>
       </c>
       <c r="E292" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I292" t="inlineStr"/>
@@ -32149,10 +32149,10 @@
         </is>
       </c>
       <c r="Q292" t="n">
-        <v>458942</v>
+        <v>458763</v>
       </c>
       <c r="R292" t="n">
-        <v>6808688</v>
+        <v>6808761</v>
       </c>
       <c r="S292" t="n">
         <v>10</v>
@@ -32211,10 +32211,10 @@
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>123920602</v>
+        <v>123920305</v>
       </c>
       <c r="B293" t="n">
-        <v>56692</v>
+        <v>79406</v>
       </c>
       <c r="C293" t="inlineStr">
         <is>
@@ -32227,42 +32227,34 @@
         </is>
       </c>
       <c r="E293" t="n">
-        <v>102612</v>
+        <v>6453</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I293" t="inlineStr"/>
-      <c r="K293" t="inlineStr"/>
-      <c r="L293" t="inlineStr"/>
-      <c r="M293" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N293" t="inlineStr"/>
       <c r="P293" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q293" t="n">
-        <v>459098</v>
+        <v>458942</v>
       </c>
       <c r="R293" t="n">
-        <v>6808349</v>
+        <v>6808688</v>
       </c>
       <c r="S293" t="n">
         <v>10</v>
@@ -32289,12 +32281,12 @@
       </c>
       <c r="Y293" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA293" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD293" t="b">
@@ -32314,17 +32306,17 @@
       </c>
       <c r="AX293" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>123920450</v>
+        <v>123920602</v>
       </c>
       <c r="B294" t="n">
-        <v>56700</v>
+        <v>56692</v>
       </c>
       <c r="C294" t="inlineStr">
         <is>
@@ -32333,43 +32325,46 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E294" t="n">
-        <v>100138</v>
+        <v>102612</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I294" t="inlineStr"/>
+      <c r="K294" t="inlineStr"/>
+      <c r="L294" t="inlineStr"/>
       <c r="M294" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N294" t="inlineStr"/>
       <c r="P294" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q294" t="n">
-        <v>459083</v>
+        <v>459098</v>
       </c>
       <c r="R294" t="n">
-        <v>6808668</v>
+        <v>6808349</v>
       </c>
       <c r="S294" t="n">
         <v>10</v>
@@ -32396,12 +32391,12 @@
       </c>
       <c r="Y294" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA294" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD294" t="b">
@@ -32421,17 +32416,17 @@
       </c>
       <c r="AX294" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>123920550</v>
+        <v>123920450</v>
       </c>
       <c r="B295" t="n">
-        <v>78525</v>
+        <v>56700</v>
       </c>
       <c r="C295" t="inlineStr">
         <is>
@@ -32440,38 +32435,43 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E295" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I295" t="inlineStr"/>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P295" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q295" t="n">
-        <v>459448</v>
+        <v>459083</v>
       </c>
       <c r="R295" t="n">
-        <v>6808388</v>
+        <v>6808668</v>
       </c>
       <c r="S295" t="n">
         <v>10</v>
@@ -32498,12 +32498,12 @@
       </c>
       <c r="Y295" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA295" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD295" t="b">
@@ -32523,7 +32523,7 @@
       </c>
       <c r="AX295" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY295" t="inlineStr"/>
@@ -33244,10 +33244,10 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>123920683</v>
+        <v>123920390</v>
       </c>
       <c r="B303" t="n">
-        <v>78788</v>
+        <v>79377</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
@@ -33260,21 +33260,21 @@
         </is>
       </c>
       <c r="E303" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I303" t="inlineStr"/>
@@ -33284,10 +33284,10 @@
         </is>
       </c>
       <c r="Q303" t="n">
-        <v>459386</v>
+        <v>459270</v>
       </c>
       <c r="R303" t="n">
-        <v>6808640</v>
+        <v>6808690</v>
       </c>
       <c r="S303" t="n">
         <v>10</v>
@@ -33346,7 +33346,7 @@
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>123920838</v>
+        <v>123920683</v>
       </c>
       <c r="B304" t="n">
         <v>78788</v>
@@ -33386,10 +33386,10 @@
         </is>
       </c>
       <c r="Q304" t="n">
-        <v>459758</v>
+        <v>459386</v>
       </c>
       <c r="R304" t="n">
-        <v>6808333</v>
+        <v>6808640</v>
       </c>
       <c r="S304" t="n">
         <v>10</v>
@@ -33416,12 +33416,12 @@
       </c>
       <c r="Y304" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA304" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD304" t="b">
@@ -33441,14 +33441,14 @@
       </c>
       <c r="AX304" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>123920801</v>
+        <v>123920838</v>
       </c>
       <c r="B305" t="n">
         <v>78788</v>
@@ -33488,10 +33488,10 @@
         </is>
       </c>
       <c r="Q305" t="n">
-        <v>459014</v>
+        <v>459758</v>
       </c>
       <c r="R305" t="n">
-        <v>6808348</v>
+        <v>6808333</v>
       </c>
       <c r="S305" t="n">
         <v>10</v>
@@ -33550,10 +33550,10 @@
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>123920370</v>
+        <v>123920801</v>
       </c>
       <c r="B306" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C306" t="inlineStr">
         <is>
@@ -33566,21 +33566,21 @@
         </is>
       </c>
       <c r="E306" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I306" t="inlineStr"/>
@@ -33590,10 +33590,10 @@
         </is>
       </c>
       <c r="Q306" t="n">
-        <v>459007</v>
+        <v>459014</v>
       </c>
       <c r="R306" t="n">
-        <v>6808305</v>
+        <v>6808348</v>
       </c>
       <c r="S306" t="n">
         <v>10</v>
@@ -33645,17 +33645,17 @@
       </c>
       <c r="AX306" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>123920662</v>
+        <v>123920370</v>
       </c>
       <c r="B307" t="n">
-        <v>78788</v>
+        <v>78820</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
@@ -33668,21 +33668,21 @@
         </is>
       </c>
       <c r="E307" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I307" t="inlineStr"/>
@@ -33692,10 +33692,10 @@
         </is>
       </c>
       <c r="Q307" t="n">
-        <v>458749</v>
+        <v>459007</v>
       </c>
       <c r="R307" t="n">
-        <v>6808795</v>
+        <v>6808305</v>
       </c>
       <c r="S307" t="n">
         <v>10</v>
@@ -33722,12 +33722,12 @@
       </c>
       <c r="Y307" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA307" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD307" t="b">
@@ -33747,14 +33747,14 @@
       </c>
       <c r="AX307" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>123920832</v>
+        <v>123920662</v>
       </c>
       <c r="B308" t="n">
         <v>78788</v>
@@ -33794,10 +33794,10 @@
         </is>
       </c>
       <c r="Q308" t="n">
-        <v>459673</v>
+        <v>458749</v>
       </c>
       <c r="R308" t="n">
-        <v>6808319</v>
+        <v>6808795</v>
       </c>
       <c r="S308" t="n">
         <v>10</v>
@@ -33824,12 +33824,12 @@
       </c>
       <c r="Y308" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA308" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD308" t="b">
@@ -33849,17 +33849,17 @@
       </c>
       <c r="AX308" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>123920304</v>
+        <v>123920832</v>
       </c>
       <c r="B309" t="n">
-        <v>79406</v>
+        <v>78788</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
@@ -33872,21 +33872,21 @@
         </is>
       </c>
       <c r="E309" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I309" t="inlineStr"/>
@@ -33896,10 +33896,10 @@
         </is>
       </c>
       <c r="Q309" t="n">
-        <v>458899</v>
+        <v>459673</v>
       </c>
       <c r="R309" t="n">
-        <v>6808695</v>
+        <v>6808319</v>
       </c>
       <c r="S309" t="n">
         <v>10</v>
@@ -33926,12 +33926,12 @@
       </c>
       <c r="Y309" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA309" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD309" t="b">
@@ -33951,17 +33951,17 @@
       </c>
       <c r="AX309" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>123920390</v>
+        <v>123920304</v>
       </c>
       <c r="B310" t="n">
-        <v>79377</v>
+        <v>79406</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
@@ -33974,21 +33974,21 @@
         </is>
       </c>
       <c r="E310" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I310" t="inlineStr"/>
@@ -33998,10 +33998,10 @@
         </is>
       </c>
       <c r="Q310" t="n">
-        <v>459270</v>
+        <v>458899</v>
       </c>
       <c r="R310" t="n">
-        <v>6808690</v>
+        <v>6808695</v>
       </c>
       <c r="S310" t="n">
         <v>10</v>
@@ -37158,10 +37158,10 @@
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>123920407</v>
+        <v>123920663</v>
       </c>
       <c r="B341" t="n">
-        <v>79377</v>
+        <v>78788</v>
       </c>
       <c r="C341" t="inlineStr">
         <is>
@@ -37174,21 +37174,21 @@
         </is>
       </c>
       <c r="E341" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I341" t="inlineStr"/>
@@ -37198,10 +37198,10 @@
         </is>
       </c>
       <c r="Q341" t="n">
-        <v>459574</v>
+        <v>458760</v>
       </c>
       <c r="R341" t="n">
-        <v>6808268</v>
+        <v>6808814</v>
       </c>
       <c r="S341" t="n">
         <v>10</v>
@@ -37228,12 +37228,12 @@
       </c>
       <c r="Y341" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA341" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD341" t="b">
@@ -37253,17 +37253,17 @@
       </c>
       <c r="AX341" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>123920663</v>
+        <v>123920316</v>
       </c>
       <c r="B342" t="n">
-        <v>78788</v>
+        <v>79406</v>
       </c>
       <c r="C342" t="inlineStr">
         <is>
@@ -37276,21 +37276,21 @@
         </is>
       </c>
       <c r="E342" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I342" t="inlineStr"/>
@@ -37300,10 +37300,10 @@
         </is>
       </c>
       <c r="Q342" t="n">
-        <v>458760</v>
+        <v>459455</v>
       </c>
       <c r="R342" t="n">
-        <v>6808814</v>
+        <v>6808627</v>
       </c>
       <c r="S342" t="n">
         <v>10</v>
@@ -37362,10 +37362,10 @@
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>123920316</v>
+        <v>123920480</v>
       </c>
       <c r="B343" t="n">
-        <v>79406</v>
+        <v>57507</v>
       </c>
       <c r="C343" t="inlineStr">
         <is>
@@ -37378,34 +37378,39 @@
         </is>
       </c>
       <c r="E343" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I343" t="inlineStr"/>
+      <c r="M343" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P343" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q343" t="n">
-        <v>459455</v>
+        <v>459472</v>
       </c>
       <c r="R343" t="n">
-        <v>6808627</v>
+        <v>6808389</v>
       </c>
       <c r="S343" t="n">
         <v>10</v>
@@ -37432,12 +37437,17 @@
       </c>
       <c r="Y343" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA343" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC343" t="inlineStr">
+        <is>
+          <t>Troligt boträd</t>
         </is>
       </c>
       <c r="AD343" t="b">
@@ -37457,17 +37467,17 @@
       </c>
       <c r="AX343" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>123920480</v>
+        <v>123920457</v>
       </c>
       <c r="B344" t="n">
-        <v>57507</v>
+        <v>56700</v>
       </c>
       <c r="C344" t="inlineStr">
         <is>
@@ -37476,31 +37486,31 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E344" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I344" t="inlineStr"/>
       <c r="M344" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P344" t="inlineStr">
@@ -37509,10 +37519,10 @@
         </is>
       </c>
       <c r="Q344" t="n">
-        <v>459472</v>
+        <v>458767</v>
       </c>
       <c r="R344" t="n">
-        <v>6808389</v>
+        <v>6808746</v>
       </c>
       <c r="S344" t="n">
         <v>10</v>
@@ -37539,17 +37549,12 @@
       </c>
       <c r="Y344" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA344" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC344" t="inlineStr">
-        <is>
-          <t>Troligt boträd</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD344" t="b">
@@ -37569,17 +37574,17 @@
       </c>
       <c r="AX344" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>123920457</v>
+        <v>123920407</v>
       </c>
       <c r="B345" t="n">
-        <v>56700</v>
+        <v>79377</v>
       </c>
       <c r="C345" t="inlineStr">
         <is>
@@ -37588,43 +37593,38 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E345" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I345" t="inlineStr"/>
-      <c r="M345" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P345" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q345" t="n">
-        <v>458767</v>
+        <v>459574</v>
       </c>
       <c r="R345" t="n">
-        <v>6808746</v>
+        <v>6808268</v>
       </c>
       <c r="S345" t="n">
         <v>10</v>
@@ -37651,12 +37651,12 @@
       </c>
       <c r="Y345" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA345" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD345" t="b">
@@ -37676,7 +37676,7 @@
       </c>
       <c r="AX345" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY345" t="inlineStr"/>
@@ -37785,10 +37785,10 @@
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>123920546</v>
+        <v>123920814</v>
       </c>
       <c r="B347" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C347" t="inlineStr">
         <is>
@@ -37801,21 +37801,21 @@
         </is>
       </c>
       <c r="E347" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I347" t="inlineStr"/>
@@ -37825,10 +37825,10 @@
         </is>
       </c>
       <c r="Q347" t="n">
-        <v>458953</v>
+        <v>459244</v>
       </c>
       <c r="R347" t="n">
-        <v>6808275</v>
+        <v>6808386</v>
       </c>
       <c r="S347" t="n">
         <v>10</v>
@@ -37887,10 +37887,10 @@
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>123920523</v>
+        <v>123920908</v>
       </c>
       <c r="B348" t="n">
-        <v>78525</v>
+        <v>92271</v>
       </c>
       <c r="C348" t="inlineStr">
         <is>
@@ -37899,25 +37899,25 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E348" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I348" t="inlineStr"/>
@@ -37927,10 +37927,10 @@
         </is>
       </c>
       <c r="Q348" t="n">
-        <v>458899</v>
+        <v>459439</v>
       </c>
       <c r="R348" t="n">
-        <v>6808695</v>
+        <v>6808385</v>
       </c>
       <c r="S348" t="n">
         <v>10</v>
@@ -37957,12 +37957,12 @@
       </c>
       <c r="Y348" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA348" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD348" t="b">
@@ -37982,17 +37982,17 @@
       </c>
       <c r="AX348" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>123920394</v>
+        <v>123920809</v>
       </c>
       <c r="B349" t="n">
-        <v>79377</v>
+        <v>78788</v>
       </c>
       <c r="C349" t="inlineStr">
         <is>
@@ -38005,21 +38005,21 @@
         </is>
       </c>
       <c r="E349" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I349" t="inlineStr"/>
@@ -38029,10 +38029,10 @@
         </is>
       </c>
       <c r="Q349" t="n">
-        <v>459406</v>
+        <v>459187</v>
       </c>
       <c r="R349" t="n">
-        <v>6808639</v>
+        <v>6808367</v>
       </c>
       <c r="S349" t="n">
         <v>10</v>
@@ -38059,12 +38059,12 @@
       </c>
       <c r="Y349" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA349" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD349" t="b">
@@ -38084,14 +38084,14 @@
       </c>
       <c r="AX349" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>123920814</v>
+        <v>123920813</v>
       </c>
       <c r="B350" t="n">
         <v>78788</v>
@@ -38131,10 +38131,10 @@
         </is>
       </c>
       <c r="Q350" t="n">
-        <v>459244</v>
+        <v>459237</v>
       </c>
       <c r="R350" t="n">
-        <v>6808386</v>
+        <v>6808364</v>
       </c>
       <c r="S350" t="n">
         <v>10</v>
@@ -38193,10 +38193,10 @@
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>123920908</v>
+        <v>123920572</v>
       </c>
       <c r="B351" t="n">
-        <v>92271</v>
+        <v>80741</v>
       </c>
       <c r="C351" t="inlineStr">
         <is>
@@ -38205,25 +38205,25 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E351" t="n">
-        <v>4364</v>
+        <v>1049</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I351" t="inlineStr"/>
@@ -38233,10 +38233,10 @@
         </is>
       </c>
       <c r="Q351" t="n">
-        <v>459439</v>
+        <v>458928</v>
       </c>
       <c r="R351" t="n">
-        <v>6808385</v>
+        <v>6808283</v>
       </c>
       <c r="S351" t="n">
         <v>10</v>
@@ -38295,7 +38295,7 @@
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>123920809</v>
+        <v>123920800</v>
       </c>
       <c r="B352" t="n">
         <v>78788</v>
@@ -38335,10 +38335,10 @@
         </is>
       </c>
       <c r="Q352" t="n">
-        <v>459187</v>
+        <v>458995</v>
       </c>
       <c r="R352" t="n">
-        <v>6808367</v>
+        <v>6808327</v>
       </c>
       <c r="S352" t="n">
         <v>10</v>
@@ -38397,10 +38397,10 @@
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>123920813</v>
+        <v>123920309</v>
       </c>
       <c r="B353" t="n">
-        <v>78788</v>
+        <v>79406</v>
       </c>
       <c r="C353" t="inlineStr">
         <is>
@@ -38413,21 +38413,21 @@
         </is>
       </c>
       <c r="E353" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I353" t="inlineStr"/>
@@ -38437,10 +38437,10 @@
         </is>
       </c>
       <c r="Q353" t="n">
-        <v>459237</v>
+        <v>459134</v>
       </c>
       <c r="R353" t="n">
-        <v>6808364</v>
+        <v>6808662</v>
       </c>
       <c r="S353" t="n">
         <v>10</v>
@@ -38467,12 +38467,12 @@
       </c>
       <c r="Y353" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA353" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD353" t="b">
@@ -38492,17 +38492,17 @@
       </c>
       <c r="AX353" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>123920572</v>
+        <v>123920546</v>
       </c>
       <c r="B354" t="n">
-        <v>80741</v>
+        <v>78525</v>
       </c>
       <c r="C354" t="inlineStr">
         <is>
@@ -38515,21 +38515,21 @@
         </is>
       </c>
       <c r="E354" t="n">
-        <v>1049</v>
+        <v>228912</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I354" t="inlineStr"/>
@@ -38539,10 +38539,10 @@
         </is>
       </c>
       <c r="Q354" t="n">
-        <v>458928</v>
+        <v>458953</v>
       </c>
       <c r="R354" t="n">
-        <v>6808283</v>
+        <v>6808275</v>
       </c>
       <c r="S354" t="n">
         <v>10</v>
@@ -38601,10 +38601,10 @@
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>123920800</v>
+        <v>123920523</v>
       </c>
       <c r="B355" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C355" t="inlineStr">
         <is>
@@ -38617,21 +38617,21 @@
         </is>
       </c>
       <c r="E355" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I355" t="inlineStr"/>
@@ -38641,10 +38641,10 @@
         </is>
       </c>
       <c r="Q355" t="n">
-        <v>458995</v>
+        <v>458899</v>
       </c>
       <c r="R355" t="n">
-        <v>6808327</v>
+        <v>6808695</v>
       </c>
       <c r="S355" t="n">
         <v>10</v>
@@ -38671,12 +38671,12 @@
       </c>
       <c r="Y355" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA355" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD355" t="b">
@@ -38696,17 +38696,17 @@
       </c>
       <c r="AX355" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>123920309</v>
+        <v>123920394</v>
       </c>
       <c r="B356" t="n">
-        <v>79406</v>
+        <v>79377</v>
       </c>
       <c r="C356" t="inlineStr">
         <is>
@@ -38719,21 +38719,21 @@
         </is>
       </c>
       <c r="E356" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I356" t="inlineStr"/>
@@ -38743,10 +38743,10 @@
         </is>
       </c>
       <c r="Q356" t="n">
-        <v>459134</v>
+        <v>459406</v>
       </c>
       <c r="R356" t="n">
-        <v>6808662</v>
+        <v>6808639</v>
       </c>
       <c r="S356" t="n">
         <v>10</v>
@@ -38805,10 +38805,10 @@
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>123920907</v>
+        <v>123920447</v>
       </c>
       <c r="B357" t="n">
-        <v>92271</v>
+        <v>56700</v>
       </c>
       <c r="C357" t="inlineStr">
         <is>
@@ -38821,34 +38821,39 @@
         </is>
       </c>
       <c r="E357" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I357" t="inlineStr"/>
+      <c r="M357" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P357" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q357" t="n">
-        <v>458744</v>
+        <v>459190</v>
       </c>
       <c r="R357" t="n">
-        <v>6808797</v>
+        <v>6808367</v>
       </c>
       <c r="S357" t="n">
         <v>10</v>
@@ -38875,12 +38880,12 @@
       </c>
       <c r="Y357" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA357" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD357" t="b">
@@ -38900,17 +38905,17 @@
       </c>
       <c r="AX357" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>123920812</v>
+        <v>123920907</v>
       </c>
       <c r="B358" t="n">
-        <v>78788</v>
+        <v>92271</v>
       </c>
       <c r="C358" t="inlineStr">
         <is>
@@ -38919,25 +38924,25 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E358" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I358" t="inlineStr"/>
@@ -38947,10 +38952,10 @@
         </is>
       </c>
       <c r="Q358" t="n">
-        <v>459239</v>
+        <v>458744</v>
       </c>
       <c r="R358" t="n">
-        <v>6808359</v>
+        <v>6808797</v>
       </c>
       <c r="S358" t="n">
         <v>10</v>
@@ -38977,12 +38982,12 @@
       </c>
       <c r="Y358" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA358" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD358" t="b">
@@ -39002,17 +39007,17 @@
       </c>
       <c r="AX358" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>123920447</v>
+        <v>123920812</v>
       </c>
       <c r="B359" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C359" t="inlineStr">
         <is>
@@ -39021,43 +39026,38 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E359" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I359" t="inlineStr"/>
-      <c r="M359" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P359" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q359" t="n">
-        <v>459190</v>
+        <v>459239</v>
       </c>
       <c r="R359" t="n">
-        <v>6808367</v>
+        <v>6808359</v>
       </c>
       <c r="S359" t="n">
         <v>10</v>
@@ -39109,7 +39109,7 @@
       </c>
       <c r="AX359" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY359" t="inlineStr"/>

--- a/artfynd/A 61324-2022 artfynd.xlsx
+++ b/artfynd/A 61324-2022 artfynd.xlsx
@@ -785,7 +785,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123544364</v>
+        <v>123548209</v>
       </c>
       <c r="B3" t="n">
         <v>78788</v>
@@ -821,17 +821,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459563</v>
+        <v>459014</v>
       </c>
       <c r="R3" t="n">
-        <v>6808917</v>
+        <v>6808874</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,19 +885,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123548209</v>
+        <v>123544364</v>
       </c>
       <c r="B4" t="n">
         <v>78788</v>
@@ -933,17 +933,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Andljusen, Andljusen, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459014</v>
+        <v>459563</v>
       </c>
       <c r="R4" t="n">
-        <v>6808874</v>
+        <v>6808917</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -997,22 +997,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123549200</v>
+        <v>123548636</v>
       </c>
       <c r="B5" t="n">
-        <v>78788</v>
+        <v>78524</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,37 +1025,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459265</v>
+        <v>459184</v>
       </c>
       <c r="R5" t="n">
-        <v>6808827</v>
+        <v>6808784</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,22 +1109,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123548636</v>
+        <v>123549262</v>
       </c>
       <c r="B6" t="n">
-        <v>78524</v>
+        <v>78788</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1137,21 +1137,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459184</v>
+        <v>459241</v>
       </c>
       <c r="R6" t="n">
-        <v>6808784</v>
+        <v>6808793</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1196,7 +1196,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,7 +1233,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123549262</v>
+        <v>123549170</v>
       </c>
       <c r="B7" t="n">
         <v>78788</v>
@@ -1269,17 +1269,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>459241</v>
+        <v>459062</v>
       </c>
       <c r="R7" t="n">
-        <v>6808793</v>
+        <v>6808854</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1333,19 +1333,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123549170</v>
+        <v>123549689</v>
       </c>
       <c r="B8" t="n">
         <v>78788</v>
@@ -1381,17 +1381,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Andljusen, Andljusen, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>459062</v>
+        <v>459457</v>
       </c>
       <c r="R8" t="n">
-        <v>6808854</v>
+        <v>6808865</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1445,19 +1445,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123549689</v>
+        <v>123549200</v>
       </c>
       <c r="B9" t="n">
         <v>78788</v>
@@ -1497,10 +1497,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>459457</v>
+        <v>459265</v>
       </c>
       <c r="R9" t="n">
-        <v>6808865</v>
+        <v>6808827</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1569,7 +1569,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123548439</v>
+        <v>123549271</v>
       </c>
       <c r="B10" t="n">
         <v>78788</v>
@@ -1605,17 +1605,17 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Andljusen, Andljusen, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>459138</v>
+        <v>459269</v>
       </c>
       <c r="R10" t="n">
-        <v>6808765</v>
+        <v>6808827</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1669,19 +1669,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123549137</v>
+        <v>123548439</v>
       </c>
       <c r="B11" t="n">
         <v>78788</v>
@@ -1717,14 +1717,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>459240</v>
+        <v>459138</v>
       </c>
       <c r="R11" t="n">
-        <v>6808796</v>
+        <v>6808765</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1793,7 +1793,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123549271</v>
+        <v>123549137</v>
       </c>
       <c r="B12" t="n">
         <v>78788</v>
@@ -1833,13 +1833,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>459269</v>
+        <v>459240</v>
       </c>
       <c r="R12" t="n">
-        <v>6808827</v>
+        <v>6808796</v>
       </c>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1893,12 +1893,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2246,10 +2246,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123548423</v>
+        <v>123548371</v>
       </c>
       <c r="B16" t="n">
-        <v>78524</v>
+        <v>78788</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2262,21 +2262,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2286,13 +2286,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>459082</v>
+        <v>459133</v>
       </c>
       <c r="R16" t="n">
-        <v>6808839</v>
+        <v>6808760</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2346,22 +2346,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123548371</v>
+        <v>123548423</v>
       </c>
       <c r="B17" t="n">
-        <v>78788</v>
+        <v>78524</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2374,21 +2374,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2398,13 +2398,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>459133</v>
+        <v>459082</v>
       </c>
       <c r="R17" t="n">
-        <v>6808760</v>
+        <v>6808839</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2458,12 +2458,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2694,10 +2694,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123549476</v>
+        <v>123543987</v>
       </c>
       <c r="B20" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2706,46 +2706,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>459369</v>
+        <v>459521</v>
       </c>
       <c r="R20" t="n">
-        <v>6808793</v>
+        <v>6808918</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2774,7 +2769,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2784,12 +2779,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:24</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Under betestall</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2804,19 +2794,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123543987</v>
+        <v>123549630</v>
       </c>
       <c r="B21" t="n">
         <v>78788</v>
@@ -2856,13 +2846,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>459521</v>
+        <v>459421</v>
       </c>
       <c r="R21" t="n">
-        <v>6808918</v>
+        <v>6808816</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2891,7 +2881,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2901,7 +2891,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2916,19 +2906,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123549630</v>
+        <v>123549099</v>
       </c>
       <c r="B22" t="n">
         <v>78788</v>
@@ -2964,14 +2954,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>459421</v>
+        <v>459197</v>
       </c>
       <c r="R22" t="n">
-        <v>6808816</v>
+        <v>6808824</v>
       </c>
       <c r="S22" t="n">
         <v>9</v>
@@ -3003,7 +2993,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3013,7 +3003,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3040,10 +3030,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123549099</v>
+        <v>123549476</v>
       </c>
       <c r="B23" t="n">
-        <v>78788</v>
+        <v>56700</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3052,38 +3042,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Andljusen, Andljusen, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>459197</v>
+        <v>459369</v>
       </c>
       <c r="R23" t="n">
-        <v>6808824</v>
+        <v>6808793</v>
       </c>
       <c r="S23" t="n">
         <v>9</v>
@@ -3115,7 +3110,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3125,7 +3120,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Under betestall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3264,10 +3264,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123544112</v>
+        <v>123546440</v>
       </c>
       <c r="B25" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3280,21 +3280,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3304,13 +3304,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>459506</v>
+        <v>459563</v>
       </c>
       <c r="R25" t="n">
-        <v>6808960</v>
+        <v>6808917</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3349,7 +3349,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3364,19 +3364,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123543936</v>
+        <v>123544112</v>
       </c>
       <c r="B26" t="n">
         <v>78788</v>
@@ -3416,10 +3416,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>459520</v>
+        <v>459506</v>
       </c>
       <c r="R26" t="n">
-        <v>6808918</v>
+        <v>6808960</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3451,7 +3451,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3488,10 +3488,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123546440</v>
+        <v>123543936</v>
       </c>
       <c r="B27" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3504,21 +3504,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3528,13 +3528,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>459563</v>
+        <v>459520</v>
       </c>
       <c r="R27" t="n">
-        <v>6808917</v>
+        <v>6808918</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3588,12 +3588,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3712,10 +3712,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123548196</v>
+        <v>123549418</v>
       </c>
       <c r="B29" t="n">
-        <v>78788</v>
+        <v>56700</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3724,41 +3724,46 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Andljusen, Andljusen, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>459024</v>
+        <v>459318</v>
       </c>
       <c r="R29" t="n">
-        <v>6808872</v>
+        <v>6808809</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3787,7 +3792,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3797,7 +3802,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Under betestall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3812,12 +3822,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -4160,10 +4170,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123549418</v>
+        <v>123548196</v>
       </c>
       <c r="B33" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4172,46 +4182,41 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>459318</v>
+        <v>459024</v>
       </c>
       <c r="R33" t="n">
-        <v>6808809</v>
+        <v>6808872</v>
       </c>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4240,7 +4245,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4250,12 +4255,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:21</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Under betestall</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4270,12 +4270,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -5066,7 +5066,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123549655</v>
+        <v>123548510</v>
       </c>
       <c r="B41" t="n">
         <v>78788</v>
@@ -5102,17 +5102,17 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>459448</v>
+        <v>459172</v>
       </c>
       <c r="R41" t="n">
-        <v>6808852</v>
+        <v>6808718</v>
       </c>
       <c r="S41" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5166,22 +5166,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123548510</v>
+        <v>123548646</v>
       </c>
       <c r="B42" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5194,21 +5194,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5218,10 +5218,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>459172</v>
+        <v>459185</v>
       </c>
       <c r="R42" t="n">
-        <v>6808718</v>
+        <v>6808785</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5253,7 +5253,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5263,7 +5263,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5290,10 +5290,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123548646</v>
+        <v>123549655</v>
       </c>
       <c r="B43" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5306,37 +5306,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>459185</v>
+        <v>459448</v>
       </c>
       <c r="R43" t="n">
-        <v>6808785</v>
+        <v>6808852</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5365,7 +5365,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5375,7 +5375,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5390,22 +5390,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123574077</v>
+        <v>123576563</v>
       </c>
       <c r="B44" t="n">
-        <v>78788</v>
+        <v>79377</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5418,21 +5418,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>459771</v>
+        <v>459569</v>
       </c>
       <c r="R44" t="n">
-        <v>6808489</v>
+        <v>6808541</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5477,7 +5477,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5502,22 +5502,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123575142</v>
+        <v>123577958</v>
       </c>
       <c r="B45" t="n">
-        <v>78788</v>
+        <v>79377</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5530,21 +5530,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5554,13 +5554,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>459609</v>
+        <v>459571</v>
       </c>
       <c r="R45" t="n">
-        <v>6808467</v>
+        <v>6808546</v>
       </c>
       <c r="S45" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5599,12 +5599,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:57</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På tallstammar</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5619,19 +5614,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123574956</v>
+        <v>123574077</v>
       </c>
       <c r="B46" t="n">
         <v>78788</v>
@@ -5671,13 +5666,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>459629</v>
+        <v>459771</v>
       </c>
       <c r="R46" t="n">
-        <v>6808493</v>
+        <v>6808489</v>
       </c>
       <c r="S46" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5706,7 +5701,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5716,12 +5711,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:52</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>På tallstammar 9st</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5736,19 +5726,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123575156</v>
+        <v>123575142</v>
       </c>
       <c r="B47" t="n">
         <v>78788</v>
@@ -5788,13 +5778,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>459576</v>
+        <v>459609</v>
       </c>
       <c r="R47" t="n">
-        <v>6808422</v>
+        <v>6808467</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5823,7 +5813,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5833,7 +5823,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>På tallstammar</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5848,22 +5843,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123576563</v>
+        <v>123574956</v>
       </c>
       <c r="B48" t="n">
-        <v>79377</v>
+        <v>78788</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5876,21 +5871,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5900,13 +5895,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>459569</v>
+        <v>459629</v>
       </c>
       <c r="R48" t="n">
-        <v>6808541</v>
+        <v>6808493</v>
       </c>
       <c r="S48" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5935,7 +5930,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5945,7 +5940,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På tallstammar 9st</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5960,22 +5960,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123577958</v>
+        <v>123575156</v>
       </c>
       <c r="B49" t="n">
-        <v>79377</v>
+        <v>78788</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5988,21 +5988,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6012,13 +6012,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>459571</v>
+        <v>459576</v>
       </c>
       <c r="R49" t="n">
-        <v>6808546</v>
+        <v>6808422</v>
       </c>
       <c r="S49" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6047,7 +6047,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6057,7 +6057,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6072,12 +6072,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -6201,10 +6201,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123575925</v>
+        <v>123575840</v>
       </c>
       <c r="B51" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6217,21 +6217,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6241,13 +6241,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>459515</v>
+        <v>459570</v>
       </c>
       <c r="R51" t="n">
-        <v>6808562</v>
+        <v>6808531</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6286,7 +6286,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6301,22 +6301,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123566115</v>
+        <v>123577149</v>
       </c>
       <c r="B52" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6329,37 +6329,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>459733</v>
+        <v>459571</v>
       </c>
       <c r="R52" t="n">
-        <v>6808745</v>
+        <v>6808546</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6388,7 +6388,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6398,7 +6398,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6413,19 +6413,19 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123576411</v>
+        <v>123575925</v>
       </c>
       <c r="B53" t="n">
         <v>78788</v>
@@ -6465,13 +6465,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>459499</v>
+        <v>459515</v>
       </c>
       <c r="R53" t="n">
-        <v>6808603</v>
+        <v>6808562</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6500,7 +6500,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6510,7 +6510,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6537,7 +6537,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123576513</v>
+        <v>123566115</v>
       </c>
       <c r="B54" t="n">
         <v>78788</v>
@@ -6573,17 +6573,17 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>459499</v>
+        <v>459733</v>
       </c>
       <c r="R54" t="n">
-        <v>6808540</v>
+        <v>6808745</v>
       </c>
       <c r="S54" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6612,7 +6612,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6622,12 +6622,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:29</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>På Granar</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6642,22 +6637,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123575840</v>
+        <v>123576411</v>
       </c>
       <c r="B55" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6670,21 +6665,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6694,13 +6689,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>459570</v>
+        <v>459499</v>
       </c>
       <c r="R55" t="n">
-        <v>6808531</v>
+        <v>6808603</v>
       </c>
       <c r="S55" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6729,7 +6724,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6739,7 +6734,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6754,22 +6749,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123577149</v>
+        <v>123576513</v>
       </c>
       <c r="B56" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6782,21 +6777,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6806,13 +6801,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>459571</v>
+        <v>459499</v>
       </c>
       <c r="R56" t="n">
-        <v>6808546</v>
+        <v>6808540</v>
       </c>
       <c r="S56" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6841,7 +6836,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6851,7 +6846,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>På Granar</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6866,12 +6866,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -7331,10 +7331,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123577066</v>
+        <v>123576787</v>
       </c>
       <c r="B61" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7343,46 +7343,41 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>459565</v>
+        <v>459480</v>
       </c>
       <c r="R61" t="n">
-        <v>6808543</v>
+        <v>6808666</v>
       </c>
       <c r="S61" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7411,7 +7406,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7421,7 +7416,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7436,19 +7431,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123576787</v>
+        <v>123566609</v>
       </c>
       <c r="B62" t="n">
         <v>78788</v>
@@ -7484,14 +7479,14 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>459480</v>
+        <v>459735</v>
       </c>
       <c r="R62" t="n">
-        <v>6808666</v>
+        <v>6808695</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7523,7 +7518,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7533,7 +7528,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7560,7 +7555,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123566609</v>
+        <v>123573845</v>
       </c>
       <c r="B63" t="n">
         <v>78788</v>
@@ -7596,17 +7591,17 @@
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>459735</v>
+        <v>459696</v>
       </c>
       <c r="R63" t="n">
-        <v>6808695</v>
+        <v>6808508</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7635,7 +7630,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7645,7 +7640,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>På tallstammar och gran</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7660,19 +7660,19 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123573845</v>
+        <v>123575574</v>
       </c>
       <c r="B64" t="n">
         <v>78788</v>
@@ -7712,10 +7712,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>459696</v>
+        <v>459574</v>
       </c>
       <c r="R64" t="n">
-        <v>6808508</v>
+        <v>6808461</v>
       </c>
       <c r="S64" t="n">
         <v>9</v>
@@ -7747,7 +7747,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>På tallstammar och gran</t>
+          <t>På tallstammar</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7789,10 +7789,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123575574</v>
+        <v>123577066</v>
       </c>
       <c r="B65" t="n">
-        <v>78788</v>
+        <v>56700</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7801,41 +7801,46 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>459574</v>
+        <v>459565</v>
       </c>
       <c r="R65" t="n">
-        <v>6808461</v>
+        <v>6808543</v>
       </c>
       <c r="S65" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7864,7 +7869,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7874,12 +7879,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:07</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>På tallstammar</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7894,12 +7894,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -8242,10 +8242,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123565752</v>
+        <v>123566457</v>
       </c>
       <c r="B69" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8258,21 +8258,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8282,13 +8282,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>459733</v>
+        <v>459669</v>
       </c>
       <c r="R69" t="n">
-        <v>6808745</v>
+        <v>6808772</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8317,7 +8317,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8327,7 +8327,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8342,19 +8342,19 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123566457</v>
+        <v>123574154</v>
       </c>
       <c r="B70" t="n">
         <v>78788</v>
@@ -8390,17 +8390,17 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>459669</v>
+        <v>459668</v>
       </c>
       <c r="R70" t="n">
-        <v>6808772</v>
+        <v>6808515</v>
       </c>
       <c r="S70" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8439,7 +8439,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>På tallstammar</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8454,19 +8459,19 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123574154</v>
+        <v>123574103</v>
       </c>
       <c r="B71" t="n">
         <v>78788</v>
@@ -8506,10 +8511,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>459668</v>
+        <v>459671</v>
       </c>
       <c r="R71" t="n">
-        <v>6808515</v>
+        <v>6808517</v>
       </c>
       <c r="S71" t="n">
         <v>9</v>
@@ -8541,7 +8546,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8551,7 +8556,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
@@ -8583,7 +8588,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123574103</v>
+        <v>123575052</v>
       </c>
       <c r="B72" t="n">
         <v>78788</v>
@@ -8623,13 +8628,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>459671</v>
+        <v>459600</v>
       </c>
       <c r="R72" t="n">
-        <v>6808517</v>
+        <v>6808513</v>
       </c>
       <c r="S72" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8658,7 +8663,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8668,12 +8673,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:34</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>På tallstammar</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8688,22 +8688,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123575052</v>
+        <v>123565752</v>
       </c>
       <c r="B73" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8716,37 +8716,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>459600</v>
+        <v>459733</v>
       </c>
       <c r="R73" t="n">
-        <v>6808513</v>
+        <v>6808745</v>
       </c>
       <c r="S73" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8785,7 +8785,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8800,12 +8800,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -9046,10 +9046,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>123566406</v>
+        <v>123577743</v>
       </c>
       <c r="B76" t="n">
-        <v>78525</v>
+        <v>77716</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9062,37 +9062,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>459735</v>
+        <v>459571</v>
       </c>
       <c r="R76" t="n">
-        <v>6808695</v>
+        <v>6808546</v>
       </c>
       <c r="S76" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9131,7 +9131,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9146,22 +9146,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>123574629</v>
+        <v>123566406</v>
       </c>
       <c r="B77" t="n">
-        <v>79377</v>
+        <v>78525</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9174,37 +9174,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>459648</v>
+        <v>459735</v>
       </c>
       <c r="R77" t="n">
-        <v>6808494</v>
+        <v>6808695</v>
       </c>
       <c r="S77" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9233,7 +9233,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9243,7 +9243,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9258,22 +9258,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>123575648</v>
+        <v>123574629</v>
       </c>
       <c r="B78" t="n">
-        <v>78525</v>
+        <v>79377</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9286,21 +9286,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9310,10 +9310,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>459612</v>
+        <v>459648</v>
       </c>
       <c r="R78" t="n">
-        <v>6808443</v>
+        <v>6808494</v>
       </c>
       <c r="S78" t="n">
         <v>9</v>
@@ -9345,7 +9345,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9355,7 +9355,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9382,10 +9382,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>123577743</v>
+        <v>123575648</v>
       </c>
       <c r="B79" t="n">
-        <v>77716</v>
+        <v>78525</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9398,21 +9398,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9422,13 +9422,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>459571</v>
+        <v>459612</v>
       </c>
       <c r="R79" t="n">
-        <v>6808546</v>
+        <v>6808443</v>
       </c>
       <c r="S79" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9457,7 +9457,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9467,7 +9467,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9482,12 +9482,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -12832,10 +12832,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>123575396</v>
+        <v>123549286</v>
       </c>
       <c r="B109" t="n">
-        <v>79406</v>
+        <v>56700</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12844,30 +12844,35 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
@@ -12875,13 +12880,13 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>459583</v>
+        <v>459241</v>
       </c>
       <c r="R109" t="n">
-        <v>6808431</v>
+        <v>6808793</v>
       </c>
       <c r="S109" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12905,22 +12910,27 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Under betestall</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12929,26 +12939,25 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>123549286</v>
+        <v>123549184</v>
       </c>
       <c r="B110" t="n">
         <v>56700</v>
@@ -12996,7 +13005,7 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>459241</v>
+        <v>459240</v>
       </c>
       <c r="R110" t="n">
         <v>6808793</v>
@@ -13031,7 +13040,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -13041,7 +13050,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr">
@@ -13073,10 +13082,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>123549184</v>
+        <v>123575396</v>
       </c>
       <c r="B111" t="n">
-        <v>56700</v>
+        <v>79406</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -13085,35 +13094,30 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
@@ -13121,13 +13125,13 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>459240</v>
+        <v>459583</v>
       </c>
       <c r="R111" t="n">
-        <v>6808793</v>
+        <v>6808431</v>
       </c>
       <c r="S111" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -13151,27 +13155,22 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>17:14</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>Under betestall</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13180,18 +13179,19 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
+      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
@@ -13866,10 +13866,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>123726510</v>
+        <v>123727261</v>
       </c>
       <c r="B118" t="n">
-        <v>78524</v>
+        <v>78788</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13882,21 +13882,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13906,10 +13906,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>458940</v>
+        <v>458928</v>
       </c>
       <c r="R118" t="n">
-        <v>6808345</v>
+        <v>6808358</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13942,6 +13942,11 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Garnlav i en radie av ca 50 meter, så långt jag ser.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13968,10 +13973,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>123727261</v>
+        <v>123726510</v>
       </c>
       <c r="B119" t="n">
-        <v>78788</v>
+        <v>78524</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13984,21 +13989,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -14008,10 +14013,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>458928</v>
+        <v>458940</v>
       </c>
       <c r="R119" t="n">
-        <v>6808358</v>
+        <v>6808345</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -14044,11 +14049,6 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-04-03</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Garnlav i en radie av ca 50 meter, så långt jag ser.</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -15747,10 +15747,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>123727583</v>
+        <v>123727363</v>
       </c>
       <c r="B136" t="n">
-        <v>56700</v>
+        <v>78525</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15759,25 +15759,25 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15787,10 +15787,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>458880</v>
+        <v>458886</v>
       </c>
       <c r="R136" t="n">
-        <v>6808416</v>
+        <v>6808352</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15823,11 +15823,6 @@
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-04-03</t>
-        </is>
-      </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>Tjäderspillning under tjädertall med garnlav.</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15854,10 +15849,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>123729517</v>
+        <v>123727583</v>
       </c>
       <c r="B137" t="n">
-        <v>78788</v>
+        <v>56700</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15866,38 +15861,38 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Andljusen, Dlr</t>
+          <t>Dyvran, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>458715</v>
+        <v>458880</v>
       </c>
       <c r="R137" t="n">
-        <v>6808620</v>
+        <v>6808416</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15934,7 +15929,7 @@
       </c>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>Garnlav i en radie av ca 50 meter.</t>
+          <t>Tjäderspillning under tjädertall med garnlav.</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15961,10 +15956,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>123728549</v>
+        <v>123729517</v>
       </c>
       <c r="B138" t="n">
-        <v>79377</v>
+        <v>78788</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -15977,34 +15972,34 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Dyvran, Dlr</t>
+          <t>Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>458798</v>
+        <v>458715</v>
       </c>
       <c r="R138" t="n">
-        <v>6808499</v>
+        <v>6808620</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -16037,6 +16032,11 @@
       <c r="AA138" t="inlineStr">
         <is>
           <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>Garnlav i en radie av ca 50 meter.</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -16063,10 +16063,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>123727363</v>
+        <v>123728549</v>
       </c>
       <c r="B139" t="n">
-        <v>78525</v>
+        <v>79377</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -16079,21 +16079,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -16103,10 +16103,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>458886</v>
+        <v>458798</v>
       </c>
       <c r="R139" t="n">
-        <v>6808352</v>
+        <v>6808499</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -19350,10 +19350,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>123826461</v>
+        <v>123827370</v>
       </c>
       <c r="B170" t="n">
-        <v>56703</v>
+        <v>79377</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -19362,43 +19362,38 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>102613</v>
+        <v>229821</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
-      <c r="M170" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P170" t="inlineStr">
         <is>
           <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>458964</v>
+        <v>458810</v>
       </c>
       <c r="R170" t="n">
-        <v>6808848</v>
+        <v>6808640</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19428,19 +19423,9 @@
           <t>2025-04-07</t>
         </is>
       </c>
-      <c r="Z170" t="inlineStr">
-        <is>
-          <t>11:53</t>
-        </is>
-      </c>
       <c r="AA170" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AB170" t="inlineStr">
-        <is>
-          <t>11:53</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -19569,10 +19554,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>123827370</v>
+        <v>123826461</v>
       </c>
       <c r="B172" t="n">
-        <v>79377</v>
+        <v>56703</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -19581,38 +19566,43 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>229821</v>
+        <v>102613</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P172" t="inlineStr">
         <is>
           <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>458810</v>
+        <v>458964</v>
       </c>
       <c r="R172" t="n">
-        <v>6808640</v>
+        <v>6808848</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19642,9 +19632,19 @@
           <t>2025-04-07</t>
         </is>
       </c>
+      <c r="Z172" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
       <c r="AA172" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AB172" t="inlineStr">
+        <is>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -21022,10 +21022,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>123834044</v>
+        <v>123828501</v>
       </c>
       <c r="B186" t="n">
-        <v>78524</v>
+        <v>79377</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -21038,37 +21038,37 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>459221</v>
+        <v>459099</v>
       </c>
       <c r="R186" t="n">
-        <v>6808409</v>
+        <v>6808563</v>
       </c>
       <c r="S186" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -21112,22 +21112,22 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>123828501</v>
+        <v>123834044</v>
       </c>
       <c r="B187" t="n">
-        <v>79377</v>
+        <v>78524</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -21140,37 +21140,37 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>459099</v>
+        <v>459221</v>
       </c>
       <c r="R187" t="n">
-        <v>6808563</v>
+        <v>6808409</v>
       </c>
       <c r="S187" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -21214,12 +21214,12 @@
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
@@ -22179,10 +22179,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>123826946</v>
+        <v>123826931</v>
       </c>
       <c r="B197" t="n">
-        <v>78788</v>
+        <v>79406</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -22195,21 +22195,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -22219,10 +22219,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>458734</v>
+        <v>458763</v>
       </c>
       <c r="R197" t="n">
-        <v>6808688</v>
+        <v>6808709</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -22291,10 +22291,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>123827249</v>
+        <v>123826946</v>
       </c>
       <c r="B198" t="n">
-        <v>78172</v>
+        <v>78788</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -22307,21 +22307,21 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -22331,10 +22331,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>458738</v>
+        <v>458734</v>
       </c>
       <c r="R198" t="n">
-        <v>6808608</v>
+        <v>6808688</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -22364,9 +22364,19 @@
           <t>2025-04-07</t>
         </is>
       </c>
+      <c r="Z198" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
       <c r="AA198" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AB198" t="inlineStr">
+        <is>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -22393,10 +22403,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>123826892</v>
+        <v>123827249</v>
       </c>
       <c r="B199" t="n">
-        <v>78788</v>
+        <v>78172</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -22409,21 +22419,21 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -22433,10 +22443,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>458763</v>
+        <v>458738</v>
       </c>
       <c r="R199" t="n">
-        <v>6808709</v>
+        <v>6808608</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -22466,19 +22476,9 @@
           <t>2025-04-07</t>
         </is>
       </c>
-      <c r="Z199" t="inlineStr">
-        <is>
-          <t>11:53</t>
-        </is>
-      </c>
       <c r="AA199" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AB199" t="inlineStr">
-        <is>
-          <t>11:53</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -22505,10 +22505,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>123826673</v>
+        <v>123826892</v>
       </c>
       <c r="B200" t="n">
-        <v>79377</v>
+        <v>78788</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -22521,21 +22521,21 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -22545,10 +22545,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>458923</v>
+        <v>458763</v>
       </c>
       <c r="R200" t="n">
-        <v>6808811</v>
+        <v>6808709</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22617,10 +22617,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>123826931</v>
+        <v>123826673</v>
       </c>
       <c r="B201" t="n">
-        <v>79406</v>
+        <v>79377</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -22633,21 +22633,21 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -22657,10 +22657,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>458763</v>
+        <v>458923</v>
       </c>
       <c r="R201" t="n">
-        <v>6808709</v>
+        <v>6808811</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -24416,10 +24416,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>123869911</v>
+        <v>123866815</v>
       </c>
       <c r="B218" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -24432,37 +24432,37 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
       <c r="P218" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>459707</v>
+        <v>458928</v>
       </c>
       <c r="R218" t="n">
-        <v>6808760</v>
+        <v>6808783</v>
       </c>
       <c r="S218" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T218" t="inlineStr">
         <is>
@@ -24518,10 +24518,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>123866815</v>
+        <v>123865783</v>
       </c>
       <c r="B219" t="n">
-        <v>78788</v>
+        <v>56700</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -24530,41 +24530,41 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>458928</v>
+        <v>459326</v>
       </c>
       <c r="R219" t="n">
-        <v>6808783</v>
+        <v>6808793</v>
       </c>
       <c r="S219" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T219" t="inlineStr">
         <is>
@@ -24594,6 +24594,11 @@
       <c r="AA219" t="inlineStr">
         <is>
           <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC219" t="inlineStr">
+        <is>
+          <t>Nyare spillning.</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -24608,22 +24613,22 @@
       <c r="AT219" t="inlineStr"/>
       <c r="AW219" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>123865783</v>
+        <v>123869911</v>
       </c>
       <c r="B220" t="n">
-        <v>56700</v>
+        <v>78525</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -24632,25 +24637,25 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -24660,13 +24665,13 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>459326</v>
+        <v>459707</v>
       </c>
       <c r="R220" t="n">
-        <v>6808793</v>
+        <v>6808760</v>
       </c>
       <c r="S220" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T220" t="inlineStr">
         <is>
@@ -24696,11 +24701,6 @@
       <c r="AA220" t="inlineStr">
         <is>
           <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AC220" t="inlineStr">
-        <is>
-          <t>Nyare spillning.</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -24715,12 +24715,12 @@
       <c r="AT220" t="inlineStr"/>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
@@ -25767,10 +25767,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>123863775</v>
+        <v>123866998</v>
       </c>
       <c r="B231" t="n">
-        <v>78788</v>
+        <v>79377</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
@@ -25783,37 +25783,37 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
       <c r="P231" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>459740</v>
+        <v>458925</v>
       </c>
       <c r="R231" t="n">
-        <v>6808693</v>
+        <v>6808789</v>
       </c>
       <c r="S231" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T231" t="inlineStr">
         <is>
@@ -25843,11 +25843,6 @@
       <c r="AA231" t="inlineStr">
         <is>
           <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AC231" t="inlineStr">
-        <is>
-          <t>Synligt i en radie av ca 50 meter. Miljöbild.</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -25862,22 +25857,22 @@
       <c r="AT231" t="inlineStr"/>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>123869316</v>
+        <v>123864015</v>
       </c>
       <c r="B232" t="n">
-        <v>56700</v>
+        <v>79377</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
@@ -25886,46 +25881,41 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
-      <c r="M232" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P232" t="inlineStr">
         <is>
-          <t>Andljusen, Andljusen, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>459292</v>
+        <v>459594</v>
       </c>
       <c r="R232" t="n">
-        <v>6808848</v>
+        <v>6808664</v>
       </c>
       <c r="S232" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T232" t="inlineStr">
         <is>
@@ -25969,22 +25959,22 @@
       <c r="AT232" t="inlineStr"/>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>123866998</v>
+        <v>123863775</v>
       </c>
       <c r="B233" t="n">
-        <v>79377</v>
+        <v>78788</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -25997,37 +25987,37 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
       <c r="P233" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>458925</v>
+        <v>459740</v>
       </c>
       <c r="R233" t="n">
-        <v>6808789</v>
+        <v>6808693</v>
       </c>
       <c r="S233" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T233" t="inlineStr">
         <is>
@@ -26057,6 +26047,11 @@
       <c r="AA233" t="inlineStr">
         <is>
           <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC233" t="inlineStr">
+        <is>
+          <t>Synligt i en radie av ca 50 meter. Miljöbild.</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -26071,22 +26066,22 @@
       <c r="AT233" t="inlineStr"/>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>123864015</v>
+        <v>123869316</v>
       </c>
       <c r="B234" t="n">
-        <v>79377</v>
+        <v>56700</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -26095,41 +26090,46 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P234" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusen, Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>459594</v>
+        <v>459292</v>
       </c>
       <c r="R234" t="n">
-        <v>6808664</v>
+        <v>6808848</v>
       </c>
       <c r="S234" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T234" t="inlineStr">
         <is>
@@ -26173,12 +26173,12 @@
       <c r="AT234" t="inlineStr"/>
       <c r="AW234" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
@@ -27678,10 +27678,10 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>123864080</v>
+        <v>123866606</v>
       </c>
       <c r="B249" t="n">
-        <v>77716</v>
+        <v>56700</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
@@ -27690,41 +27690,46 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>6487</v>
+        <v>100138</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P249" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>459555</v>
+        <v>459103</v>
       </c>
       <c r="R249" t="n">
-        <v>6808660</v>
+        <v>6808786</v>
       </c>
       <c r="S249" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T249" t="inlineStr">
         <is>
@@ -27768,22 +27773,22 @@
       <c r="AT249" t="inlineStr"/>
       <c r="AW249" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>123864326</v>
+        <v>123864080</v>
       </c>
       <c r="B250" t="n">
-        <v>78433</v>
+        <v>77716</v>
       </c>
       <c r="C250" t="inlineStr">
         <is>
@@ -27796,21 +27801,21 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>353</v>
+        <v>6487</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
@@ -27820,10 +27825,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>459507</v>
+        <v>459555</v>
       </c>
       <c r="R250" t="n">
-        <v>6808603</v>
+        <v>6808660</v>
       </c>
       <c r="S250" t="n">
         <v>20</v>
@@ -27882,10 +27887,10 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>123866829</v>
+        <v>123864326</v>
       </c>
       <c r="B251" t="n">
-        <v>78788</v>
+        <v>78433</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>
@@ -27898,21 +27903,21 @@
         </is>
       </c>
       <c r="E251" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
@@ -27922,10 +27927,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>458970</v>
+        <v>459507</v>
       </c>
       <c r="R251" t="n">
-        <v>6808773</v>
+        <v>6808603</v>
       </c>
       <c r="S251" t="n">
         <v>20</v>
@@ -27984,7 +27989,7 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>123866750</v>
+        <v>123866829</v>
       </c>
       <c r="B252" t="n">
         <v>78788</v>
@@ -28020,17 +28025,17 @@
       <c r="I252" t="inlineStr"/>
       <c r="P252" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>459080</v>
+        <v>458970</v>
       </c>
       <c r="R252" t="n">
-        <v>6808643</v>
+        <v>6808773</v>
       </c>
       <c r="S252" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T252" t="inlineStr">
         <is>
@@ -28060,11 +28065,6 @@
       <c r="AA252" t="inlineStr">
         <is>
           <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AC252" t="inlineStr">
-        <is>
-          <t>I en radie av ca 50 meter, garnlav. Miljöbilder.</t>
         </is>
       </c>
       <c r="AD252" t="b">
@@ -28079,22 +28079,22 @@
       <c r="AT252" t="inlineStr"/>
       <c r="AW252" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>123866606</v>
+        <v>123866750</v>
       </c>
       <c r="B253" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
@@ -28103,46 +28103,41 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
-      <c r="M253" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P253" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>459103</v>
+        <v>459080</v>
       </c>
       <c r="R253" t="n">
-        <v>6808786</v>
+        <v>6808643</v>
       </c>
       <c r="S253" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T253" t="inlineStr">
         <is>
@@ -28172,6 +28167,11 @@
       <c r="AA253" t="inlineStr">
         <is>
           <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC253" t="inlineStr">
+        <is>
+          <t>I en radie av ca 50 meter, garnlav. Miljöbilder.</t>
         </is>
       </c>
       <c r="AD253" t="b">
@@ -28186,12 +28186,12 @@
       <c r="AT253" t="inlineStr"/>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
@@ -30467,10 +30467,10 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>123920677</v>
+        <v>123920449</v>
       </c>
       <c r="B276" t="n">
-        <v>78788</v>
+        <v>56700</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
@@ -30479,38 +30479,43 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P276" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>459121</v>
+        <v>458862</v>
       </c>
       <c r="R276" t="n">
-        <v>6808649</v>
+        <v>6808791</v>
       </c>
       <c r="S276" t="n">
         <v>10</v>
@@ -30569,7 +30574,7 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>123920803</v>
+        <v>123920677</v>
       </c>
       <c r="B277" t="n">
         <v>78788</v>
@@ -30609,10 +30614,10 @@
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>459061</v>
+        <v>459121</v>
       </c>
       <c r="R277" t="n">
-        <v>6808332</v>
+        <v>6808649</v>
       </c>
       <c r="S277" t="n">
         <v>10</v>
@@ -30639,12 +30644,12 @@
       </c>
       <c r="Y277" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA277" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD277" t="b">
@@ -30664,17 +30669,17 @@
       </c>
       <c r="AX277" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>123920449</v>
+        <v>123920803</v>
       </c>
       <c r="B278" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
@@ -30683,43 +30688,38 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E278" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
-      <c r="M278" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P278" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>458862</v>
+        <v>459061</v>
       </c>
       <c r="R278" t="n">
-        <v>6808791</v>
+        <v>6808332</v>
       </c>
       <c r="S278" t="n">
         <v>10</v>
@@ -30746,12 +30746,12 @@
       </c>
       <c r="Y278" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA278" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD278" t="b">
@@ -30771,14 +30771,14 @@
       </c>
       <c r="AX278" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>123920810</v>
+        <v>123920679</v>
       </c>
       <c r="B279" t="n">
         <v>78788</v>
@@ -30818,10 +30818,10 @@
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>459205</v>
+        <v>459257</v>
       </c>
       <c r="R279" t="n">
-        <v>6808378</v>
+        <v>6808663</v>
       </c>
       <c r="S279" t="n">
         <v>10</v>
@@ -30848,12 +30848,12 @@
       </c>
       <c r="Y279" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA279" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD279" t="b">
@@ -30873,14 +30873,14 @@
       </c>
       <c r="AX279" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>123920679</v>
+        <v>123920810</v>
       </c>
       <c r="B280" t="n">
         <v>78788</v>
@@ -30920,10 +30920,10 @@
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>459257</v>
+        <v>459205</v>
       </c>
       <c r="R280" t="n">
-        <v>6808663</v>
+        <v>6808378</v>
       </c>
       <c r="S280" t="n">
         <v>10</v>
@@ -30950,12 +30950,12 @@
       </c>
       <c r="Y280" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA280" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD280" t="b">
@@ -30975,7 +30975,7 @@
       </c>
       <c r="AX280" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY280" t="inlineStr"/>
@@ -33050,10 +33050,10 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>123920306</v>
+        <v>123920805</v>
       </c>
       <c r="B301" t="n">
-        <v>79406</v>
+        <v>78788</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
@@ -33066,21 +33066,21 @@
         </is>
       </c>
       <c r="E301" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I301" t="inlineStr"/>
@@ -33090,10 +33090,10 @@
         </is>
       </c>
       <c r="Q301" t="n">
-        <v>458976</v>
+        <v>459076</v>
       </c>
       <c r="R301" t="n">
-        <v>6808671</v>
+        <v>6808337</v>
       </c>
       <c r="S301" t="n">
         <v>10</v>
@@ -33120,12 +33120,12 @@
       </c>
       <c r="Y301" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA301" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD301" t="b">
@@ -33145,17 +33145,17 @@
       </c>
       <c r="AX301" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>123920550</v>
+        <v>123920306</v>
       </c>
       <c r="B302" t="n">
-        <v>78525</v>
+        <v>79406</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
@@ -33168,21 +33168,21 @@
         </is>
       </c>
       <c r="E302" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I302" t="inlineStr"/>
@@ -33192,10 +33192,10 @@
         </is>
       </c>
       <c r="Q302" t="n">
-        <v>459448</v>
+        <v>458976</v>
       </c>
       <c r="R302" t="n">
-        <v>6808388</v>
+        <v>6808671</v>
       </c>
       <c r="S302" t="n">
         <v>10</v>
@@ -33222,12 +33222,12 @@
       </c>
       <c r="Y302" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA302" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD302" t="b">
@@ -33247,17 +33247,17 @@
       </c>
       <c r="AX302" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>123920805</v>
+        <v>123920550</v>
       </c>
       <c r="B303" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
@@ -33270,21 +33270,21 @@
         </is>
       </c>
       <c r="E303" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I303" t="inlineStr"/>
@@ -33294,10 +33294,10 @@
         </is>
       </c>
       <c r="Q303" t="n">
-        <v>459076</v>
+        <v>459448</v>
       </c>
       <c r="R303" t="n">
-        <v>6808337</v>
+        <v>6808388</v>
       </c>
       <c r="S303" t="n">
         <v>10</v>
@@ -33356,10 +33356,10 @@
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>123866170</v>
+        <v>123920908</v>
       </c>
       <c r="B304" t="n">
-        <v>56700</v>
+        <v>92271</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
@@ -33372,42 +33372,34 @@
         </is>
       </c>
       <c r="E304" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I304" t="inlineStr"/>
-      <c r="K304" t="inlineStr"/>
-      <c r="L304" t="inlineStr"/>
-      <c r="M304" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N304" t="inlineStr"/>
       <c r="P304" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q304" t="n">
-        <v>459236</v>
+        <v>459439</v>
       </c>
       <c r="R304" t="n">
-        <v>6808707</v>
+        <v>6808385</v>
       </c>
       <c r="S304" t="n">
         <v>10</v>
@@ -33434,17 +33426,12 @@
       </c>
       <c r="Y304" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA304" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AC304" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD304" t="b">
@@ -33459,22 +33446,22 @@
       <c r="AT304" t="inlineStr"/>
       <c r="AW304" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX304" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>123920457</v>
+        <v>123920813</v>
       </c>
       <c r="B305" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
@@ -33483,43 +33470,38 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E305" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I305" t="inlineStr"/>
-      <c r="M305" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P305" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q305" t="n">
-        <v>458767</v>
+        <v>459237</v>
       </c>
       <c r="R305" t="n">
-        <v>6808746</v>
+        <v>6808364</v>
       </c>
       <c r="S305" t="n">
         <v>10</v>
@@ -33546,12 +33528,12 @@
       </c>
       <c r="Y305" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA305" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD305" t="b">
@@ -33571,17 +33553,17 @@
       </c>
       <c r="AX305" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>123920445</v>
+        <v>123920723</v>
       </c>
       <c r="B306" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C306" t="inlineStr">
         <is>
@@ -33590,43 +33572,38 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E306" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I306" t="inlineStr"/>
-      <c r="M306" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P306" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q306" t="n">
-        <v>459187</v>
+        <v>459760</v>
       </c>
       <c r="R306" t="n">
-        <v>6808368</v>
+        <v>6808280</v>
       </c>
       <c r="S306" t="n">
         <v>10</v>
@@ -33678,17 +33655,17 @@
       </c>
       <c r="AX306" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>123920598</v>
+        <v>123920388</v>
       </c>
       <c r="B307" t="n">
-        <v>78524</v>
+        <v>79377</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
@@ -33701,21 +33678,21 @@
         </is>
       </c>
       <c r="E307" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I307" t="inlineStr"/>
@@ -33725,10 +33702,10 @@
         </is>
       </c>
       <c r="Q307" t="n">
-        <v>459727</v>
+        <v>459257</v>
       </c>
       <c r="R307" t="n">
-        <v>6808344</v>
+        <v>6808639</v>
       </c>
       <c r="S307" t="n">
         <v>10</v>
@@ -33755,12 +33732,12 @@
       </c>
       <c r="Y307" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA307" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD307" t="b">
@@ -33780,17 +33757,17 @@
       </c>
       <c r="AX307" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>123920683</v>
+        <v>123920457</v>
       </c>
       <c r="B308" t="n">
-        <v>78788</v>
+        <v>56700</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
@@ -33799,38 +33776,43 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E308" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I308" t="inlineStr"/>
+      <c r="M308" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P308" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q308" t="n">
-        <v>459386</v>
+        <v>458767</v>
       </c>
       <c r="R308" t="n">
-        <v>6808640</v>
+        <v>6808746</v>
       </c>
       <c r="S308" t="n">
         <v>10</v>
@@ -33889,10 +33871,10 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>123920806</v>
+        <v>123920445</v>
       </c>
       <c r="B309" t="n">
-        <v>78788</v>
+        <v>56700</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
@@ -33901,38 +33883,43 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E309" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I309" t="inlineStr"/>
+      <c r="M309" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P309" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q309" t="n">
-        <v>459086</v>
+        <v>459187</v>
       </c>
       <c r="R309" t="n">
-        <v>6808349</v>
+        <v>6808368</v>
       </c>
       <c r="S309" t="n">
         <v>10</v>
@@ -33984,17 +33971,17 @@
       </c>
       <c r="AX309" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>123920908</v>
+        <v>123920598</v>
       </c>
       <c r="B310" t="n">
-        <v>92271</v>
+        <v>78524</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
@@ -34003,25 +33990,25 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E310" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I310" t="inlineStr"/>
@@ -34031,10 +34018,10 @@
         </is>
       </c>
       <c r="Q310" t="n">
-        <v>459439</v>
+        <v>459727</v>
       </c>
       <c r="R310" t="n">
-        <v>6808385</v>
+        <v>6808344</v>
       </c>
       <c r="S310" t="n">
         <v>10</v>
@@ -34093,7 +34080,7 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>123920813</v>
+        <v>123920683</v>
       </c>
       <c r="B311" t="n">
         <v>78788</v>
@@ -34133,10 +34120,10 @@
         </is>
       </c>
       <c r="Q311" t="n">
-        <v>459237</v>
+        <v>459386</v>
       </c>
       <c r="R311" t="n">
-        <v>6808364</v>
+        <v>6808640</v>
       </c>
       <c r="S311" t="n">
         <v>10</v>
@@ -34163,12 +34150,12 @@
       </c>
       <c r="Y311" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA311" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD311" t="b">
@@ -34188,14 +34175,14 @@
       </c>
       <c r="AX311" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>123920723</v>
+        <v>123920806</v>
       </c>
       <c r="B312" t="n">
         <v>78788</v>
@@ -34235,10 +34222,10 @@
         </is>
       </c>
       <c r="Q312" t="n">
-        <v>459760</v>
+        <v>459086</v>
       </c>
       <c r="R312" t="n">
-        <v>6808280</v>
+        <v>6808349</v>
       </c>
       <c r="S312" t="n">
         <v>10</v>
@@ -34297,10 +34284,10 @@
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>123920388</v>
+        <v>123866170</v>
       </c>
       <c r="B313" t="n">
-        <v>79377</v>
+        <v>56700</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
@@ -34309,38 +34296,46 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E313" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I313" t="inlineStr"/>
+      <c r="K313" t="inlineStr"/>
+      <c r="L313" t="inlineStr"/>
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N313" t="inlineStr"/>
       <c r="P313" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q313" t="n">
-        <v>459257</v>
+        <v>459236</v>
       </c>
       <c r="R313" t="n">
-        <v>6808639</v>
+        <v>6808707</v>
       </c>
       <c r="S313" t="n">
         <v>10</v>
@@ -34375,6 +34370,11 @@
           <t>2025-04-08</t>
         </is>
       </c>
+      <c r="AC313" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
+        </is>
+      </c>
       <c r="AD313" t="b">
         <v>0</v>
       </c>
@@ -34387,12 +34387,12 @@
       <c r="AT313" t="inlineStr"/>
       <c r="AW313" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX313" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY313" t="inlineStr"/>
@@ -36566,10 +36566,10 @@
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>123920309</v>
+        <v>123920802</v>
       </c>
       <c r="B335" t="n">
-        <v>79406</v>
+        <v>78788</v>
       </c>
       <c r="C335" t="inlineStr">
         <is>
@@ -36582,21 +36582,21 @@
         </is>
       </c>
       <c r="E335" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I335" t="inlineStr"/>
@@ -36606,10 +36606,10 @@
         </is>
       </c>
       <c r="Q335" t="n">
-        <v>459134</v>
+        <v>459050</v>
       </c>
       <c r="R335" t="n">
-        <v>6808662</v>
+        <v>6808338</v>
       </c>
       <c r="S335" t="n">
         <v>10</v>
@@ -36636,12 +36636,12 @@
       </c>
       <c r="Y335" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA335" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD335" t="b">
@@ -36661,14 +36661,14 @@
       </c>
       <c r="AX335" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>123920662</v>
+        <v>123920808</v>
       </c>
       <c r="B336" t="n">
         <v>78788</v>
@@ -36708,10 +36708,10 @@
         </is>
       </c>
       <c r="Q336" t="n">
-        <v>458749</v>
+        <v>459142</v>
       </c>
       <c r="R336" t="n">
-        <v>6808795</v>
+        <v>6808358</v>
       </c>
       <c r="S336" t="n">
         <v>10</v>
@@ -36738,12 +36738,12 @@
       </c>
       <c r="Y336" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA336" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD336" t="b">
@@ -36763,14 +36763,14 @@
       </c>
       <c r="AX336" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>123920315</v>
+        <v>123920300</v>
       </c>
       <c r="B337" t="n">
         <v>79406</v>
@@ -36810,10 +36810,10 @@
         </is>
       </c>
       <c r="Q337" t="n">
-        <v>459450</v>
+        <v>458749</v>
       </c>
       <c r="R337" t="n">
-        <v>6808625</v>
+        <v>6808795</v>
       </c>
       <c r="S337" t="n">
         <v>10</v>
@@ -36872,10 +36872,10 @@
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>123920802</v>
+        <v>123920309</v>
       </c>
       <c r="B338" t="n">
-        <v>78788</v>
+        <v>79406</v>
       </c>
       <c r="C338" t="inlineStr">
         <is>
@@ -36888,21 +36888,21 @@
         </is>
       </c>
       <c r="E338" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I338" t="inlineStr"/>
@@ -36912,10 +36912,10 @@
         </is>
       </c>
       <c r="Q338" t="n">
-        <v>459050</v>
+        <v>459134</v>
       </c>
       <c r="R338" t="n">
-        <v>6808338</v>
+        <v>6808662</v>
       </c>
       <c r="S338" t="n">
         <v>10</v>
@@ -36942,12 +36942,12 @@
       </c>
       <c r="Y338" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA338" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD338" t="b">
@@ -36967,14 +36967,14 @@
       </c>
       <c r="AX338" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>123920808</v>
+        <v>123920662</v>
       </c>
       <c r="B339" t="n">
         <v>78788</v>
@@ -37014,10 +37014,10 @@
         </is>
       </c>
       <c r="Q339" t="n">
-        <v>459142</v>
+        <v>458749</v>
       </c>
       <c r="R339" t="n">
-        <v>6808358</v>
+        <v>6808795</v>
       </c>
       <c r="S339" t="n">
         <v>10</v>
@@ -37044,12 +37044,12 @@
       </c>
       <c r="Y339" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA339" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD339" t="b">
@@ -37069,14 +37069,14 @@
       </c>
       <c r="AX339" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>123920300</v>
+        <v>123920315</v>
       </c>
       <c r="B340" t="n">
         <v>79406</v>
@@ -37116,10 +37116,10 @@
         </is>
       </c>
       <c r="Q340" t="n">
-        <v>458749</v>
+        <v>459450</v>
       </c>
       <c r="R340" t="n">
-        <v>6808795</v>
+        <v>6808625</v>
       </c>
       <c r="S340" t="n">
         <v>10</v>
@@ -38402,10 +38402,10 @@
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>123920314</v>
+        <v>123920814</v>
       </c>
       <c r="B353" t="n">
-        <v>79406</v>
+        <v>78788</v>
       </c>
       <c r="C353" t="inlineStr">
         <is>
@@ -38418,21 +38418,21 @@
         </is>
       </c>
       <c r="E353" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I353" t="inlineStr"/>
@@ -38442,10 +38442,10 @@
         </is>
       </c>
       <c r="Q353" t="n">
-        <v>459405</v>
+        <v>459244</v>
       </c>
       <c r="R353" t="n">
-        <v>6808632</v>
+        <v>6808386</v>
       </c>
       <c r="S353" t="n">
         <v>10</v>
@@ -38472,12 +38472,12 @@
       </c>
       <c r="Y353" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA353" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD353" t="b">
@@ -38497,14 +38497,14 @@
       </c>
       <c r="AX353" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>123920725</v>
+        <v>123920839</v>
       </c>
       <c r="B354" t="n">
         <v>78788</v>
@@ -38544,10 +38544,10 @@
         </is>
       </c>
       <c r="Q354" t="n">
-        <v>459665</v>
+        <v>459764</v>
       </c>
       <c r="R354" t="n">
-        <v>6808220</v>
+        <v>6808338</v>
       </c>
       <c r="S354" t="n">
         <v>10</v>
@@ -38606,10 +38606,10 @@
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>123920594</v>
+        <v>123920369</v>
       </c>
       <c r="B355" t="n">
-        <v>78524</v>
+        <v>78820</v>
       </c>
       <c r="C355" t="inlineStr">
         <is>
@@ -38622,21 +38622,21 @@
         </is>
       </c>
       <c r="E355" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I355" t="inlineStr"/>
@@ -38646,10 +38646,10 @@
         </is>
       </c>
       <c r="Q355" t="n">
-        <v>459274</v>
+        <v>458919</v>
       </c>
       <c r="R355" t="n">
-        <v>6808674</v>
+        <v>6808282</v>
       </c>
       <c r="S355" t="n">
         <v>10</v>
@@ -38676,12 +38676,12 @@
       </c>
       <c r="Y355" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA355" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD355" t="b">
@@ -38701,17 +38701,17 @@
       </c>
       <c r="AX355" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>123920597</v>
+        <v>123920314</v>
       </c>
       <c r="B356" t="n">
-        <v>78524</v>
+        <v>79406</v>
       </c>
       <c r="C356" t="inlineStr">
         <is>
@@ -38724,21 +38724,21 @@
         </is>
       </c>
       <c r="E356" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I356" t="inlineStr"/>
@@ -38748,10 +38748,10 @@
         </is>
       </c>
       <c r="Q356" t="n">
-        <v>459448</v>
+        <v>459405</v>
       </c>
       <c r="R356" t="n">
-        <v>6808388</v>
+        <v>6808632</v>
       </c>
       <c r="S356" t="n">
         <v>10</v>
@@ -38778,12 +38778,12 @@
       </c>
       <c r="Y356" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA356" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD356" t="b">
@@ -38803,17 +38803,17 @@
       </c>
       <c r="AX356" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>123920316</v>
+        <v>123920725</v>
       </c>
       <c r="B357" t="n">
-        <v>79406</v>
+        <v>78788</v>
       </c>
       <c r="C357" t="inlineStr">
         <is>
@@ -38826,21 +38826,21 @@
         </is>
       </c>
       <c r="E357" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I357" t="inlineStr"/>
@@ -38850,10 +38850,10 @@
         </is>
       </c>
       <c r="Q357" t="n">
-        <v>459455</v>
+        <v>459665</v>
       </c>
       <c r="R357" t="n">
-        <v>6808627</v>
+        <v>6808220</v>
       </c>
       <c r="S357" t="n">
         <v>10</v>
@@ -38880,12 +38880,12 @@
       </c>
       <c r="Y357" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA357" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD357" t="b">
@@ -38905,17 +38905,17 @@
       </c>
       <c r="AX357" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>123920807</v>
+        <v>123920594</v>
       </c>
       <c r="B358" t="n">
-        <v>78788</v>
+        <v>78524</v>
       </c>
       <c r="C358" t="inlineStr">
         <is>
@@ -38928,21 +38928,21 @@
         </is>
       </c>
       <c r="E358" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I358" t="inlineStr"/>
@@ -38952,10 +38952,10 @@
         </is>
       </c>
       <c r="Q358" t="n">
-        <v>459115</v>
+        <v>459274</v>
       </c>
       <c r="R358" t="n">
-        <v>6808339</v>
+        <v>6808674</v>
       </c>
       <c r="S358" t="n">
         <v>10</v>
@@ -38982,12 +38982,12 @@
       </c>
       <c r="Y358" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA358" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD358" t="b">
@@ -39007,17 +39007,17 @@
       </c>
       <c r="AX358" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>123920814</v>
+        <v>123920597</v>
       </c>
       <c r="B359" t="n">
-        <v>78788</v>
+        <v>78524</v>
       </c>
       <c r="C359" t="inlineStr">
         <is>
@@ -39030,21 +39030,21 @@
         </is>
       </c>
       <c r="E359" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I359" t="inlineStr"/>
@@ -39054,10 +39054,10 @@
         </is>
       </c>
       <c r="Q359" t="n">
-        <v>459244</v>
+        <v>459448</v>
       </c>
       <c r="R359" t="n">
-        <v>6808386</v>
+        <v>6808388</v>
       </c>
       <c r="S359" t="n">
         <v>10</v>
@@ -39116,10 +39116,10 @@
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>123920839</v>
+        <v>123920316</v>
       </c>
       <c r="B360" t="n">
-        <v>78788</v>
+        <v>79406</v>
       </c>
       <c r="C360" t="inlineStr">
         <is>
@@ -39132,21 +39132,21 @@
         </is>
       </c>
       <c r="E360" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I360" t="inlineStr"/>
@@ -39156,10 +39156,10 @@
         </is>
       </c>
       <c r="Q360" t="n">
-        <v>459764</v>
+        <v>459455</v>
       </c>
       <c r="R360" t="n">
-        <v>6808338</v>
+        <v>6808627</v>
       </c>
       <c r="S360" t="n">
         <v>10</v>
@@ -39186,12 +39186,12 @@
       </c>
       <c r="Y360" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA360" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD360" t="b">
@@ -39211,17 +39211,17 @@
       </c>
       <c r="AX360" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>123920369</v>
+        <v>123920807</v>
       </c>
       <c r="B361" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C361" t="inlineStr">
         <is>
@@ -39234,21 +39234,21 @@
         </is>
       </c>
       <c r="E361" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I361" t="inlineStr"/>
@@ -39258,10 +39258,10 @@
         </is>
       </c>
       <c r="Q361" t="n">
-        <v>458919</v>
+        <v>459115</v>
       </c>
       <c r="R361" t="n">
-        <v>6808282</v>
+        <v>6808339</v>
       </c>
       <c r="S361" t="n">
         <v>10</v>
@@ -39313,7 +39313,7 @@
       </c>
       <c r="AX361" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY361" t="inlineStr"/>
@@ -41574,7 +41574,7 @@
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>123920691</v>
+        <v>123920795</v>
       </c>
       <c r="B384" t="n">
         <v>78788</v>
@@ -41614,10 +41614,10 @@
         </is>
       </c>
       <c r="Q384" t="n">
-        <v>459688</v>
+        <v>458927</v>
       </c>
       <c r="R384" t="n">
-        <v>6808555</v>
+        <v>6808282</v>
       </c>
       <c r="S384" t="n">
         <v>10</v>
@@ -41644,12 +41644,12 @@
       </c>
       <c r="Y384" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA384" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD384" t="b">
@@ -41669,17 +41669,17 @@
       </c>
       <c r="AX384" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY384" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>123920447</v>
+        <v>123920821</v>
       </c>
       <c r="B385" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C385" t="inlineStr">
         <is>
@@ -41688,43 +41688,38 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E385" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I385" t="inlineStr"/>
-      <c r="M385" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P385" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q385" t="n">
-        <v>459190</v>
+        <v>459539</v>
       </c>
       <c r="R385" t="n">
-        <v>6808367</v>
+        <v>6808387</v>
       </c>
       <c r="S385" t="n">
         <v>10</v>
@@ -41776,17 +41771,17 @@
       </c>
       <c r="AX385" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>123920459</v>
+        <v>123920835</v>
       </c>
       <c r="B386" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C386" t="inlineStr">
         <is>
@@ -41795,43 +41790,38 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E386" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I386" t="inlineStr"/>
-      <c r="M386" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P386" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q386" t="n">
-        <v>459135</v>
+        <v>459699</v>
       </c>
       <c r="R386" t="n">
-        <v>6808663</v>
+        <v>6808338</v>
       </c>
       <c r="S386" t="n">
         <v>10</v>
@@ -41858,12 +41848,12 @@
       </c>
       <c r="Y386" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA386" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD386" t="b">
@@ -41883,17 +41873,17 @@
       </c>
       <c r="AX386" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY386" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>123920407</v>
+        <v>123920691</v>
       </c>
       <c r="B387" t="n">
-        <v>79377</v>
+        <v>78788</v>
       </c>
       <c r="C387" t="inlineStr">
         <is>
@@ -41906,21 +41896,21 @@
         </is>
       </c>
       <c r="E387" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I387" t="inlineStr"/>
@@ -41930,10 +41920,10 @@
         </is>
       </c>
       <c r="Q387" t="n">
-        <v>459574</v>
+        <v>459688</v>
       </c>
       <c r="R387" t="n">
-        <v>6808268</v>
+        <v>6808555</v>
       </c>
       <c r="S387" t="n">
         <v>10</v>
@@ -41960,12 +41950,12 @@
       </c>
       <c r="Y387" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA387" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD387" t="b">
@@ -41985,17 +41975,17 @@
       </c>
       <c r="AX387" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>123920406</v>
+        <v>123920447</v>
       </c>
       <c r="B388" t="n">
-        <v>79377</v>
+        <v>56700</v>
       </c>
       <c r="C388" t="inlineStr">
         <is>
@@ -42004,38 +41994,43 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E388" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I388" t="inlineStr"/>
+      <c r="M388" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P388" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q388" t="n">
-        <v>459448</v>
+        <v>459190</v>
       </c>
       <c r="R388" t="n">
-        <v>6808388</v>
+        <v>6808367</v>
       </c>
       <c r="S388" t="n">
         <v>10</v>
@@ -42094,10 +42089,10 @@
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>123920795</v>
+        <v>123920459</v>
       </c>
       <c r="B389" t="n">
-        <v>78788</v>
+        <v>56700</v>
       </c>
       <c r="C389" t="inlineStr">
         <is>
@@ -42106,38 +42101,43 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E389" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I389" t="inlineStr"/>
+      <c r="M389" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P389" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q389" t="n">
-        <v>458927</v>
+        <v>459135</v>
       </c>
       <c r="R389" t="n">
-        <v>6808282</v>
+        <v>6808663</v>
       </c>
       <c r="S389" t="n">
         <v>10</v>
@@ -42164,12 +42164,12 @@
       </c>
       <c r="Y389" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA389" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD389" t="b">
@@ -42189,17 +42189,17 @@
       </c>
       <c r="AX389" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY389" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>123920821</v>
+        <v>123920407</v>
       </c>
       <c r="B390" t="n">
-        <v>78788</v>
+        <v>79377</v>
       </c>
       <c r="C390" t="inlineStr">
         <is>
@@ -42212,21 +42212,21 @@
         </is>
       </c>
       <c r="E390" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I390" t="inlineStr"/>
@@ -42236,10 +42236,10 @@
         </is>
       </c>
       <c r="Q390" t="n">
-        <v>459539</v>
+        <v>459574</v>
       </c>
       <c r="R390" t="n">
-        <v>6808387</v>
+        <v>6808268</v>
       </c>
       <c r="S390" t="n">
         <v>10</v>
@@ -42291,17 +42291,17 @@
       </c>
       <c r="AX390" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY390" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" t="n">
-        <v>123920835</v>
+        <v>123920406</v>
       </c>
       <c r="B391" t="n">
-        <v>78788</v>
+        <v>79377</v>
       </c>
       <c r="C391" t="inlineStr">
         <is>
@@ -42314,21 +42314,21 @@
         </is>
       </c>
       <c r="E391" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I391" t="inlineStr"/>
@@ -42338,10 +42338,10 @@
         </is>
       </c>
       <c r="Q391" t="n">
-        <v>459699</v>
+        <v>459448</v>
       </c>
       <c r="R391" t="n">
-        <v>6808338</v>
+        <v>6808388</v>
       </c>
       <c r="S391" t="n">
         <v>10</v>
@@ -42393,7 +42393,7 @@
       </c>
       <c r="AX391" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY391" t="inlineStr"/>
@@ -43318,10 +43318,10 @@
     </row>
     <row r="401">
       <c r="A401" t="n">
-        <v>123920935</v>
+        <v>123920939</v>
       </c>
       <c r="B401" t="n">
-        <v>78433</v>
+        <v>78172</v>
       </c>
       <c r="C401" t="inlineStr">
         <is>
@@ -43334,21 +43334,21 @@
         </is>
       </c>
       <c r="E401" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I401" t="inlineStr"/>
@@ -43358,10 +43358,10 @@
         </is>
       </c>
       <c r="Q401" t="n">
-        <v>459423</v>
+        <v>459429</v>
       </c>
       <c r="R401" t="n">
-        <v>6808389</v>
+        <v>6808646</v>
       </c>
       <c r="S401" t="n">
         <v>10</v>
@@ -43388,12 +43388,12 @@
       </c>
       <c r="Y401" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA401" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD401" t="b">
@@ -43413,17 +43413,17 @@
       </c>
       <c r="AX401" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY401" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" t="n">
-        <v>123920576</v>
+        <v>123920798</v>
       </c>
       <c r="B402" t="n">
-        <v>80741</v>
+        <v>78788</v>
       </c>
       <c r="C402" t="inlineStr">
         <is>
@@ -43436,21 +43436,21 @@
         </is>
       </c>
       <c r="E402" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I402" t="inlineStr"/>
@@ -43460,10 +43460,10 @@
         </is>
       </c>
       <c r="Q402" t="n">
-        <v>459654</v>
+        <v>458998</v>
       </c>
       <c r="R402" t="n">
-        <v>6808298</v>
+        <v>6808288</v>
       </c>
       <c r="S402" t="n">
         <v>10</v>
@@ -43522,10 +43522,10 @@
     </row>
     <row r="403">
       <c r="A403" t="n">
-        <v>123920939</v>
+        <v>123920658</v>
       </c>
       <c r="B403" t="n">
-        <v>78172</v>
+        <v>78788</v>
       </c>
       <c r="C403" t="inlineStr">
         <is>
@@ -43538,21 +43538,21 @@
         </is>
       </c>
       <c r="E403" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H403" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I403" t="inlineStr"/>
@@ -43562,10 +43562,10 @@
         </is>
       </c>
       <c r="Q403" t="n">
-        <v>459429</v>
+        <v>458778</v>
       </c>
       <c r="R403" t="n">
-        <v>6808646</v>
+        <v>6808585</v>
       </c>
       <c r="S403" t="n">
         <v>10</v>
@@ -43624,7 +43624,7 @@
     </row>
     <row r="404">
       <c r="A404" t="n">
-        <v>123920798</v>
+        <v>123920664</v>
       </c>
       <c r="B404" t="n">
         <v>78788</v>
@@ -43664,10 +43664,10 @@
         </is>
       </c>
       <c r="Q404" t="n">
-        <v>458998</v>
+        <v>458750</v>
       </c>
       <c r="R404" t="n">
-        <v>6808288</v>
+        <v>6808837</v>
       </c>
       <c r="S404" t="n">
         <v>10</v>
@@ -43694,12 +43694,12 @@
       </c>
       <c r="Y404" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA404" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD404" t="b">
@@ -43719,17 +43719,17 @@
       </c>
       <c r="AX404" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY404" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" t="n">
-        <v>123920658</v>
+        <v>123920935</v>
       </c>
       <c r="B405" t="n">
-        <v>78788</v>
+        <v>78433</v>
       </c>
       <c r="C405" t="inlineStr">
         <is>
@@ -43742,21 +43742,21 @@
         </is>
       </c>
       <c r="E405" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I405" t="inlineStr"/>
@@ -43766,10 +43766,10 @@
         </is>
       </c>
       <c r="Q405" t="n">
-        <v>458778</v>
+        <v>459423</v>
       </c>
       <c r="R405" t="n">
-        <v>6808585</v>
+        <v>6808389</v>
       </c>
       <c r="S405" t="n">
         <v>10</v>
@@ -43796,12 +43796,12 @@
       </c>
       <c r="Y405" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA405" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD405" t="b">
@@ -43821,17 +43821,17 @@
       </c>
       <c r="AX405" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY405" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" t="n">
-        <v>123920664</v>
+        <v>123920576</v>
       </c>
       <c r="B406" t="n">
-        <v>78788</v>
+        <v>80741</v>
       </c>
       <c r="C406" t="inlineStr">
         <is>
@@ -43844,21 +43844,21 @@
         </is>
       </c>
       <c r="E406" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I406" t="inlineStr"/>
@@ -43868,10 +43868,10 @@
         </is>
       </c>
       <c r="Q406" t="n">
-        <v>458750</v>
+        <v>459654</v>
       </c>
       <c r="R406" t="n">
-        <v>6808837</v>
+        <v>6808298</v>
       </c>
       <c r="S406" t="n">
         <v>10</v>
@@ -43898,12 +43898,12 @@
       </c>
       <c r="Y406" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA406" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD406" t="b">
@@ -43923,7 +43923,7 @@
       </c>
       <c r="AX406" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY406" t="inlineStr"/>

--- a/artfynd/A 61324-2022 artfynd.xlsx
+++ b/artfynd/A 61324-2022 artfynd.xlsx
@@ -28519,10 +28519,10 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>123920598</v>
+        <v>123920448</v>
       </c>
       <c r="B257" t="n">
-        <v>78546</v>
+        <v>56722</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
@@ -28531,38 +28531,43 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P257" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>459727</v>
+        <v>458790</v>
       </c>
       <c r="R257" t="n">
-        <v>6808344</v>
+        <v>6808708</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -28589,12 +28594,12 @@
       </c>
       <c r="Y257" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA257" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD257" t="b">
@@ -28614,17 +28619,17 @@
       </c>
       <c r="AX257" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>123920798</v>
+        <v>123920451</v>
       </c>
       <c r="B258" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
@@ -28633,38 +28638,43 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P258" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>458998</v>
+        <v>459257</v>
       </c>
       <c r="R258" t="n">
-        <v>6808288</v>
+        <v>6808663</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -28691,12 +28701,12 @@
       </c>
       <c r="Y258" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA258" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD258" t="b">
@@ -28716,17 +28726,17 @@
       </c>
       <c r="AX258" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>123920658</v>
+        <v>123920602</v>
       </c>
       <c r="B259" t="n">
-        <v>78810</v>
+        <v>56714</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
@@ -28739,34 +28749,42 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
+      <c r="K259" t="inlineStr"/>
+      <c r="L259" t="inlineStr"/>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N259" t="inlineStr"/>
       <c r="P259" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>458778</v>
+        <v>459098</v>
       </c>
       <c r="R259" t="n">
-        <v>6808585</v>
+        <v>6808349</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -28793,12 +28811,12 @@
       </c>
       <c r="Y259" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA259" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD259" t="b">
@@ -28818,14 +28836,14 @@
       </c>
       <c r="AX259" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>123920838</v>
+        <v>123920679</v>
       </c>
       <c r="B260" t="n">
         <v>78810</v>
@@ -28865,10 +28883,10 @@
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>459758</v>
+        <v>459257</v>
       </c>
       <c r="R260" t="n">
-        <v>6808333</v>
+        <v>6808663</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -28895,12 +28913,12 @@
       </c>
       <c r="Y260" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA260" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD260" t="b">
@@ -28920,17 +28938,17 @@
       </c>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>123920723</v>
+        <v>123920306</v>
       </c>
       <c r="B261" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
@@ -28943,21 +28961,21 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
@@ -28967,10 +28985,10 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>459760</v>
+        <v>458976</v>
       </c>
       <c r="R261" t="n">
-        <v>6808280</v>
+        <v>6808671</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -28997,12 +29015,12 @@
       </c>
       <c r="Y261" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA261" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD261" t="b">
@@ -29022,17 +29040,17 @@
       </c>
       <c r="AX261" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>123920602</v>
+        <v>123920798</v>
       </c>
       <c r="B262" t="n">
-        <v>56714</v>
+        <v>78810</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
@@ -29045,42 +29063,34 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
-      <c r="K262" t="inlineStr"/>
-      <c r="L262" t="inlineStr"/>
-      <c r="M262" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N262" t="inlineStr"/>
       <c r="P262" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>459098</v>
+        <v>458998</v>
       </c>
       <c r="R262" t="n">
-        <v>6808349</v>
+        <v>6808288</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -29139,10 +29149,10 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>123920393</v>
+        <v>123920658</v>
       </c>
       <c r="B263" t="n">
-        <v>79399</v>
+        <v>78810</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
@@ -29155,21 +29165,21 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I263" t="inlineStr"/>
@@ -29179,10 +29189,10 @@
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>459347</v>
+        <v>458778</v>
       </c>
       <c r="R263" t="n">
-        <v>6808645</v>
+        <v>6808585</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -29241,7 +29251,7 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>123920679</v>
+        <v>123920838</v>
       </c>
       <c r="B264" t="n">
         <v>78810</v>
@@ -29281,10 +29291,10 @@
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>459257</v>
+        <v>459758</v>
       </c>
       <c r="R264" t="n">
-        <v>6808663</v>
+        <v>6808333</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -29311,12 +29321,12 @@
       </c>
       <c r="Y264" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA264" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD264" t="b">
@@ -29336,17 +29346,17 @@
       </c>
       <c r="AX264" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>123920306</v>
+        <v>123920723</v>
       </c>
       <c r="B265" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
@@ -29359,21 +29369,21 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I265" t="inlineStr"/>
@@ -29383,10 +29393,10 @@
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>458976</v>
+        <v>459760</v>
       </c>
       <c r="R265" t="n">
-        <v>6808671</v>
+        <v>6808280</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -29413,12 +29423,12 @@
       </c>
       <c r="Y265" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA265" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD265" t="b">
@@ -29438,17 +29448,17 @@
       </c>
       <c r="AX265" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>123920448</v>
+        <v>123920598</v>
       </c>
       <c r="B266" t="n">
-        <v>56722</v>
+        <v>78546</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
@@ -29457,43 +29467,38 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E266" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I266" t="inlineStr"/>
-      <c r="M266" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P266" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>458790</v>
+        <v>459727</v>
       </c>
       <c r="R266" t="n">
-        <v>6808708</v>
+        <v>6808344</v>
       </c>
       <c r="S266" t="n">
         <v>10</v>
@@ -29520,12 +29525,12 @@
       </c>
       <c r="Y266" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA266" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD266" t="b">
@@ -29545,17 +29550,17 @@
       </c>
       <c r="AX266" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>123920451</v>
+        <v>123920393</v>
       </c>
       <c r="B267" t="n">
-        <v>56722</v>
+        <v>79399</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
@@ -29564,43 +29569,38 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E267" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I267" t="inlineStr"/>
-      <c r="M267" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P267" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>459257</v>
+        <v>459347</v>
       </c>
       <c r="R267" t="n">
-        <v>6808663</v>
+        <v>6808645</v>
       </c>
       <c r="S267" t="n">
         <v>10</v>
@@ -30271,10 +30271,10 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>123920910</v>
+        <v>123920315</v>
       </c>
       <c r="B274" t="n">
-        <v>92293</v>
+        <v>79428</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
@@ -30283,25 +30283,25 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
@@ -30311,10 +30311,10 @@
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>458914</v>
+        <v>459450</v>
       </c>
       <c r="R274" t="n">
-        <v>6808283</v>
+        <v>6808625</v>
       </c>
       <c r="S274" t="n">
         <v>10</v>
@@ -30341,12 +30341,12 @@
       </c>
       <c r="Y274" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA274" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD274" t="b">
@@ -30366,17 +30366,17 @@
       </c>
       <c r="AX274" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Niklas Rehn, Håkan Thenander, lennart karlsson, Anders Heggestad</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>123920315</v>
+        <v>123920662</v>
       </c>
       <c r="B275" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
@@ -30389,21 +30389,21 @@
         </is>
       </c>
       <c r="E275" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I275" t="inlineStr"/>
@@ -30413,10 +30413,10 @@
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>459450</v>
+        <v>458749</v>
       </c>
       <c r="R275" t="n">
-        <v>6808625</v>
+        <v>6808795</v>
       </c>
       <c r="S275" t="n">
         <v>10</v>
@@ -30475,10 +30475,10 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>123920662</v>
+        <v>123920910</v>
       </c>
       <c r="B276" t="n">
-        <v>78810</v>
+        <v>92293</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
@@ -30487,25 +30487,25 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
@@ -30515,10 +30515,10 @@
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>458749</v>
+        <v>458914</v>
       </c>
       <c r="R276" t="n">
-        <v>6808795</v>
+        <v>6808283</v>
       </c>
       <c r="S276" t="n">
         <v>10</v>
@@ -30545,12 +30545,12 @@
       </c>
       <c r="Y276" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA276" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD276" t="b">
@@ -30570,17 +30570,17 @@
       </c>
       <c r="AX276" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Niklas Rehn, Håkan Thenander, lennart karlsson, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>123920911</v>
+        <v>123920443</v>
       </c>
       <c r="B277" t="n">
-        <v>92293</v>
+        <v>56722</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
@@ -30593,34 +30593,39 @@
         </is>
       </c>
       <c r="E277" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I277" t="inlineStr"/>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P277" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>459628</v>
+        <v>459076</v>
       </c>
       <c r="R277" t="n">
-        <v>6808232</v>
+        <v>6808337</v>
       </c>
       <c r="S277" t="n">
         <v>10</v>
@@ -30672,17 +30677,17 @@
       </c>
       <c r="AX277" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Niklas Rehn, Håkan Thenander, lennart karlsson, Anders Heggestad</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>123920795</v>
+        <v>123920392</v>
       </c>
       <c r="B278" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
@@ -30695,21 +30700,21 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
@@ -30719,10 +30724,10 @@
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>458927</v>
+        <v>459317</v>
       </c>
       <c r="R278" t="n">
-        <v>6808282</v>
+        <v>6808694</v>
       </c>
       <c r="S278" t="n">
         <v>10</v>
@@ -30749,12 +30754,12 @@
       </c>
       <c r="Y278" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA278" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD278" t="b">
@@ -30774,14 +30779,14 @@
       </c>
       <c r="AX278" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>123920813</v>
+        <v>123920795</v>
       </c>
       <c r="B279" t="n">
         <v>78810</v>
@@ -30821,10 +30826,10 @@
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>459237</v>
+        <v>458927</v>
       </c>
       <c r="R279" t="n">
-        <v>6808364</v>
+        <v>6808282</v>
       </c>
       <c r="S279" t="n">
         <v>10</v>
@@ -30883,10 +30888,10 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>123920443</v>
+        <v>123920689</v>
       </c>
       <c r="B280" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
@@ -30895,43 +30900,38 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E280" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I280" t="inlineStr"/>
-      <c r="M280" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P280" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>459076</v>
+        <v>459656</v>
       </c>
       <c r="R280" t="n">
-        <v>6808337</v>
+        <v>6808574</v>
       </c>
       <c r="S280" t="n">
         <v>10</v>
@@ -30958,12 +30958,12 @@
       </c>
       <c r="Y280" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA280" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD280" t="b">
@@ -30983,17 +30983,17 @@
       </c>
       <c r="AX280" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>123920392</v>
+        <v>123920911</v>
       </c>
       <c r="B281" t="n">
-        <v>79399</v>
+        <v>92293</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
@@ -31002,25 +31002,25 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E281" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I281" t="inlineStr"/>
@@ -31030,10 +31030,10 @@
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>459317</v>
+        <v>459628</v>
       </c>
       <c r="R281" t="n">
-        <v>6808694</v>
+        <v>6808232</v>
       </c>
       <c r="S281" t="n">
         <v>10</v>
@@ -31060,12 +31060,12 @@
       </c>
       <c r="Y281" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA281" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD281" t="b">
@@ -31085,14 +31085,14 @@
       </c>
       <c r="AX281" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Niklas Rehn, Håkan Thenander, lennart karlsson, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>123920689</v>
+        <v>123920813</v>
       </c>
       <c r="B282" t="n">
         <v>78810</v>
@@ -31132,10 +31132,10 @@
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>459656</v>
+        <v>459237</v>
       </c>
       <c r="R282" t="n">
-        <v>6808574</v>
+        <v>6808364</v>
       </c>
       <c r="S282" t="n">
         <v>10</v>
@@ -31162,12 +31162,12 @@
       </c>
       <c r="Y282" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA282" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD282" t="b">
@@ -31187,7 +31187,7 @@
       </c>
       <c r="AX282" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY282" t="inlineStr"/>
@@ -32130,10 +32130,10 @@
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>123920458</v>
+        <v>123920676</v>
       </c>
       <c r="B292" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C292" t="inlineStr">
         <is>
@@ -32142,43 +32142,38 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E292" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I292" t="inlineStr"/>
-      <c r="M292" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P292" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q292" t="n">
-        <v>458745</v>
+        <v>459081</v>
       </c>
       <c r="R292" t="n">
-        <v>6808854</v>
+        <v>6808680</v>
       </c>
       <c r="S292" t="n">
         <v>10</v>
@@ -32237,10 +32232,10 @@
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>123920450</v>
+        <v>123920724</v>
       </c>
       <c r="B293" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C293" t="inlineStr">
         <is>
@@ -32249,43 +32244,38 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E293" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I293" t="inlineStr"/>
-      <c r="M293" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P293" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q293" t="n">
-        <v>459083</v>
+        <v>459751</v>
       </c>
       <c r="R293" t="n">
-        <v>6808668</v>
+        <v>6808270</v>
       </c>
       <c r="S293" t="n">
         <v>10</v>
@@ -32312,12 +32302,12 @@
       </c>
       <c r="Y293" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA293" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD293" t="b">
@@ -32337,17 +32327,17 @@
       </c>
       <c r="AX293" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>123920461</v>
+        <v>123920669</v>
       </c>
       <c r="B294" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C294" t="inlineStr">
         <is>
@@ -32356,43 +32346,38 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E294" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I294" t="inlineStr"/>
-      <c r="M294" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P294" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q294" t="n">
-        <v>459317</v>
+        <v>458872</v>
       </c>
       <c r="R294" t="n">
-        <v>6808694</v>
+        <v>6808710</v>
       </c>
       <c r="S294" t="n">
         <v>10</v>
@@ -32451,10 +32436,10 @@
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>123920594</v>
+        <v>123920691</v>
       </c>
       <c r="B295" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C295" t="inlineStr">
         <is>
@@ -32467,21 +32452,21 @@
         </is>
       </c>
       <c r="E295" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I295" t="inlineStr"/>
@@ -32491,10 +32476,10 @@
         </is>
       </c>
       <c r="Q295" t="n">
-        <v>459274</v>
+        <v>459688</v>
       </c>
       <c r="R295" t="n">
-        <v>6808674</v>
+        <v>6808555</v>
       </c>
       <c r="S295" t="n">
         <v>10</v>
@@ -32553,10 +32538,10 @@
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>123920380</v>
+        <v>123920594</v>
       </c>
       <c r="B296" t="n">
-        <v>79428</v>
+        <v>78546</v>
       </c>
       <c r="C296" t="inlineStr">
         <is>
@@ -32569,21 +32554,21 @@
         </is>
       </c>
       <c r="E296" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I296" t="inlineStr"/>
@@ -32593,10 +32578,10 @@
         </is>
       </c>
       <c r="Q296" t="n">
-        <v>459217</v>
+        <v>459274</v>
       </c>
       <c r="R296" t="n">
-        <v>6808383</v>
+        <v>6808674</v>
       </c>
       <c r="S296" t="n">
         <v>10</v>
@@ -32623,12 +32608,12 @@
       </c>
       <c r="Y296" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA296" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD296" t="b">
@@ -32648,17 +32633,17 @@
       </c>
       <c r="AX296" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>123920676</v>
+        <v>123920380</v>
       </c>
       <c r="B297" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C297" t="inlineStr">
         <is>
@@ -32671,21 +32656,21 @@
         </is>
       </c>
       <c r="E297" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I297" t="inlineStr"/>
@@ -32695,10 +32680,10 @@
         </is>
       </c>
       <c r="Q297" t="n">
-        <v>459081</v>
+        <v>459217</v>
       </c>
       <c r="R297" t="n">
-        <v>6808680</v>
+        <v>6808383</v>
       </c>
       <c r="S297" t="n">
         <v>10</v>
@@ -32725,12 +32710,12 @@
       </c>
       <c r="Y297" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA297" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD297" t="b">
@@ -32750,17 +32735,17 @@
       </c>
       <c r="AX297" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>123920724</v>
+        <v>123920458</v>
       </c>
       <c r="B298" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C298" t="inlineStr">
         <is>
@@ -32769,38 +32754,43 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E298" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I298" t="inlineStr"/>
+      <c r="M298" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P298" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q298" t="n">
-        <v>459751</v>
+        <v>458745</v>
       </c>
       <c r="R298" t="n">
-        <v>6808270</v>
+        <v>6808854</v>
       </c>
       <c r="S298" t="n">
         <v>10</v>
@@ -32827,12 +32817,12 @@
       </c>
       <c r="Y298" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA298" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD298" t="b">
@@ -32852,17 +32842,17 @@
       </c>
       <c r="AX298" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>123920669</v>
+        <v>123920450</v>
       </c>
       <c r="B299" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C299" t="inlineStr">
         <is>
@@ -32871,38 +32861,43 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E299" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I299" t="inlineStr"/>
+      <c r="M299" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P299" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q299" t="n">
-        <v>458872</v>
+        <v>459083</v>
       </c>
       <c r="R299" t="n">
-        <v>6808710</v>
+        <v>6808668</v>
       </c>
       <c r="S299" t="n">
         <v>10</v>
@@ -32961,10 +32956,10 @@
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>123920691</v>
+        <v>123920461</v>
       </c>
       <c r="B300" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C300" t="inlineStr">
         <is>
@@ -32973,38 +32968,43 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E300" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I300" t="inlineStr"/>
+      <c r="M300" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P300" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q300" t="n">
-        <v>459688</v>
+        <v>459317</v>
       </c>
       <c r="R300" t="n">
-        <v>6808555</v>
+        <v>6808694</v>
       </c>
       <c r="S300" t="n">
         <v>10</v>
@@ -33063,10 +33063,10 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>123920548</v>
+        <v>123920818</v>
       </c>
       <c r="B301" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
@@ -33079,21 +33079,21 @@
         </is>
       </c>
       <c r="E301" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I301" t="inlineStr"/>
@@ -33103,10 +33103,10 @@
         </is>
       </c>
       <c r="Q301" t="n">
-        <v>459139</v>
+        <v>459458</v>
       </c>
       <c r="R301" t="n">
-        <v>6808358</v>
+        <v>6808385</v>
       </c>
       <c r="S301" t="n">
         <v>10</v>
@@ -33165,10 +33165,10 @@
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>123920386</v>
+        <v>123920829</v>
       </c>
       <c r="B302" t="n">
-        <v>79399</v>
+        <v>78810</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
@@ -33181,21 +33181,21 @@
         </is>
       </c>
       <c r="E302" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I302" t="inlineStr"/>
@@ -33205,10 +33205,10 @@
         </is>
       </c>
       <c r="Q302" t="n">
-        <v>458872</v>
+        <v>459622</v>
       </c>
       <c r="R302" t="n">
-        <v>6808771</v>
+        <v>6808222</v>
       </c>
       <c r="S302" t="n">
         <v>10</v>
@@ -33235,12 +33235,12 @@
       </c>
       <c r="Y302" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA302" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD302" t="b">
@@ -33260,17 +33260,17 @@
       </c>
       <c r="AX302" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>123920818</v>
+        <v>123920300</v>
       </c>
       <c r="B303" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
@@ -33283,21 +33283,21 @@
         </is>
       </c>
       <c r="E303" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I303" t="inlineStr"/>
@@ -33307,10 +33307,10 @@
         </is>
       </c>
       <c r="Q303" t="n">
-        <v>459458</v>
+        <v>458749</v>
       </c>
       <c r="R303" t="n">
-        <v>6808385</v>
+        <v>6808795</v>
       </c>
       <c r="S303" t="n">
         <v>10</v>
@@ -33337,12 +33337,12 @@
       </c>
       <c r="Y303" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA303" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD303" t="b">
@@ -33362,17 +33362,17 @@
       </c>
       <c r="AX303" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>123920829</v>
+        <v>123920548</v>
       </c>
       <c r="B304" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
@@ -33385,21 +33385,21 @@
         </is>
       </c>
       <c r="E304" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I304" t="inlineStr"/>
@@ -33409,10 +33409,10 @@
         </is>
       </c>
       <c r="Q304" t="n">
-        <v>459622</v>
+        <v>459139</v>
       </c>
       <c r="R304" t="n">
-        <v>6808222</v>
+        <v>6808358</v>
       </c>
       <c r="S304" t="n">
         <v>10</v>
@@ -33471,10 +33471,10 @@
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>123920300</v>
+        <v>123920386</v>
       </c>
       <c r="B305" t="n">
-        <v>79428</v>
+        <v>79399</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
@@ -33487,21 +33487,21 @@
         </is>
       </c>
       <c r="E305" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I305" t="inlineStr"/>
@@ -33511,10 +33511,10 @@
         </is>
       </c>
       <c r="Q305" t="n">
-        <v>458749</v>
+        <v>458872</v>
       </c>
       <c r="R305" t="n">
-        <v>6808795</v>
+        <v>6808771</v>
       </c>
       <c r="S305" t="n">
         <v>10</v>
@@ -35725,10 +35725,10 @@
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>123920445</v>
+        <v>123920677</v>
       </c>
       <c r="B327" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C327" t="inlineStr">
         <is>
@@ -35737,43 +35737,38 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E327" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I327" t="inlineStr"/>
-      <c r="M327" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P327" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q327" t="n">
-        <v>459187</v>
+        <v>459121</v>
       </c>
       <c r="R327" t="n">
-        <v>6808368</v>
+        <v>6808649</v>
       </c>
       <c r="S327" t="n">
         <v>10</v>
@@ -35800,12 +35795,12 @@
       </c>
       <c r="Y327" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA327" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD327" t="b">
@@ -35825,14 +35820,14 @@
       </c>
       <c r="AX327" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>123920677</v>
+        <v>123920805</v>
       </c>
       <c r="B328" t="n">
         <v>78810</v>
@@ -35872,10 +35867,10 @@
         </is>
       </c>
       <c r="Q328" t="n">
-        <v>459121</v>
+        <v>459076</v>
       </c>
       <c r="R328" t="n">
-        <v>6808649</v>
+        <v>6808337</v>
       </c>
       <c r="S328" t="n">
         <v>10</v>
@@ -35902,12 +35897,12 @@
       </c>
       <c r="Y328" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA328" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD328" t="b">
@@ -35927,14 +35922,14 @@
       </c>
       <c r="AX328" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>123920805</v>
+        <v>123920811</v>
       </c>
       <c r="B329" t="n">
         <v>78810</v>
@@ -35974,10 +35969,10 @@
         </is>
       </c>
       <c r="Q329" t="n">
-        <v>459076</v>
+        <v>459218</v>
       </c>
       <c r="R329" t="n">
-        <v>6808337</v>
+        <v>6808375</v>
       </c>
       <c r="S329" t="n">
         <v>10</v>
@@ -36036,10 +36031,10 @@
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>123920811</v>
+        <v>123920403</v>
       </c>
       <c r="B330" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C330" t="inlineStr">
         <is>
@@ -36052,21 +36047,21 @@
         </is>
       </c>
       <c r="E330" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I330" t="inlineStr"/>
@@ -36076,10 +36071,10 @@
         </is>
       </c>
       <c r="Q330" t="n">
-        <v>459218</v>
+        <v>458928</v>
       </c>
       <c r="R330" t="n">
-        <v>6808375</v>
+        <v>6808283</v>
       </c>
       <c r="S330" t="n">
         <v>10</v>
@@ -36131,17 +36126,17 @@
       </c>
       <c r="AX330" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>123920403</v>
+        <v>123920445</v>
       </c>
       <c r="B331" t="n">
-        <v>79399</v>
+        <v>56722</v>
       </c>
       <c r="C331" t="inlineStr">
         <is>
@@ -36150,38 +36145,43 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E331" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I331" t="inlineStr"/>
+      <c r="M331" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P331" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q331" t="n">
-        <v>458928</v>
+        <v>459187</v>
       </c>
       <c r="R331" t="n">
-        <v>6808283</v>
+        <v>6808368</v>
       </c>
       <c r="S331" t="n">
         <v>10</v>
@@ -36240,10 +36240,10 @@
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>123920684</v>
+        <v>123920304</v>
       </c>
       <c r="B332" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C332" t="inlineStr">
         <is>
@@ -36256,21 +36256,21 @@
         </is>
       </c>
       <c r="E332" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I332" t="inlineStr"/>
@@ -36280,10 +36280,10 @@
         </is>
       </c>
       <c r="Q332" t="n">
-        <v>459414</v>
+        <v>458899</v>
       </c>
       <c r="R332" t="n">
-        <v>6808641</v>
+        <v>6808695</v>
       </c>
       <c r="S332" t="n">
         <v>10</v>
@@ -36342,10 +36342,10 @@
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>123920304</v>
+        <v>123920803</v>
       </c>
       <c r="B333" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C333" t="inlineStr">
         <is>
@@ -36358,21 +36358,21 @@
         </is>
       </c>
       <c r="E333" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I333" t="inlineStr"/>
@@ -36382,10 +36382,10 @@
         </is>
       </c>
       <c r="Q333" t="n">
-        <v>458899</v>
+        <v>459061</v>
       </c>
       <c r="R333" t="n">
-        <v>6808695</v>
+        <v>6808332</v>
       </c>
       <c r="S333" t="n">
         <v>10</v>
@@ -36412,12 +36412,12 @@
       </c>
       <c r="Y333" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA333" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD333" t="b">
@@ -36437,17 +36437,17 @@
       </c>
       <c r="AX333" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>123920449</v>
+        <v>123920408</v>
       </c>
       <c r="B334" t="n">
-        <v>56722</v>
+        <v>79399</v>
       </c>
       <c r="C334" t="inlineStr">
         <is>
@@ -36456,43 +36456,38 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E334" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I334" t="inlineStr"/>
-      <c r="M334" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P334" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q334" t="n">
-        <v>458862</v>
+        <v>459598</v>
       </c>
       <c r="R334" t="n">
-        <v>6808791</v>
+        <v>6808240</v>
       </c>
       <c r="S334" t="n">
         <v>10</v>
@@ -36519,12 +36514,12 @@
       </c>
       <c r="Y334" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA334" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD334" t="b">
@@ -36544,17 +36539,17 @@
       </c>
       <c r="AX334" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>123920456</v>
+        <v>123920409</v>
       </c>
       <c r="B335" t="n">
-        <v>56722</v>
+        <v>79399</v>
       </c>
       <c r="C335" t="inlineStr">
         <is>
@@ -36563,43 +36558,38 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E335" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I335" t="inlineStr"/>
-      <c r="M335" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P335" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q335" t="n">
-        <v>458796</v>
+        <v>459764</v>
       </c>
       <c r="R335" t="n">
-        <v>6808681</v>
+        <v>6808338</v>
       </c>
       <c r="S335" t="n">
         <v>10</v>
@@ -36626,12 +36616,12 @@
       </c>
       <c r="Y335" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA335" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD335" t="b">
@@ -36651,17 +36641,17 @@
       </c>
       <c r="AX335" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>123920408</v>
+        <v>123920523</v>
       </c>
       <c r="B336" t="n">
-        <v>79399</v>
+        <v>78547</v>
       </c>
       <c r="C336" t="inlineStr">
         <is>
@@ -36674,21 +36664,21 @@
         </is>
       </c>
       <c r="E336" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I336" t="inlineStr"/>
@@ -36698,10 +36688,10 @@
         </is>
       </c>
       <c r="Q336" t="n">
-        <v>459598</v>
+        <v>458899</v>
       </c>
       <c r="R336" t="n">
-        <v>6808240</v>
+        <v>6808695</v>
       </c>
       <c r="S336" t="n">
         <v>10</v>
@@ -36728,12 +36718,12 @@
       </c>
       <c r="Y336" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA336" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD336" t="b">
@@ -36753,17 +36743,17 @@
       </c>
       <c r="AX336" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>123920409</v>
+        <v>123920684</v>
       </c>
       <c r="B337" t="n">
-        <v>79399</v>
+        <v>78810</v>
       </c>
       <c r="C337" t="inlineStr">
         <is>
@@ -36776,21 +36766,21 @@
         </is>
       </c>
       <c r="E337" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I337" t="inlineStr"/>
@@ -36800,10 +36790,10 @@
         </is>
       </c>
       <c r="Q337" t="n">
-        <v>459764</v>
+        <v>459414</v>
       </c>
       <c r="R337" t="n">
-        <v>6808338</v>
+        <v>6808641</v>
       </c>
       <c r="S337" t="n">
         <v>10</v>
@@ -36830,12 +36820,12 @@
       </c>
       <c r="Y337" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA337" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD337" t="b">
@@ -36855,17 +36845,17 @@
       </c>
       <c r="AX337" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>123920523</v>
+        <v>123920673</v>
       </c>
       <c r="B338" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C338" t="inlineStr">
         <is>
@@ -36878,21 +36868,21 @@
         </is>
       </c>
       <c r="E338" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I338" t="inlineStr"/>
@@ -36902,10 +36892,10 @@
         </is>
       </c>
       <c r="Q338" t="n">
-        <v>458899</v>
+        <v>459011</v>
       </c>
       <c r="R338" t="n">
-        <v>6808695</v>
+        <v>6808662</v>
       </c>
       <c r="S338" t="n">
         <v>10</v>
@@ -36964,7 +36954,7 @@
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>123920673</v>
+        <v>123920808</v>
       </c>
       <c r="B339" t="n">
         <v>78810</v>
@@ -37004,10 +36994,10 @@
         </is>
       </c>
       <c r="Q339" t="n">
-        <v>459011</v>
+        <v>459142</v>
       </c>
       <c r="R339" t="n">
-        <v>6808662</v>
+        <v>6808358</v>
       </c>
       <c r="S339" t="n">
         <v>10</v>
@@ -37034,12 +37024,12 @@
       </c>
       <c r="Y339" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA339" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD339" t="b">
@@ -37059,14 +37049,14 @@
       </c>
       <c r="AX339" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>123920808</v>
+        <v>123920824</v>
       </c>
       <c r="B340" t="n">
         <v>78810</v>
@@ -37106,10 +37096,10 @@
         </is>
       </c>
       <c r="Q340" t="n">
-        <v>459142</v>
+        <v>459567</v>
       </c>
       <c r="R340" t="n">
-        <v>6808358</v>
+        <v>6808306</v>
       </c>
       <c r="S340" t="n">
         <v>10</v>
@@ -37168,7 +37158,7 @@
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>123920824</v>
+        <v>123920810</v>
       </c>
       <c r="B341" t="n">
         <v>78810</v>
@@ -37208,10 +37198,10 @@
         </is>
       </c>
       <c r="Q341" t="n">
-        <v>459567</v>
+        <v>459205</v>
       </c>
       <c r="R341" t="n">
-        <v>6808306</v>
+        <v>6808378</v>
       </c>
       <c r="S341" t="n">
         <v>10</v>
@@ -37270,10 +37260,10 @@
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>123920810</v>
+        <v>123920449</v>
       </c>
       <c r="B342" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C342" t="inlineStr">
         <is>
@@ -37282,38 +37272,43 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E342" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I342" t="inlineStr"/>
+      <c r="M342" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P342" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q342" t="n">
-        <v>459205</v>
+        <v>458862</v>
       </c>
       <c r="R342" t="n">
-        <v>6808378</v>
+        <v>6808791</v>
       </c>
       <c r="S342" t="n">
         <v>10</v>
@@ -37340,12 +37335,12 @@
       </c>
       <c r="Y342" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA342" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD342" t="b">
@@ -37365,17 +37360,17 @@
       </c>
       <c r="AX342" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>123920803</v>
+        <v>123920456</v>
       </c>
       <c r="B343" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C343" t="inlineStr">
         <is>
@@ -37384,38 +37379,43 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E343" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I343" t="inlineStr"/>
+      <c r="M343" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P343" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q343" t="n">
-        <v>459061</v>
+        <v>458796</v>
       </c>
       <c r="R343" t="n">
-        <v>6808332</v>
+        <v>6808681</v>
       </c>
       <c r="S343" t="n">
         <v>10</v>
@@ -37442,12 +37442,12 @@
       </c>
       <c r="Y343" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA343" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD343" t="b">
@@ -37467,7 +37467,7 @@
       </c>
       <c r="AX343" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY343" t="inlineStr"/>
@@ -38698,7 +38698,7 @@
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>123920807</v>
+        <v>123920794</v>
       </c>
       <c r="B356" t="n">
         <v>78810</v>
@@ -38738,10 +38738,10 @@
         </is>
       </c>
       <c r="Q356" t="n">
-        <v>459115</v>
+        <v>458919</v>
       </c>
       <c r="R356" t="n">
-        <v>6808339</v>
+        <v>6808281</v>
       </c>
       <c r="S356" t="n">
         <v>10</v>
@@ -38800,10 +38800,10 @@
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>123920547</v>
+        <v>123920807</v>
       </c>
       <c r="B357" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C357" t="inlineStr">
         <is>
@@ -38816,21 +38816,21 @@
         </is>
       </c>
       <c r="E357" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I357" t="inlineStr"/>
@@ -38840,10 +38840,10 @@
         </is>
       </c>
       <c r="Q357" t="n">
-        <v>459076</v>
+        <v>459115</v>
       </c>
       <c r="R357" t="n">
-        <v>6808337</v>
+        <v>6808339</v>
       </c>
       <c r="S357" t="n">
         <v>10</v>
@@ -39310,10 +39310,10 @@
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>123920794</v>
+        <v>123920547</v>
       </c>
       <c r="B362" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C362" t="inlineStr">
         <is>
@@ -39326,21 +39326,21 @@
         </is>
       </c>
       <c r="E362" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I362" t="inlineStr"/>
@@ -39350,10 +39350,10 @@
         </is>
       </c>
       <c r="Q362" t="n">
-        <v>458919</v>
+        <v>459076</v>
       </c>
       <c r="R362" t="n">
-        <v>6808281</v>
+        <v>6808337</v>
       </c>
       <c r="S362" t="n">
         <v>10</v>
@@ -42696,10 +42696,10 @@
     </row>
     <row r="395">
       <c r="A395" t="n">
-        <v>123920444</v>
+        <v>123920370</v>
       </c>
       <c r="B395" t="n">
-        <v>56722</v>
+        <v>78842</v>
       </c>
       <c r="C395" t="inlineStr">
         <is>
@@ -42708,43 +42708,38 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E395" t="n">
-        <v>100138</v>
+        <v>185</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I395" t="inlineStr"/>
-      <c r="M395" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P395" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q395" t="n">
-        <v>459153</v>
+        <v>459007</v>
       </c>
       <c r="R395" t="n">
-        <v>6808356</v>
+        <v>6808305</v>
       </c>
       <c r="S395" t="n">
         <v>10</v>
@@ -42803,10 +42798,10 @@
     </row>
     <row r="396">
       <c r="A396" t="n">
-        <v>123920549</v>
+        <v>123920591</v>
       </c>
       <c r="B396" t="n">
-        <v>78547</v>
+        <v>78546</v>
       </c>
       <c r="C396" t="inlineStr">
         <is>
@@ -42819,21 +42814,21 @@
         </is>
       </c>
       <c r="E396" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I396" t="inlineStr"/>
@@ -42843,10 +42838,10 @@
         </is>
       </c>
       <c r="Q396" t="n">
-        <v>459425</v>
+        <v>459083</v>
       </c>
       <c r="R396" t="n">
-        <v>6808381</v>
+        <v>6808668</v>
       </c>
       <c r="S396" t="n">
         <v>10</v>
@@ -42873,12 +42868,12 @@
       </c>
       <c r="Y396" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA396" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD396" t="b">
@@ -42898,17 +42893,17 @@
       </c>
       <c r="AX396" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY396" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" t="n">
-        <v>123920525</v>
+        <v>123920827</v>
       </c>
       <c r="B397" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C397" t="inlineStr">
         <is>
@@ -42921,21 +42916,21 @@
         </is>
       </c>
       <c r="E397" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I397" t="inlineStr"/>
@@ -42945,10 +42940,10 @@
         </is>
       </c>
       <c r="Q397" t="n">
-        <v>459300</v>
+        <v>459598</v>
       </c>
       <c r="R397" t="n">
-        <v>6808710</v>
+        <v>6808240</v>
       </c>
       <c r="S397" t="n">
         <v>10</v>
@@ -42975,12 +42970,12 @@
       </c>
       <c r="Y397" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA397" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD397" t="b">
@@ -43000,17 +42995,17 @@
       </c>
       <c r="AX397" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY397" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" t="n">
-        <v>123920406</v>
+        <v>123920799</v>
       </c>
       <c r="B398" t="n">
-        <v>79399</v>
+        <v>78810</v>
       </c>
       <c r="C398" t="inlineStr">
         <is>
@@ -43023,21 +43018,21 @@
         </is>
       </c>
       <c r="E398" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I398" t="inlineStr"/>
@@ -43047,10 +43042,10 @@
         </is>
       </c>
       <c r="Q398" t="n">
-        <v>459448</v>
+        <v>459007</v>
       </c>
       <c r="R398" t="n">
-        <v>6808388</v>
+        <v>6808305</v>
       </c>
       <c r="S398" t="n">
         <v>10</v>
@@ -43102,17 +43097,17 @@
       </c>
       <c r="AX398" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY398" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" t="n">
-        <v>123920370</v>
+        <v>123920830</v>
       </c>
       <c r="B399" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C399" t="inlineStr">
         <is>
@@ -43125,21 +43120,21 @@
         </is>
       </c>
       <c r="E399" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I399" t="inlineStr"/>
@@ -43149,10 +43144,10 @@
         </is>
       </c>
       <c r="Q399" t="n">
-        <v>459007</v>
+        <v>459650</v>
       </c>
       <c r="R399" t="n">
-        <v>6808305</v>
+        <v>6808252</v>
       </c>
       <c r="S399" t="n">
         <v>10</v>
@@ -43204,17 +43199,17 @@
       </c>
       <c r="AX399" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" t="n">
-        <v>123920591</v>
+        <v>123920828</v>
       </c>
       <c r="B400" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C400" t="inlineStr">
         <is>
@@ -43227,21 +43222,21 @@
         </is>
       </c>
       <c r="E400" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I400" t="inlineStr"/>
@@ -43251,10 +43246,10 @@
         </is>
       </c>
       <c r="Q400" t="n">
-        <v>459083</v>
+        <v>459599</v>
       </c>
       <c r="R400" t="n">
-        <v>6808668</v>
+        <v>6808237</v>
       </c>
       <c r="S400" t="n">
         <v>10</v>
@@ -43281,12 +43276,12 @@
       </c>
       <c r="Y400" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA400" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD400" t="b">
@@ -43306,14 +43301,14 @@
       </c>
       <c r="AX400" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY400" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" t="n">
-        <v>123920827</v>
+        <v>123920670</v>
       </c>
       <c r="B401" t="n">
         <v>78810</v>
@@ -43353,10 +43348,10 @@
         </is>
       </c>
       <c r="Q401" t="n">
-        <v>459598</v>
+        <v>458914</v>
       </c>
       <c r="R401" t="n">
-        <v>6808240</v>
+        <v>6808701</v>
       </c>
       <c r="S401" t="n">
         <v>10</v>
@@ -43383,12 +43378,12 @@
       </c>
       <c r="Y401" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA401" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD401" t="b">
@@ -43408,14 +43403,14 @@
       </c>
       <c r="AX401" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY401" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" t="n">
-        <v>123920799</v>
+        <v>123920801</v>
       </c>
       <c r="B402" t="n">
         <v>78810</v>
@@ -43455,10 +43450,10 @@
         </is>
       </c>
       <c r="Q402" t="n">
-        <v>459007</v>
+        <v>459014</v>
       </c>
       <c r="R402" t="n">
-        <v>6808305</v>
+        <v>6808348</v>
       </c>
       <c r="S402" t="n">
         <v>10</v>
@@ -43517,10 +43512,10 @@
     </row>
     <row r="403">
       <c r="A403" t="n">
-        <v>123920830</v>
+        <v>123920444</v>
       </c>
       <c r="B403" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C403" t="inlineStr">
         <is>
@@ -43529,38 +43524,43 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E403" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H403" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I403" t="inlineStr"/>
+      <c r="M403" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P403" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q403" t="n">
-        <v>459650</v>
+        <v>459153</v>
       </c>
       <c r="R403" t="n">
-        <v>6808252</v>
+        <v>6808356</v>
       </c>
       <c r="S403" t="n">
         <v>10</v>
@@ -43612,17 +43612,17 @@
       </c>
       <c r="AX403" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY403" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" t="n">
-        <v>123920828</v>
+        <v>123920549</v>
       </c>
       <c r="B404" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C404" t="inlineStr">
         <is>
@@ -43635,21 +43635,21 @@
         </is>
       </c>
       <c r="E404" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I404" t="inlineStr"/>
@@ -43659,10 +43659,10 @@
         </is>
       </c>
       <c r="Q404" t="n">
-        <v>459599</v>
+        <v>459425</v>
       </c>
       <c r="R404" t="n">
-        <v>6808237</v>
+        <v>6808381</v>
       </c>
       <c r="S404" t="n">
         <v>10</v>
@@ -43721,10 +43721,10 @@
     </row>
     <row r="405">
       <c r="A405" t="n">
-        <v>123920670</v>
+        <v>123920525</v>
       </c>
       <c r="B405" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C405" t="inlineStr">
         <is>
@@ -43737,21 +43737,21 @@
         </is>
       </c>
       <c r="E405" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I405" t="inlineStr"/>
@@ -43761,10 +43761,10 @@
         </is>
       </c>
       <c r="Q405" t="n">
-        <v>458914</v>
+        <v>459300</v>
       </c>
       <c r="R405" t="n">
-        <v>6808701</v>
+        <v>6808710</v>
       </c>
       <c r="S405" t="n">
         <v>10</v>
@@ -43823,10 +43823,10 @@
     </row>
     <row r="406">
       <c r="A406" t="n">
-        <v>123920801</v>
+        <v>123920406</v>
       </c>
       <c r="B406" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C406" t="inlineStr">
         <is>
@@ -43839,21 +43839,21 @@
         </is>
       </c>
       <c r="E406" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I406" t="inlineStr"/>
@@ -43863,10 +43863,10 @@
         </is>
       </c>
       <c r="Q406" t="n">
-        <v>459014</v>
+        <v>459448</v>
       </c>
       <c r="R406" t="n">
-        <v>6808348</v>
+        <v>6808388</v>
       </c>
       <c r="S406" t="n">
         <v>10</v>
@@ -43918,7 +43918,7 @@
       </c>
       <c r="AX406" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY406" t="inlineStr"/>
